--- a/MIGC_Season_Dashboard.xlsx
+++ b/MIGC_Season_Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevinvargas/Desktop/migc-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49C27EB5-A8FE-C645-BB14-EEA13262ED83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80C3186-3B4A-B84A-9520-3A7908B8A5FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="16760" windowHeight="19160" activeTab="1" xr2:uid="{BBF77493-EF1A-3942-9440-E7AC2E03DB26}"/>
+    <workbookView xWindow="16780" yWindow="600" windowWidth="16820" windowHeight="19160" activeTab="3" xr2:uid="{BBF77493-EF1A-3942-9440-E7AC2E03DB26}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Players!$A$1:$D$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Tournament_Acheivements!$A$1:$F$122</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Tournament_Results!$A$1:$L$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Tournament_Skins!$A$1:$F$57</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -590,7 +592,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -674,6 +676,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -762,7 +765,7 @@
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>125</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>101600</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2039,7 +2042,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3B800D8-26AB-5145-974D-2E86BCED24A0}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:N152"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2086,7 +2088,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -2122,7 +2124,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>66</v>
       </c>
@@ -2158,7 +2160,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>66</v>
       </c>
@@ -2197,7 +2199,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>66</v>
       </c>
@@ -2233,7 +2235,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>66</v>
       </c>
@@ -2269,7 +2271,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>66</v>
       </c>
@@ -2305,7 +2307,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -2341,7 +2343,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>66</v>
       </c>
@@ -2377,7 +2379,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>66</v>
       </c>
@@ -2413,7 +2415,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>66</v>
       </c>
@@ -2449,7 +2451,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -2485,7 +2487,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -2521,7 +2523,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>66</v>
       </c>
@@ -2557,7 +2559,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -2593,7 +2595,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="16" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>66</v>
       </c>
@@ -2629,7 +2631,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>66</v>
       </c>
@@ -2665,7 +2667,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>66</v>
       </c>
@@ -2701,7 +2703,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>66</v>
       </c>
@@ -2737,7 +2739,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>66</v>
       </c>
@@ -2773,7 +2775,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>66</v>
       </c>
@@ -2809,7 +2811,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>66</v>
       </c>
@@ -2845,7 +2847,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>66</v>
       </c>
@@ -2881,7 +2883,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>66</v>
       </c>
@@ -2917,7 +2919,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>66</v>
       </c>
@@ -2953,7 +2955,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>66</v>
       </c>
@@ -2989,7 +2991,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -3025,7 +3027,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -3061,7 +3063,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>66</v>
       </c>
@@ -3097,7 +3099,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -3133,7 +3135,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -3169,7 +3171,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -3205,7 +3207,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>66</v>
       </c>
@@ -3241,7 +3243,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>66</v>
       </c>
@@ -3277,7 +3279,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>66</v>
       </c>
@@ -3313,7 +3315,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>66</v>
       </c>
@@ -3349,7 +3351,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>66</v>
       </c>
@@ -3385,7 +3387,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>68</v>
       </c>
@@ -3424,7 +3426,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>68</v>
       </c>
@@ -3461,7 +3463,7 @@
       </c>
       <c r="L39" s="1"/>
     </row>
-    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>68</v>
       </c>
@@ -3498,7 +3500,7 @@
       </c>
       <c r="L40" s="1"/>
     </row>
-    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>68</v>
       </c>
@@ -3535,7 +3537,7 @@
       </c>
       <c r="L41" s="1"/>
     </row>
-    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>68</v>
       </c>
@@ -3571,10 +3573,10 @@
         <v>123</v>
       </c>
       <c r="L42" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>68</v>
       </c>
@@ -3611,7 +3613,7 @@
       </c>
       <c r="L43" s="1"/>
     </row>
-    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>68</v>
       </c>
@@ -3648,7 +3650,7 @@
       </c>
       <c r="L44" s="1"/>
     </row>
-    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>68</v>
       </c>
@@ -3685,7 +3687,7 @@
       </c>
       <c r="L45" s="1"/>
     </row>
-    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>68</v>
       </c>
@@ -3724,7 +3726,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>68</v>
       </c>
@@ -3761,7 +3763,7 @@
       </c>
       <c r="L47" s="1"/>
     </row>
-    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>68</v>
       </c>
@@ -3798,7 +3800,7 @@
       </c>
       <c r="L48" s="1"/>
     </row>
-    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>68</v>
       </c>
@@ -3835,7 +3837,7 @@
       </c>
       <c r="L49" s="1"/>
     </row>
-    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>68</v>
       </c>
@@ -3872,7 +3874,7 @@
       </c>
       <c r="L50" s="1"/>
     </row>
-    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>68</v>
       </c>
@@ -3911,7 +3913,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>68</v>
       </c>
@@ -3950,7 +3952,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>68</v>
       </c>
@@ -3987,7 +3989,7 @@
       </c>
       <c r="L53" s="1"/>
     </row>
-    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>68</v>
       </c>
@@ -4023,10 +4025,10 @@
         <v>123</v>
       </c>
       <c r="L54" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>68</v>
       </c>
@@ -4063,7 +4065,7 @@
       </c>
       <c r="L55" s="1"/>
     </row>
-    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>68</v>
       </c>
@@ -4102,7 +4104,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>68</v>
       </c>
@@ -4139,7 +4141,7 @@
       </c>
       <c r="L57" s="1"/>
     </row>
-    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>68</v>
       </c>
@@ -4176,7 +4178,7 @@
       </c>
       <c r="L58" s="1"/>
     </row>
-    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>68</v>
       </c>
@@ -4213,7 +4215,7 @@
       </c>
       <c r="L59" s="1"/>
     </row>
-    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -4252,7 +4254,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>68</v>
       </c>
@@ -4289,7 +4291,7 @@
       </c>
       <c r="L61" s="1"/>
     </row>
-    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>71</v>
       </c>
@@ -4324,7 +4326,7 @@
       <c r="L62" s="1"/>
       <c r="M62" s="1"/>
     </row>
-    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -4364,7 +4366,7 @@
       </c>
       <c r="M63" s="1"/>
     </row>
-    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>71</v>
       </c>
@@ -4399,7 +4401,7 @@
       <c r="L64" s="25"/>
       <c r="M64" s="1"/>
     </row>
-    <row r="65" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>71</v>
       </c>
@@ -4439,7 +4441,7 @@
       </c>
       <c r="M65" s="1"/>
     </row>
-    <row r="66" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>71</v>
       </c>
@@ -4479,7 +4481,7 @@
       </c>
       <c r="M66" s="1"/>
     </row>
-    <row r="67" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>71</v>
       </c>
@@ -4514,7 +4516,7 @@
       <c r="L67" s="24"/>
       <c r="M67" s="1"/>
     </row>
-    <row r="68" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>71</v>
       </c>
@@ -4549,7 +4551,7 @@
       <c r="L68" s="24"/>
       <c r="M68" s="1"/>
     </row>
-    <row r="69" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>71</v>
       </c>
@@ -4584,7 +4586,7 @@
       <c r="L69" s="24"/>
       <c r="M69" s="1"/>
     </row>
-    <row r="70" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>71</v>
       </c>
@@ -4619,7 +4621,7 @@
       <c r="L70" s="24"/>
       <c r="M70" s="1"/>
     </row>
-    <row r="71" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>71</v>
       </c>
@@ -4654,7 +4656,7 @@
       <c r="L71" s="24"/>
       <c r="M71" s="1"/>
     </row>
-    <row r="72" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>71</v>
       </c>
@@ -4689,7 +4691,7 @@
       <c r="L72" s="24"/>
       <c r="M72" s="1"/>
     </row>
-    <row r="73" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>71</v>
       </c>
@@ -4729,7 +4731,7 @@
       </c>
       <c r="M73" s="1"/>
     </row>
-    <row r="74" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>71</v>
       </c>
@@ -4769,7 +4771,7 @@
       </c>
       <c r="M74" s="1"/>
     </row>
-    <row r="75" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>71</v>
       </c>
@@ -4803,7 +4805,7 @@
       </c>
       <c r="L75" s="24"/>
     </row>
-    <row r="76" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>71</v>
       </c>
@@ -4837,7 +4839,7 @@
       </c>
       <c r="L76" s="24"/>
     </row>
-    <row r="77" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>71</v>
       </c>
@@ -4871,7 +4873,7 @@
       </c>
       <c r="L77" s="24"/>
     </row>
-    <row r="78" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>71</v>
       </c>
@@ -4910,7 +4912,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="79" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>71</v>
       </c>
@@ -4944,7 +4946,7 @@
       </c>
       <c r="L79" s="24"/>
     </row>
-    <row r="80" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>71</v>
       </c>
@@ -4983,7 +4985,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>71</v>
       </c>
@@ -5017,7 +5019,7 @@
       </c>
       <c r="L81" s="24"/>
     </row>
-    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>71</v>
       </c>
@@ -5051,7 +5053,7 @@
       </c>
       <c r="L82" s="24"/>
     </row>
-    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>71</v>
       </c>
@@ -5085,7 +5087,7 @@
       </c>
       <c r="L83" s="24"/>
     </row>
-    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>71</v>
       </c>
@@ -5121,10 +5123,10 @@
         <v>123</v>
       </c>
       <c r="L84" s="24">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>71</v>
       </c>
@@ -5158,7 +5160,7 @@
       </c>
       <c r="L85" s="24"/>
     </row>
-    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>71</v>
       </c>
@@ -5191,7 +5193,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>71</v>
       </c>
@@ -5224,7 +5226,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>71</v>
       </c>
@@ -5257,7 +5259,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>71</v>
       </c>
@@ -5290,7 +5292,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>74</v>
       </c>
@@ -5329,7 +5331,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>74</v>
       </c>
@@ -5363,7 +5365,7 @@
       </c>
       <c r="L91" s="1"/>
     </row>
-    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>74</v>
       </c>
@@ -5397,7 +5399,7 @@
       </c>
       <c r="L92" s="1"/>
     </row>
-    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>74</v>
       </c>
@@ -5436,7 +5438,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>74</v>
       </c>
@@ -5470,7 +5472,7 @@
       </c>
       <c r="L94" s="1"/>
     </row>
-    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>74</v>
       </c>
@@ -5504,7 +5506,7 @@
       </c>
       <c r="L95" s="1"/>
     </row>
-    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>74</v>
       </c>
@@ -5538,7 +5540,7 @@
       </c>
       <c r="L96" s="1"/>
     </row>
-    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>74</v>
       </c>
@@ -5577,7 +5579,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>74</v>
       </c>
@@ -5611,7 +5613,7 @@
       </c>
       <c r="L98" s="1"/>
     </row>
-    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>74</v>
       </c>
@@ -5650,7 +5652,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>74</v>
       </c>
@@ -5686,10 +5688,10 @@
         <v>123</v>
       </c>
       <c r="L100" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>74</v>
       </c>
@@ -5723,7 +5725,7 @@
       </c>
       <c r="L101" s="1"/>
     </row>
-    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>74</v>
       </c>
@@ -5757,7 +5759,7 @@
       </c>
       <c r="L102" s="1"/>
     </row>
-    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>74</v>
       </c>
@@ -5791,7 +5793,7 @@
       </c>
       <c r="L103" s="1"/>
     </row>
-    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>74</v>
       </c>
@@ -5825,7 +5827,7 @@
       </c>
       <c r="L104" s="1"/>
     </row>
-    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>74</v>
       </c>
@@ -5859,7 +5861,7 @@
       </c>
       <c r="L105" s="1"/>
     </row>
-    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>74</v>
       </c>
@@ -5893,7 +5895,7 @@
       </c>
       <c r="L106" s="1"/>
     </row>
-    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>74</v>
       </c>
@@ -5927,7 +5929,7 @@
       </c>
       <c r="L107" s="1"/>
     </row>
-    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>74</v>
       </c>
@@ -5961,7 +5963,7 @@
       </c>
       <c r="L108" s="1"/>
     </row>
-    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>74</v>
       </c>
@@ -6000,7 +6002,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>74</v>
       </c>
@@ -6034,7 +6036,7 @@
       </c>
       <c r="L110" s="1"/>
     </row>
-    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>74</v>
       </c>
@@ -6068,7 +6070,7 @@
       </c>
       <c r="L111" s="1"/>
     </row>
-    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>74</v>
       </c>
@@ -6102,7 +6104,7 @@
       </c>
       <c r="L112" s="1"/>
     </row>
-    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>74</v>
       </c>
@@ -6136,7 +6138,7 @@
       </c>
       <c r="L113" s="1"/>
     </row>
-    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>74</v>
       </c>
@@ -6170,7 +6172,7 @@
       </c>
       <c r="L114" s="1"/>
     </row>
-    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>74</v>
       </c>
@@ -6204,7 +6206,7 @@
       </c>
       <c r="L115" s="1"/>
     </row>
-    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>74</v>
       </c>
@@ -6238,7 +6240,7 @@
       </c>
       <c r="L116" s="1"/>
     </row>
-    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>74</v>
       </c>
@@ -6272,7 +6274,7 @@
       </c>
       <c r="L117" s="1"/>
     </row>
-    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>74</v>
       </c>
@@ -6311,7 +6313,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>74</v>
       </c>
@@ -6345,7 +6347,7 @@
       </c>
       <c r="L119" s="1"/>
     </row>
-    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>74</v>
       </c>
@@ -6379,7 +6381,7 @@
       </c>
       <c r="L120" s="1"/>
     </row>
-    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>74</v>
       </c>
@@ -6413,7 +6415,7 @@
       </c>
       <c r="L121" s="1"/>
     </row>
-    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>74</v>
       </c>
@@ -6447,7 +6449,7 @@
       </c>
       <c r="L122" s="1"/>
     </row>
-    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>74</v>
       </c>
@@ -6486,7 +6488,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>74</v>
       </c>
@@ -7451,17 +7453,7 @@
       <c r="L152" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L150" xr:uid="{F3B800D8-26AB-5145-974D-2E86BCED24A0}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="2026_05"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A125:L150">
-      <sortCondition ref="D2:D150"/>
-      <sortCondition ref="G2:G150"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:L150" xr:uid="{F3B800D8-26AB-5145-974D-2E86BCED24A0}"/>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -7503,161 +7495,161 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B2" s="11">
         <f>_xlfn.XLOOKUP(C2,Players!B:B,Players!A:A)</f>
-        <v>41</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>13</v>
+        <v>34</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E2" s="11">
-        <v>1</v>
+        <v>96</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F2" s="11">
-        <v>70</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B3" s="11">
         <f>_xlfn.XLOOKUP(C3,Players!B:B,Players!A:A)</f>
-        <v>13</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>14</v>
+        <v>32</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>53</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E3" s="11">
-        <v>2</v>
+        <v>96</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F3" s="11">
-        <v>35</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B4" s="11">
         <f>_xlfn.XLOOKUP(C4,Players!B:B,Players!A:A)</f>
-        <v>35</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>15</v>
+        <v>34</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E4" s="11">
-        <v>2</v>
+        <v>96</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F4" s="11">
-        <v>35</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B5" s="11">
         <f>_xlfn.XLOOKUP(C5,Players!B:B,Players!A:A)</f>
-        <v>14</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>26</v>
+        <v>23</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>50</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" s="11">
-        <v>1</v>
+        <v>96</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F5" s="11">
-        <v>65</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B6" s="11">
         <f>_xlfn.XLOOKUP(C6,Players!B:B,Players!A:A)</f>
-        <v>10</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>28</v>
+        <v>34</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E6" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="11">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B7" s="11">
         <f>_xlfn.XLOOKUP(C7,Players!B:B,Players!A:A)</f>
-        <v>43</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>29</v>
+        <v>12</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E7" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" s="11">
-        <v>26</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B8" s="11">
         <f>_xlfn.XLOOKUP(C8,Players!B:B,Players!A:A)</f>
-        <v>41</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>13</v>
+        <v>35</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E8" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="11">
-        <v>21</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B9" s="11">
         <f>_xlfn.XLOOKUP(C9,Players!B:B,Players!A:A)</f>
-        <v>13</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>14</v>
+        <v>36</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>88</v>
@@ -7666,523 +7658,523 @@
         <v>1</v>
       </c>
       <c r="F9" s="11">
-        <v>21</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B10" s="11">
         <f>_xlfn.XLOOKUP(C10,Players!B:B,Players!A:A)</f>
-        <v>14</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>26</v>
+        <v>34</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E10" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="11">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B11" s="11">
         <f>_xlfn.XLOOKUP(C11,Players!B:B,Players!A:A)</f>
-        <v>9</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="E11" s="11">
-        <v>2</v>
+        <v>94</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F11" s="11">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B12" s="11">
         <f>_xlfn.XLOOKUP(C12,Players!B:B,Players!A:A)</f>
-        <v>17</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>17</v>
+        <v>36</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E12" s="11">
         <v>1</v>
       </c>
       <c r="F12" s="11">
-        <v>28</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B13" s="11">
         <f>_xlfn.XLOOKUP(C13,Players!B:B,Players!A:A)</f>
-        <v>15</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>11</v>
+        <v>34</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E13" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="11">
-        <v>14</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B14" s="11">
         <f>_xlfn.XLOOKUP(C14,Players!B:B,Players!A:A)</f>
-        <v>14</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>26</v>
+        <v>12</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E14" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" s="11">
-        <v>19.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B15" s="11">
         <f>_xlfn.XLOOKUP(C15,Players!B:B,Players!A:A)</f>
-        <v>1</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>30</v>
+        <v>35</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E15" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" s="11">
-        <v>19.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11">
         <f>_xlfn.XLOOKUP(C16,Players!B:B,Players!A:A)</f>
-        <v>15</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>19</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
+      </c>
+      <c r="E16" s="11">
+        <v>1</v>
       </c>
       <c r="F16" s="11">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B17" s="11">
         <f>_xlfn.XLOOKUP(C17,Players!B:B,Players!A:A)</f>
-        <v>20</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>18</v>
+        <v>23</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>50</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
+      </c>
+      <c r="E17" s="11">
+        <v>2</v>
       </c>
       <c r="F17" s="11">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B18" s="11">
         <f>_xlfn.XLOOKUP(C18,Players!B:B,Players!A:A)</f>
-        <v>19</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>34</v>
+        <v>9</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>93</v>
+        <v>89</v>
+      </c>
+      <c r="E18" s="11">
+        <v>1</v>
       </c>
       <c r="F18" s="11">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B19" s="11">
         <f>_xlfn.XLOOKUP(C19,Players!B:B,Players!A:A)</f>
-        <v>20</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>26</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>93</v>
+        <v>89</v>
+      </c>
+      <c r="E19" s="11">
+        <v>2</v>
       </c>
       <c r="F19" s="11">
-        <v>27</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B20" s="11">
         <f>_xlfn.XLOOKUP(C20,Players!B:B,Players!A:A)</f>
-        <v>44</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>34</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>93</v>
+        <v>89</v>
+      </c>
+      <c r="E20" s="11">
+        <v>2</v>
       </c>
       <c r="F20" s="11">
-        <v>27</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B21" s="11">
         <f>_xlfn.XLOOKUP(C21,Players!B:B,Players!A:A)</f>
-        <v>29</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>50</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>93</v>
       </c>
       <c r="F21" s="11">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B22" s="11">
         <f>_xlfn.XLOOKUP(C22,Players!B:B,Players!A:A)</f>
-        <v>25</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>38</v>
+        <v>23</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>50</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>93</v>
+        <v>87</v>
+      </c>
+      <c r="E22" s="11">
+        <v>1</v>
       </c>
       <c r="F22" s="11">
-        <v>27</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B23" s="11">
         <f>_xlfn.XLOOKUP(C23,Players!B:B,Players!A:A)</f>
-        <v>1</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>30</v>
+        <v>26</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>19</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>93</v>
+        <v>87</v>
+      </c>
+      <c r="E23" s="11">
+        <v>2</v>
       </c>
       <c r="F23" s="11">
-        <v>27</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="11" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B24" s="11">
         <f>_xlfn.XLOOKUP(C24,Players!B:B,Players!A:A)</f>
-        <v>29</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E24" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24" s="11">
-        <v>90</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B25" s="11">
         <f>_xlfn.XLOOKUP(C25,Players!B:B,Players!A:A)</f>
-        <v>40</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>81</v>
+        <v>28</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E25" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" s="11">
-        <v>54</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B26" s="11">
         <f>_xlfn.XLOOKUP(C26,Players!B:B,Players!A:A)</f>
-        <v>20</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>18</v>
+        <v>12</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E26" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F26" s="11">
-        <v>12</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B27" s="11">
         <f>_xlfn.XLOOKUP(C27,Players!B:B,Players!A:A)</f>
-        <v>10</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>28</v>
+        <v>37</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E27" s="11">
         <v>1</v>
       </c>
       <c r="F27" s="11">
-        <v>72</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B28" s="11">
         <f>_xlfn.XLOOKUP(C28,Players!B:B,Players!A:A)</f>
-        <v>19</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E28" s="11">
         <v>1</v>
       </c>
       <c r="F28" s="11">
-        <v>72</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B29" s="11">
         <f>_xlfn.XLOOKUP(C29,Players!B:B,Players!A:A)</f>
-        <v>18</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>33</v>
+        <v>25</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>38</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E29" s="11">
-        <v>3</v>
+        <v>96</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F29" s="11">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B30" s="11">
         <f>_xlfn.XLOOKUP(C30,Players!B:B,Players!A:A)</f>
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E30" s="11">
-        <v>1</v>
+        <v>96</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F30" s="11">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B31" s="11">
         <f>_xlfn.XLOOKUP(C31,Players!B:B,Players!A:A)</f>
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E31" s="11">
-        <v>1</v>
+        <v>96</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F31" s="11">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B32" s="11">
         <f>_xlfn.XLOOKUP(C32,Players!B:B,Players!A:A)</f>
-        <v>19</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>34</v>
+        <v>24</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>31</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="E32" s="11">
-        <v>1</v>
+        <v>96</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F32" s="11">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B33" s="11">
         <f>_xlfn.XLOOKUP(C33,Players!B:B,Players!A:A)</f>
+        <v>20</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E33" s="11">
         <v>1</v>
       </c>
-      <c r="C33" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="E33" s="11">
-        <v>2</v>
-      </c>
       <c r="F33" s="11">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B34" s="11">
         <f>_xlfn.XLOOKUP(C34,Players!B:B,Players!A:A)</f>
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>90</v>
@@ -8191,103 +8183,103 @@
         <v>1</v>
       </c>
       <c r="F34" s="11">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B35" s="11">
         <f>_xlfn.XLOOKUP(C35,Players!B:B,Players!A:A)</f>
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>90</v>
       </c>
       <c r="E35" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35" s="11">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B36" s="11">
         <f>_xlfn.XLOOKUP(C36,Players!B:B,Players!A:A)</f>
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E36" s="11">
         <v>1</v>
       </c>
       <c r="F36" s="11">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B37" s="11">
         <f>_xlfn.XLOOKUP(C37,Players!B:B,Players!A:A)</f>
+        <v>20</v>
+      </c>
+      <c r="C37" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C37" s="11" t="s">
-        <v>33</v>
-      </c>
       <c r="D37" s="11" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E37" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37" s="11">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B38" s="11">
         <f>_xlfn.XLOOKUP(C38,Players!B:B,Players!A:A)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>93</v>
+        <v>88</v>
+      </c>
+      <c r="E38" s="11">
+        <v>2</v>
       </c>
       <c r="F38" s="11">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B39" s="11">
         <f>_xlfn.XLOOKUP(C39,Players!B:B,Players!A:A)</f>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>94</v>
@@ -8296,151 +8288,151 @@
         <v>93</v>
       </c>
       <c r="F39" s="11">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B40" s="11">
         <f>_xlfn.XLOOKUP(C40,Players!B:B,Players!A:A)</f>
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>93</v>
+        <v>86</v>
+      </c>
+      <c r="E40" s="11">
+        <v>1</v>
       </c>
       <c r="F40" s="11">
-        <v>36</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B41" s="11">
         <f>_xlfn.XLOOKUP(C41,Players!B:B,Players!A:A)</f>
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>93</v>
+        <v>86</v>
+      </c>
+      <c r="E41" s="11">
+        <v>2</v>
       </c>
       <c r="F41" s="11">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B42" s="11">
         <f>_xlfn.XLOOKUP(C42,Players!B:B,Players!A:A)</f>
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>93</v>
+        <v>86</v>
+      </c>
+      <c r="E42" s="11">
+        <v>3</v>
       </c>
       <c r="F42" s="11">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B43" s="11">
         <f>_xlfn.XLOOKUP(C43,Players!B:B,Players!A:A)</f>
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E43" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
+      </c>
+      <c r="E43" s="11">
+        <v>1</v>
       </c>
       <c r="F43" s="11">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B44" s="11">
         <f>_xlfn.XLOOKUP(C44,Players!B:B,Players!A:A)</f>
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
+      </c>
+      <c r="E44" s="11">
+        <v>2</v>
       </c>
       <c r="F44" s="11">
-        <v>45</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B45" s="11">
         <f>_xlfn.XLOOKUP(C45,Players!B:B,Players!A:A)</f>
-        <v>7</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E45" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F45" s="11">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B46" s="11">
         <f>_xlfn.XLOOKUP(C46,Players!B:B,Players!A:A)</f>
-        <v>15</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E46" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F46" s="11">
         <v>12</v>
@@ -8448,490 +8440,490 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B47" s="11">
         <f>_xlfn.XLOOKUP(C47,Players!B:B,Players!A:A)</f>
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E47" s="11">
-        <v>2</v>
+        <v>95</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F47" s="11">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B48" s="11">
         <f>_xlfn.XLOOKUP(C48,Players!B:B,Players!A:A)</f>
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E48" s="11">
         <v>1</v>
       </c>
       <c r="F48" s="11">
-        <v>123.5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B49" s="11">
         <f>_xlfn.XLOOKUP(C49,Players!B:B,Players!A:A)</f>
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E49" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" s="11">
-        <v>123.5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B50" s="11">
         <f>_xlfn.XLOOKUP(C50,Players!B:B,Players!A:A)</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E50" s="11">
         <v>3</v>
       </c>
       <c r="F50" s="11">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B51" s="11">
         <f>_xlfn.XLOOKUP(C51,Players!B:B,Players!A:A)</f>
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E51" s="11">
-        <v>1</v>
+        <v>92</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F51" s="11">
-        <v>95</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B52" s="11">
         <f>_xlfn.XLOOKUP(C52,Players!B:B,Players!A:A)</f>
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E52" s="11">
-        <v>2</v>
+        <v>96</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F52" s="11">
-        <v>57</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B53" s="11">
         <f>_xlfn.XLOOKUP(C53,Players!B:B,Players!A:A)</f>
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E53" s="11">
-        <v>3</v>
+        <v>96</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F53" s="11">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B54" s="11">
         <f>_xlfn.XLOOKUP(C54,Players!B:B,Players!A:A)</f>
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E54" s="11">
-        <v>1</v>
+        <v>96</v>
+      </c>
+      <c r="E54" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F54" s="11">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B55" s="11">
         <f>_xlfn.XLOOKUP(C55,Players!B:B,Players!A:A)</f>
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E55" s="11">
-        <v>2</v>
+        <v>96</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F55" s="11">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B56" s="11">
         <f>_xlfn.XLOOKUP(C56,Players!B:B,Players!A:A)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E56" s="11">
         <v>1</v>
       </c>
       <c r="F56" s="11">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B57" s="11">
         <f>_xlfn.XLOOKUP(C57,Players!B:B,Players!A:A)</f>
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E57" s="11">
         <v>2</v>
       </c>
       <c r="F57" s="11">
-        <v>9.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B58" s="11">
         <f>_xlfn.XLOOKUP(C58,Players!B:B,Players!A:A)</f>
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="D58" s="11" t="s">
         <v>90</v>
       </c>
       <c r="E58" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58" s="11">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B59" s="11">
         <f>_xlfn.XLOOKUP(C59,Players!B:B,Players!A:A)</f>
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E59" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F59" s="11">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B60" s="11">
         <f>_xlfn.XLOOKUP(C60,Players!B:B,Players!A:A)</f>
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E60" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" s="11">
-        <v>38</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B61" s="11">
         <f>_xlfn.XLOOKUP(C61,Players!B:B,Players!A:A)</f>
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E61" s="11">
-        <v>2</v>
+        <v>94</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F61" s="11">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B62" s="11">
         <f>_xlfn.XLOOKUP(C62,Players!B:B,Players!A:A)</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E62" s="11">
         <v>1</v>
       </c>
       <c r="F62" s="11">
-        <v>12.66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B63" s="11">
         <f>_xlfn.XLOOKUP(C63,Players!B:B,Players!A:A)</f>
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="E63" s="11" t="s">
-        <v>93</v>
+        <v>86</v>
+      </c>
+      <c r="E63" s="11">
+        <v>1</v>
       </c>
       <c r="F63" s="11">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B64" s="11">
         <f>_xlfn.XLOOKUP(C64,Players!B:B,Players!A:A)</f>
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E64" s="11" t="s">
-        <v>93</v>
+        <v>86</v>
+      </c>
+      <c r="E64" s="11">
+        <v>3</v>
       </c>
       <c r="F64" s="11">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B65" s="11">
         <f>_xlfn.XLOOKUP(C65,Players!B:B,Players!A:A)</f>
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E65" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
+      </c>
+      <c r="E65" s="11">
+        <v>1</v>
       </c>
       <c r="F65" s="11">
-        <v>47.5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B66" s="11">
         <f>_xlfn.XLOOKUP(C66,Players!B:B,Players!A:A)</f>
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E66" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
+      </c>
+      <c r="E66" s="11">
+        <v>2</v>
       </c>
       <c r="F66" s="11">
-        <v>47.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B67" s="11">
         <f>_xlfn.XLOOKUP(C67,Players!B:B,Players!A:A)</f>
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E67" s="11" t="s">
-        <v>93</v>
+        <v>89</v>
+      </c>
+      <c r="E67" s="11">
+        <v>1</v>
       </c>
       <c r="F67" s="11">
-        <v>47.5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B68" s="11">
         <f>_xlfn.XLOOKUP(C68,Players!B:B,Players!A:A)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E68" s="11" t="s">
-        <v>93</v>
+        <v>89</v>
+      </c>
+      <c r="E68" s="11">
+        <v>2</v>
       </c>
       <c r="F68" s="11">
-        <v>47.5</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B69" s="11">
         <f>_xlfn.XLOOKUP(C69,Players!B:B,Players!A:A)</f>
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E69" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F69" s="11">
-        <v>19</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B70" s="11">
         <f>_xlfn.XLOOKUP(C70,Players!B:B,Players!A:A)</f>
@@ -8941,763 +8933,763 @@
         <v>35</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E70" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F70" s="11">
-        <v>19</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B71" s="11">
         <f>_xlfn.XLOOKUP(C71,Players!B:B,Players!A:A)</f>
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E71" s="11">
-        <v>2</v>
+        <v>95</v>
+      </c>
+      <c r="E71" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F71" s="11">
-        <v>9.5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B72" s="11">
         <f>_xlfn.XLOOKUP(C72,Players!B:B,Players!A:A)</f>
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E72" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F72" s="11">
-        <v>9.5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B73" s="11">
         <f>_xlfn.XLOOKUP(C73,Players!B:B,Players!A:A)</f>
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E73" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" s="11">
-        <v>12.66</v>
+        <v>42</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B74" s="11">
         <f>_xlfn.XLOOKUP(C74,Players!B:B,Players!A:A)</f>
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E74" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F74" s="11">
-        <v>12.66</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B75" s="11">
         <f>_xlfn.XLOOKUP(C75,Players!B:B,Players!A:A)</f>
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E75" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F75" s="11">
-        <v>60</v>
+        <v>14</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B76" s="11">
         <f>_xlfn.XLOOKUP(C76,Players!B:B,Players!A:A)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E76" s="11">
-        <v>2</v>
+        <v>92</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F76" s="11">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B77" s="11">
         <f>_xlfn.XLOOKUP(C77,Players!B:B,Players!A:A)</f>
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E77" s="11">
-        <v>3</v>
+        <v>96</v>
+      </c>
+      <c r="E77" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F77" s="11">
-        <v>24</v>
+        <v>45</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B78" s="11">
         <f>_xlfn.XLOOKUP(C78,Players!B:B,Players!A:A)</f>
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E78" s="11">
-        <v>1</v>
+        <v>96</v>
+      </c>
+      <c r="E78" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F78" s="11">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B79" s="11">
         <f>_xlfn.XLOOKUP(C79,Players!B:B,Players!A:A)</f>
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E79" s="11">
-        <v>2</v>
+        <v>96</v>
+      </c>
+      <c r="E79" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F79" s="11">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B80" s="11">
         <f>_xlfn.XLOOKUP(C80,Players!B:B,Players!A:A)</f>
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E80" s="11">
-        <v>3</v>
+        <v>96</v>
+      </c>
+      <c r="E80" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F80" s="11">
-        <v>24</v>
+        <v>45</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B81" s="11">
         <f>_xlfn.XLOOKUP(C81,Players!B:B,Players!A:A)</f>
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E81" s="11">
         <v>1</v>
       </c>
       <c r="F81" s="11">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B82" s="11">
         <f>_xlfn.XLOOKUP(C82,Players!B:B,Players!A:A)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E82" s="11">
         <v>2</v>
       </c>
       <c r="F82" s="11">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B83" s="11">
         <f>_xlfn.XLOOKUP(C83,Players!B:B,Players!A:A)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E83" s="11">
         <v>1</v>
       </c>
       <c r="F83" s="11">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B84" s="11">
         <f>_xlfn.XLOOKUP(C84,Players!B:B,Players!A:A)</f>
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E84" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" s="11">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B85" s="11">
         <f>_xlfn.XLOOKUP(C85,Players!B:B,Players!A:A)</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E85" s="11">
-        <v>1</v>
+        <v>94</v>
+      </c>
+      <c r="E85" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F85" s="11">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B86" s="11">
         <f>_xlfn.XLOOKUP(C86,Players!B:B,Players!A:A)</f>
-        <v>26</v>
-      </c>
-      <c r="C86" s="11" t="s">
-        <v>19</v>
+        <v>29</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>20</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E86" s="11">
         <v>1</v>
       </c>
       <c r="F86" s="11">
-        <v>24</v>
+        <v>90</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B87" s="11">
         <f>_xlfn.XLOOKUP(C87,Players!B:B,Players!A:A)</f>
-        <v>18</v>
-      </c>
-      <c r="C87" s="11" t="s">
-        <v>33</v>
+        <v>40</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>81</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E87" s="11">
         <v>2</v>
       </c>
       <c r="F87" s="11">
-        <v>6</v>
+        <v>54</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B88" s="11">
         <f>_xlfn.XLOOKUP(C88,Players!B:B,Players!A:A)</f>
         <v>20</v>
       </c>
-      <c r="C88" s="11" t="s">
+      <c r="C88" s="9" t="s">
         <v>18</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="E88" s="11" t="s">
-        <v>93</v>
+        <v>86</v>
+      </c>
+      <c r="E88" s="11">
+        <v>3</v>
       </c>
       <c r="F88" s="11">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B89" s="11">
         <f>_xlfn.XLOOKUP(C89,Players!B:B,Players!A:A)</f>
-        <v>20</v>
-      </c>
-      <c r="C89" s="11" t="s">
-        <v>18</v>
+        <v>7</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="E89" s="11" t="s">
-        <v>93</v>
+        <v>86</v>
+      </c>
+      <c r="E89" s="11">
+        <v>3</v>
       </c>
       <c r="F89" s="11">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" s="11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B90" s="11">
         <f>_xlfn.XLOOKUP(C90,Players!B:B,Players!A:A)</f>
-        <v>26</v>
-      </c>
-      <c r="C90" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="C90" s="9" t="s">
+        <v>11</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E90" s="11" t="s">
-        <v>93</v>
+        <v>86</v>
+      </c>
+      <c r="E90" s="11">
+        <v>3</v>
       </c>
       <c r="F90" s="11">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B91" s="11">
         <f>_xlfn.XLOOKUP(C91,Players!B:B,Players!A:A)</f>
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E91" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
+      </c>
+      <c r="E91" s="11">
+        <v>1</v>
       </c>
       <c r="F91" s="11">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B92" s="11">
         <f>_xlfn.XLOOKUP(C92,Players!B:B,Players!A:A)</f>
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E92" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
+      </c>
+      <c r="E92" s="11">
+        <v>2</v>
       </c>
       <c r="F92" s="11">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" s="11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B93" s="11">
         <f>_xlfn.XLOOKUP(C93,Players!B:B,Players!A:A)</f>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E93" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
+      </c>
+      <c r="E93" s="11">
+        <v>2</v>
       </c>
       <c r="F93" s="11">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" s="11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B94" s="11">
         <f>_xlfn.XLOOKUP(C94,Players!B:B,Players!A:A)</f>
-        <v>24</v>
-      </c>
-      <c r="C94" s="11" t="s">
-        <v>31</v>
+        <v>19</v>
+      </c>
+      <c r="C94" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E94" s="11" t="s">
-        <v>93</v>
+        <v>89</v>
+      </c>
+      <c r="E94" s="11">
+        <v>1</v>
       </c>
       <c r="F94" s="11">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B95" s="11">
         <f>_xlfn.XLOOKUP(C95,Players!B:B,Players!A:A)</f>
-        <v>6</v>
-      </c>
-      <c r="C95" s="11" t="s">
-        <v>22</v>
+        <v>1</v>
+      </c>
+      <c r="C95" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E95" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" s="11">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B96" s="11">
         <f>_xlfn.XLOOKUP(C96,Players!B:B,Players!A:A)</f>
+        <v>28</v>
+      </c>
+      <c r="C96" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D96" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="E96" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="F96" s="11">
         <v>36</v>
-      </c>
-      <c r="C96" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D96" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E96" s="11">
-        <v>1</v>
-      </c>
-      <c r="F96" s="11">
-        <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B97" s="11">
         <f>_xlfn.XLOOKUP(C97,Players!B:B,Players!A:A)</f>
+        <v>10</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D97" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E97" s="11">
         <v>1</v>
       </c>
-      <c r="C97" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D97" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E97" s="11">
-        <v>2</v>
-      </c>
       <c r="F97" s="11">
-        <v>6</v>
+        <v>72</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="11" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B98" s="11">
         <f>_xlfn.XLOOKUP(C98,Players!B:B,Players!A:A)</f>
-        <v>6</v>
-      </c>
-      <c r="C98" s="11" t="s">
-        <v>22</v>
+        <v>19</v>
+      </c>
+      <c r="C98" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E98" s="11">
         <v>1</v>
       </c>
       <c r="F98" s="11">
-        <v>56</v>
+        <v>72</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="11" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B99" s="11">
         <f>_xlfn.XLOOKUP(C99,Players!B:B,Players!A:A)</f>
-        <v>8</v>
-      </c>
-      <c r="C99" s="11" t="s">
-        <v>44</v>
+        <v>18</v>
+      </c>
+      <c r="C99" s="9" t="s">
+        <v>33</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E99" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F99" s="11">
-        <v>56</v>
+        <v>36</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="11" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B100" s="11">
         <f>_xlfn.XLOOKUP(C100,Players!B:B,Players!A:A)</f>
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E100" s="11">
-        <v>3</v>
+        <v>92</v>
+      </c>
+      <c r="E100" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F100" s="11">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="11" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B101" s="11">
         <f>_xlfn.XLOOKUP(C101,Players!B:B,Players!A:A)</f>
-        <v>24</v>
-      </c>
-      <c r="C101" s="11" t="s">
-        <v>31</v>
+        <v>20</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E101" s="11">
-        <v>1</v>
+        <v>96</v>
+      </c>
+      <c r="E101" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F101" s="11">
-        <v>70</v>
+        <v>27</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="11" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B102" s="11">
         <f>_xlfn.XLOOKUP(C102,Players!B:B,Players!A:A)</f>
-        <v>1</v>
-      </c>
-      <c r="C102" s="11" t="s">
-        <v>30</v>
+        <v>44</v>
+      </c>
+      <c r="C102" s="9" t="s">
+        <v>23</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E102" s="11">
-        <v>2</v>
+        <v>96</v>
+      </c>
+      <c r="E102" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F102" s="11">
-        <v>42</v>
+        <v>27</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="11" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B103" s="11">
         <f>_xlfn.XLOOKUP(C103,Players!B:B,Players!A:A)</f>
-        <v>26</v>
-      </c>
-      <c r="C103" s="11" t="s">
-        <v>19</v>
+        <v>29</v>
+      </c>
+      <c r="C103" s="9" t="s">
+        <v>20</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E103" s="11">
-        <v>3</v>
+        <v>96</v>
+      </c>
+      <c r="E103" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F103" s="11">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="11" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B104" s="11">
         <f>_xlfn.XLOOKUP(C104,Players!B:B,Players!A:A)</f>
-        <v>29</v>
-      </c>
-      <c r="C104" s="11" t="s">
-        <v>20</v>
+        <v>25</v>
+      </c>
+      <c r="C104" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E104" s="11">
-        <v>1</v>
+        <v>96</v>
+      </c>
+      <c r="E104" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F104" s="11">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="11" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B105" s="11">
         <f>_xlfn.XLOOKUP(C105,Players!B:B,Players!A:A)</f>
-        <v>6</v>
-      </c>
-      <c r="C105" s="11" t="s">
-        <v>22</v>
+        <v>1</v>
+      </c>
+      <c r="C105" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E105" s="11">
-        <v>2</v>
+        <v>96</v>
+      </c>
+      <c r="E105" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F105" s="11">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="11" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B106" s="11">
         <f>_xlfn.XLOOKUP(C106,Players!B:B,Players!A:A)</f>
-        <v>26</v>
-      </c>
-      <c r="C106" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="C106" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E106" s="11">
         <v>1</v>
@@ -9708,83 +9700,83 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="11" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B107" s="11">
         <f>_xlfn.XLOOKUP(C107,Players!B:B,Players!A:A)</f>
-        <v>24</v>
-      </c>
-      <c r="C107" s="11" t="s">
-        <v>31</v>
+        <v>15</v>
+      </c>
+      <c r="C107" s="9" t="s">
+        <v>11</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E107" s="11">
         <v>2</v>
       </c>
       <c r="F107" s="11">
-        <v>4.6500000000000004</v>
+        <v>14</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="11" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B108" s="11">
         <f>_xlfn.XLOOKUP(C108,Players!B:B,Players!A:A)</f>
-        <v>8</v>
-      </c>
-      <c r="C108" s="11" t="s">
-        <v>44</v>
+        <v>41</v>
+      </c>
+      <c r="C108" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E108" s="11">
         <v>1</v>
       </c>
       <c r="F108" s="11">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="11" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B109" s="11">
         <f>_xlfn.XLOOKUP(C109,Players!B:B,Players!A:A)</f>
-        <v>6</v>
-      </c>
-      <c r="C109" s="11" t="s">
-        <v>22</v>
+        <v>13</v>
+      </c>
+      <c r="C109" s="9" t="s">
+        <v>14</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E109" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F109" s="11">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="11" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B110" s="11">
         <f>_xlfn.XLOOKUP(C110,Players!B:B,Players!A:A)</f>
-        <v>24</v>
-      </c>
-      <c r="C110" s="11" t="s">
-        <v>31</v>
+        <v>20</v>
+      </c>
+      <c r="C110" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E110" s="11">
-        <v>1</v>
+        <v>94</v>
+      </c>
+      <c r="E110" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="F110" s="11">
         <v>28</v>
@@ -9792,257 +9784,262 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="11" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B111" s="11">
         <f>_xlfn.XLOOKUP(C111,Players!B:B,Players!A:A)</f>
+        <v>41</v>
+      </c>
+      <c r="C111" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D111" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E111" s="11">
         <v>1</v>
       </c>
-      <c r="C111" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D111" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E111" s="11">
-        <v>2</v>
-      </c>
       <c r="F111" s="11">
-        <v>14</v>
+        <v>70</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="11" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B112" s="11">
         <f>_xlfn.XLOOKUP(C112,Players!B:B,Players!A:A)</f>
-        <v>1</v>
-      </c>
-      <c r="C112" s="11" t="s">
-        <v>30</v>
+        <v>13</v>
+      </c>
+      <c r="C112" s="9" t="s">
+        <v>14</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="E112" s="11" t="s">
-        <v>93</v>
+        <v>86</v>
+      </c>
+      <c r="E112" s="11">
+        <v>2</v>
       </c>
       <c r="F112" s="11">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="11" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B113" s="11">
         <f>_xlfn.XLOOKUP(C113,Players!B:B,Players!A:A)</f>
-        <v>32</v>
-      </c>
-      <c r="C113" s="11" t="s">
-        <v>53</v>
+        <v>35</v>
+      </c>
+      <c r="C113" s="9" t="s">
+        <v>15</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="E113" s="11" t="s">
-        <v>93</v>
+        <v>86</v>
+      </c>
+      <c r="E113" s="11">
+        <v>2</v>
       </c>
       <c r="F113" s="11">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="11" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B114" s="11">
         <f>_xlfn.XLOOKUP(C114,Players!B:B,Players!A:A)</f>
-        <v>24</v>
-      </c>
-      <c r="C114" s="11" t="s">
-        <v>31</v>
+        <v>14</v>
+      </c>
+      <c r="C114" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E114" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
+      </c>
+      <c r="E114" s="11">
+        <v>1</v>
       </c>
       <c r="F114" s="11">
-        <v>28</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="11" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B115" s="11">
         <f>_xlfn.XLOOKUP(C115,Players!B:B,Players!A:A)</f>
-        <v>20</v>
-      </c>
-      <c r="C115" s="11" t="s">
-        <v>18</v>
+        <v>1</v>
+      </c>
+      <c r="C115" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E115" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
+      </c>
+      <c r="E115" s="11">
+        <v>1</v>
       </c>
       <c r="F115" s="11">
-        <v>35</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="11" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B116" s="11">
         <f>_xlfn.XLOOKUP(C116,Players!B:B,Players!A:A)</f>
+        <v>14</v>
+      </c>
+      <c r="C116" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C116" s="11" t="s">
-        <v>19</v>
-      </c>
       <c r="D116" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E116" s="11" t="s">
-        <v>93</v>
+        <v>89</v>
+      </c>
+      <c r="E116" s="11">
+        <v>1</v>
       </c>
       <c r="F116" s="11">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="11" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B117" s="11">
         <f>_xlfn.XLOOKUP(C117,Players!B:B,Players!A:A)</f>
-        <v>8</v>
-      </c>
-      <c r="C117" s="11" t="s">
-        <v>44</v>
+        <v>9</v>
+      </c>
+      <c r="C117" s="9" t="s">
+        <v>37</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E117" s="11" t="s">
-        <v>93</v>
+        <v>89</v>
+      </c>
+      <c r="E117" s="11">
+        <v>2</v>
       </c>
       <c r="F117" s="11">
-        <v>35</v>
+        <v>13</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="11" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B118" s="11">
         <f>_xlfn.XLOOKUP(C118,Players!B:B,Players!A:A)</f>
-        <v>2</v>
-      </c>
-      <c r="C118" s="11" t="s">
-        <v>41</v>
+        <v>19</v>
+      </c>
+      <c r="C118" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E118" s="11" t="s">
         <v>93</v>
       </c>
       <c r="F118" s="11">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="11" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B119" s="11">
         <f>_xlfn.XLOOKUP(C119,Players!B:B,Players!A:A)</f>
-        <v>28</v>
-      </c>
-      <c r="C119" s="11" t="s">
-        <v>35</v>
+        <v>14</v>
+      </c>
+      <c r="C119" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="D119" s="11" t="s">
         <v>87</v>
       </c>
       <c r="E119" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F119" s="11">
-        <v>14</v>
+        <v>65</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" s="11" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B120" s="11">
         <f>_xlfn.XLOOKUP(C120,Players!B:B,Players!A:A)</f>
-        <v>1</v>
-      </c>
-      <c r="C120" s="11" t="s">
-        <v>30</v>
+        <v>10</v>
+      </c>
+      <c r="C120" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E120" s="11">
         <v>2</v>
       </c>
       <c r="F120" s="11">
-        <v>4.6500000000000004</v>
+        <v>39</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" s="11" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B121" s="11">
         <f>_xlfn.XLOOKUP(C121,Players!B:B,Players!A:A)</f>
-        <v>28</v>
-      </c>
-      <c r="C121" s="11" t="s">
-        <v>35</v>
+        <v>43</v>
+      </c>
+      <c r="C121" s="9" t="s">
+        <v>29</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E121" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F121" s="11">
-        <v>4.6500000000000004</v>
+        <v>26</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="11" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B122" s="11">
         <f>_xlfn.XLOOKUP(C122,Players!B:B,Players!A:A)</f>
+        <v>15</v>
+      </c>
+      <c r="C122" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D122" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="E122" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="F122" s="11">
         <v>27</v>
       </c>
-      <c r="C122" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D122" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E122" s="11">
-        <v>2</v>
-      </c>
-      <c r="F122" s="11">
-        <v>7</v>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F122" xr:uid="{45C531C9-F436-4F48-BF76-4EB6DECD4D79}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F122">
+    <sortCondition ref="A2:A122"/>
+    <sortCondition ref="D2:D122"/>
+  </sortState>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10078,56 +10075,56 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B2">
         <f>_xlfn.XLOOKUP(C2,Players!B:B,Players!A:A)</f>
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
         <v>98</v>
       </c>
       <c r="E2" s="1">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>126</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B3">
         <f>_xlfn.XLOOKUP(C3,Players!B:B,Players!A:A)</f>
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
         <v>98</v>
       </c>
       <c r="E3" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>42</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B4">
         <f>_xlfn.XLOOKUP(C4,Players!B:B,Players!A:A)</f>
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
         <v>98</v>
@@ -10136,103 +10133,103 @@
         <v>3</v>
       </c>
       <c r="F4">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B5">
         <f>_xlfn.XLOOKUP(C5,Players!B:B,Players!A:A)</f>
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
         <v>98</v>
       </c>
       <c r="E5" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>42</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B6">
         <f>_xlfn.XLOOKUP(C6,Players!B:B,Players!A:A)</f>
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E6" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B7">
         <f>_xlfn.XLOOKUP(C7,Players!B:B,Players!A:A)</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
         <v>99</v>
       </c>
       <c r="E7" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B8">
         <f>_xlfn.XLOOKUP(C8,Players!B:B,Players!A:A)</f>
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
         <v>99</v>
       </c>
       <c r="E8" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B9">
         <f>_xlfn.XLOOKUP(C9,Players!B:B,Players!A:A)</f>
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
         <v>99</v>
@@ -10241,151 +10238,151 @@
         <v>2</v>
       </c>
       <c r="F9">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B10">
         <f>_xlfn.XLOOKUP(C10,Players!B:B,Players!A:A)</f>
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
         <v>99</v>
       </c>
       <c r="E10" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10">
-        <v>26</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B11">
         <f>_xlfn.XLOOKUP(C11,Players!B:B,Players!A:A)</f>
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
         <v>99</v>
       </c>
       <c r="E11" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B12">
         <f>_xlfn.XLOOKUP(C12,Players!B:B,Players!A:A)</f>
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
         <v>99</v>
       </c>
       <c r="E12" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F12">
-        <v>13</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B13">
         <f>_xlfn.XLOOKUP(C13,Players!B:B,Players!A:A)</f>
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E13" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F13">
-        <v>36</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B14">
         <f>_xlfn.XLOOKUP(C14,Players!B:B,Players!A:A)</f>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
         <v>98</v>
       </c>
       <c r="E14" s="1">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F14">
-        <v>288</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B15">
         <f>_xlfn.XLOOKUP(C15,Players!B:B,Players!A:A)</f>
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E15" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B16">
         <f>_xlfn.XLOOKUP(C16,Players!B:B,Players!A:A)</f>
-        <v>10</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>28</v>
+        <v>5</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="D16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E16" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16">
         <v>36</v>
@@ -10393,49 +10390,49 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B17">
         <f>_xlfn.XLOOKUP(C17,Players!B:B,Players!A:A)</f>
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E17" s="1">
         <v>3</v>
       </c>
       <c r="F17">
-        <v>54</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B18">
         <f>_xlfn.XLOOKUP(C18,Players!B:B,Players!A:A)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E18" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F18">
-        <v>72</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B19">
         <f>_xlfn.XLOOKUP(C19,Players!B:B,Players!A:A)</f>
@@ -10448,490 +10445,490 @@
         <v>99</v>
       </c>
       <c r="E19" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>72</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B20">
         <f>_xlfn.XLOOKUP(C20,Players!B:B,Players!A:A)</f>
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
         <v>99</v>
       </c>
       <c r="E20" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>72</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B21">
         <f>_xlfn.XLOOKUP(C21,Players!B:B,Players!A:A)</f>
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E21" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B22">
         <f>_xlfn.XLOOKUP(C22,Players!B:B,Players!A:A)</f>
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E22" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>95</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B23">
         <f>_xlfn.XLOOKUP(C23,Players!B:B,Players!A:A)</f>
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="D23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E23" s="1">
         <v>3</v>
       </c>
       <c r="F23">
-        <v>57</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B24">
         <f>_xlfn.XLOOKUP(C24,Players!B:B,Players!A:A)</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D24" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E24" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>76</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B25">
         <f>_xlfn.XLOOKUP(C25,Players!B:B,Players!A:A)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D25" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E25" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F25">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B26">
         <f>_xlfn.XLOOKUP(C26,Players!B:B,Players!A:A)</f>
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E26" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B27">
         <f>_xlfn.XLOOKUP(C27,Players!B:B,Players!A:A)</f>
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="D27" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E27" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B28">
         <f>_xlfn.XLOOKUP(C28,Players!B:B,Players!A:A)</f>
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="D28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E28" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B29">
         <f>_xlfn.XLOOKUP(C29,Players!B:B,Players!A:A)</f>
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D29" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E29" s="1">
         <v>3</v>
       </c>
       <c r="F29">
-        <v>57</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B30">
         <f>_xlfn.XLOOKUP(C30,Players!B:B,Players!A:A)</f>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="D30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E30" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B31">
         <f>_xlfn.XLOOKUP(C31,Players!B:B,Players!A:A)</f>
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E31" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F31">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B32">
         <f>_xlfn.XLOOKUP(C32,Players!B:B,Players!A:A)</f>
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D32" t="s">
         <v>99</v>
       </c>
       <c r="E32" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>95</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B33">
         <f>_xlfn.XLOOKUP(C33,Players!B:B,Players!A:A)</f>
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="D33" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
       </c>
       <c r="F33">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B34">
         <f>_xlfn.XLOOKUP(C34,Players!B:B,Players!A:A)</f>
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E34" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B35">
         <f>_xlfn.XLOOKUP(C35,Players!B:B,Players!A:A)</f>
-        <v>5</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>43</v>
+        <v>26</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>19</v>
       </c>
       <c r="D35" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E35" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F35">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B36">
         <f>_xlfn.XLOOKUP(C36,Players!B:B,Players!A:A)</f>
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="D36" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E36" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F36">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B37">
         <f>_xlfn.XLOOKUP(C37,Players!B:B,Players!A:A)</f>
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D37" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E37" s="1">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F37">
-        <v>108</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B38">
         <f>_xlfn.XLOOKUP(C38,Players!B:B,Players!A:A)</f>
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D38" t="s">
         <v>99</v>
       </c>
       <c r="E38" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F38">
-        <v>12</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B39">
         <f>_xlfn.XLOOKUP(C39,Players!B:B,Players!A:A)</f>
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E39" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B40">
         <f>_xlfn.XLOOKUP(C40,Players!B:B,Players!A:A)</f>
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D40" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E40" s="1">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F40">
-        <v>12</v>
+        <v>288</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B41">
         <f>_xlfn.XLOOKUP(C41,Players!B:B,Players!A:A)</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="D41" t="s">
         <v>99</v>
       </c>
       <c r="E41" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F41">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B42">
         <f>_xlfn.XLOOKUP(C42,Players!B:B,Players!A:A)</f>
+        <v>10</v>
+      </c>
+      <c r="C42" s="17" t="s">
         <v>28</v>
-      </c>
-      <c r="C42" s="17" t="s">
-        <v>35</v>
       </c>
       <c r="D42" t="s">
         <v>99</v>
       </c>
       <c r="E42" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F42">
         <v>36</v>
@@ -10939,14 +10936,14 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B43">
         <f>_xlfn.XLOOKUP(C43,Players!B:B,Players!A:A)</f>
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D43" t="s">
         <v>99</v>
@@ -10955,103 +10952,103 @@
         <v>3</v>
       </c>
       <c r="F43">
-        <v>36</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B44">
         <f>_xlfn.XLOOKUP(C44,Players!B:B,Players!A:A)</f>
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D44" t="s">
         <v>99</v>
       </c>
       <c r="E44" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F44">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B45">
         <f>_xlfn.XLOOKUP(C45,Players!B:B,Players!A:A)</f>
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D45" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E45" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F45">
-        <v>28</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B46">
         <f>_xlfn.XLOOKUP(C46,Players!B:B,Players!A:A)</f>
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D46" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E46" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F46">
-        <v>28</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B47">
         <f>_xlfn.XLOOKUP(C47,Players!B:B,Players!A:A)</f>
         <v>15</v>
       </c>
-      <c r="C47" s="17" t="s">
+      <c r="C47" s="33" t="s">
         <v>11</v>
       </c>
       <c r="D47" t="s">
         <v>98</v>
       </c>
       <c r="E47" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F47">
-        <v>42</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B48">
         <f>_xlfn.XLOOKUP(C48,Players!B:B,Players!A:A)</f>
-        <v>8</v>
-      </c>
-      <c r="C48" s="17" t="s">
-        <v>44</v>
+        <v>13</v>
+      </c>
+      <c r="C48" s="33" t="s">
+        <v>14</v>
       </c>
       <c r="D48" t="s">
         <v>98</v>
@@ -11065,14 +11062,14 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B49">
         <f>_xlfn.XLOOKUP(C49,Players!B:B,Players!A:A)</f>
-        <v>27</v>
-      </c>
-      <c r="C49" s="17" t="s">
-        <v>51</v>
+        <v>20</v>
+      </c>
+      <c r="C49" s="33" t="s">
+        <v>18</v>
       </c>
       <c r="D49" t="s">
         <v>98</v>
@@ -11086,98 +11083,98 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B50">
         <f>_xlfn.XLOOKUP(C50,Players!B:B,Players!A:A)</f>
-        <v>6</v>
-      </c>
-      <c r="C50" s="17" t="s">
-        <v>22</v>
+        <v>44</v>
+      </c>
+      <c r="C50" s="33" t="s">
+        <v>23</v>
       </c>
       <c r="D50" t="s">
         <v>98</v>
       </c>
       <c r="E50" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F50">
-        <v>70</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B51">
         <f>_xlfn.XLOOKUP(C51,Players!B:B,Players!A:A)</f>
-        <v>35</v>
-      </c>
-      <c r="C51" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="C51" s="33" t="s">
+        <v>26</v>
       </c>
       <c r="D51" t="s">
         <v>99</v>
       </c>
       <c r="E51" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F51">
-        <v>14</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B52">
         <f>_xlfn.XLOOKUP(C52,Players!B:B,Players!A:A)</f>
-        <v>2</v>
-      </c>
-      <c r="C52" s="17" t="s">
-        <v>41</v>
+        <v>10</v>
+      </c>
+      <c r="C52" s="33" t="s">
+        <v>28</v>
       </c>
       <c r="D52" t="s">
         <v>99</v>
       </c>
       <c r="E52" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F52">
-        <v>14</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B53">
         <f>_xlfn.XLOOKUP(C53,Players!B:B,Players!A:A)</f>
-        <v>19</v>
-      </c>
-      <c r="C53" s="17" t="s">
-        <v>34</v>
+        <v>25</v>
+      </c>
+      <c r="C53" s="33" t="s">
+        <v>38</v>
       </c>
       <c r="D53" t="s">
         <v>99</v>
       </c>
       <c r="E53" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F53">
-        <v>14</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B54">
         <f>_xlfn.XLOOKUP(C54,Players!B:B,Players!A:A)</f>
-        <v>26</v>
-      </c>
-      <c r="C54" s="17" t="s">
-        <v>19</v>
+        <v>43</v>
+      </c>
+      <c r="C54" s="33" t="s">
+        <v>29</v>
       </c>
       <c r="D54" t="s">
         <v>99</v>
@@ -11186,19 +11183,19 @@
         <v>2</v>
       </c>
       <c r="F54">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B55">
         <f>_xlfn.XLOOKUP(C55,Players!B:B,Players!A:A)</f>
-        <v>39</v>
-      </c>
-      <c r="C55" s="17" t="s">
-        <v>56</v>
+        <v>28</v>
+      </c>
+      <c r="C55" s="33" t="s">
+        <v>35</v>
       </c>
       <c r="D55" t="s">
         <v>99</v>
@@ -11207,52 +11204,53 @@
         <v>2</v>
       </c>
       <c r="F55">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B56">
         <f>_xlfn.XLOOKUP(C56,Players!B:B,Players!A:A)</f>
-        <v>24</v>
-      </c>
-      <c r="C56" s="17" t="s">
-        <v>31</v>
+        <v>1</v>
+      </c>
+      <c r="C56" s="33" t="s">
+        <v>30</v>
       </c>
       <c r="D56" t="s">
         <v>99</v>
       </c>
       <c r="E56" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F56">
-        <v>56</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B57">
         <f>_xlfn.XLOOKUP(C57,Players!B:B,Players!A:A)</f>
-        <v>28</v>
-      </c>
-      <c r="C57" s="17" t="s">
-        <v>35</v>
+        <v>9</v>
+      </c>
+      <c r="C57" s="33" t="s">
+        <v>37</v>
       </c>
       <c r="D57" t="s">
         <v>99</v>
       </c>
       <c r="E57" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F57">
-        <v>98</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F57" xr:uid="{4723CA7E-3717-814A-BF66-62A12120D4EC}"/>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MIGC_Season_Dashboard.xlsx
+++ b/MIGC_Season_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevinvargas/Desktop/migc-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80C3186-3B4A-B84A-9520-3A7908B8A5FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A34BACC-06D7-764E-81A9-F020DB27E058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16780" yWindow="600" windowWidth="16820" windowHeight="19160" activeTab="3" xr2:uid="{BBF77493-EF1A-3942-9440-E7AC2E03DB26}"/>
   </bookViews>
@@ -592,7 +592,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -676,7 +676,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11026,7 +11025,7 @@
         <f>_xlfn.XLOOKUP(C47,Players!B:B,Players!A:A)</f>
         <v>15</v>
       </c>
-      <c r="C47" s="33" t="s">
+      <c r="C47" s="17" t="s">
         <v>11</v>
       </c>
       <c r="D47" t="s">
@@ -11047,7 +11046,7 @@
         <f>_xlfn.XLOOKUP(C48,Players!B:B,Players!A:A)</f>
         <v>13</v>
       </c>
-      <c r="C48" s="33" t="s">
+      <c r="C48" s="17" t="s">
         <v>14</v>
       </c>
       <c r="D48" t="s">
@@ -11068,7 +11067,7 @@
         <f>_xlfn.XLOOKUP(C49,Players!B:B,Players!A:A)</f>
         <v>20</v>
       </c>
-      <c r="C49" s="33" t="s">
+      <c r="C49" s="17" t="s">
         <v>18</v>
       </c>
       <c r="D49" t="s">
@@ -11089,7 +11088,7 @@
         <f>_xlfn.XLOOKUP(C50,Players!B:B,Players!A:A)</f>
         <v>44</v>
       </c>
-      <c r="C50" s="33" t="s">
+      <c r="C50" s="17" t="s">
         <v>23</v>
       </c>
       <c r="D50" t="s">
@@ -11110,7 +11109,7 @@
         <f>_xlfn.XLOOKUP(C51,Players!B:B,Players!A:A)</f>
         <v>14</v>
       </c>
-      <c r="C51" s="33" t="s">
+      <c r="C51" s="17" t="s">
         <v>26</v>
       </c>
       <c r="D51" t="s">
@@ -11131,7 +11130,7 @@
         <f>_xlfn.XLOOKUP(C52,Players!B:B,Players!A:A)</f>
         <v>10</v>
       </c>
-      <c r="C52" s="33" t="s">
+      <c r="C52" s="17" t="s">
         <v>28</v>
       </c>
       <c r="D52" t="s">
@@ -11152,7 +11151,7 @@
         <f>_xlfn.XLOOKUP(C53,Players!B:B,Players!A:A)</f>
         <v>25</v>
       </c>
-      <c r="C53" s="33" t="s">
+      <c r="C53" s="17" t="s">
         <v>38</v>
       </c>
       <c r="D53" t="s">
@@ -11173,7 +11172,7 @@
         <f>_xlfn.XLOOKUP(C54,Players!B:B,Players!A:A)</f>
         <v>43</v>
       </c>
-      <c r="C54" s="33" t="s">
+      <c r="C54" s="17" t="s">
         <v>29</v>
       </c>
       <c r="D54" t="s">
@@ -11194,7 +11193,7 @@
         <f>_xlfn.XLOOKUP(C55,Players!B:B,Players!A:A)</f>
         <v>28</v>
       </c>
-      <c r="C55" s="33" t="s">
+      <c r="C55" s="17" t="s">
         <v>35</v>
       </c>
       <c r="D55" t="s">
@@ -11215,7 +11214,7 @@
         <f>_xlfn.XLOOKUP(C56,Players!B:B,Players!A:A)</f>
         <v>1</v>
       </c>
-      <c r="C56" s="33" t="s">
+      <c r="C56" s="17" t="s">
         <v>30</v>
       </c>
       <c r="D56" t="s">
@@ -11236,7 +11235,7 @@
         <f>_xlfn.XLOOKUP(C57,Players!B:B,Players!A:A)</f>
         <v>9</v>
       </c>
-      <c r="C57" s="33" t="s">
+      <c r="C57" s="17" t="s">
         <v>37</v>
       </c>
       <c r="D57" t="s">

--- a/MIGC_Season_Dashboard.xlsx
+++ b/MIGC_Season_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevinvargas/Desktop/migc-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A34BACC-06D7-764E-81A9-F020DB27E058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E95F9D5F-EE64-CB44-B030-DC8AC89A6634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16780" yWindow="600" windowWidth="16820" windowHeight="19160" activeTab="3" xr2:uid="{BBF77493-EF1A-3942-9440-E7AC2E03DB26}"/>
   </bookViews>

--- a/MIGC_Season_Dashboard.xlsx
+++ b/MIGC_Season_Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevinvargas/Desktop/migc-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E95F9D5F-EE64-CB44-B030-DC8AC89A6634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72413F23-772B-6840-84AE-891B0645E7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16780" yWindow="600" windowWidth="16820" windowHeight="19160" activeTab="3" xr2:uid="{BBF77493-EF1A-3942-9440-E7AC2E03DB26}"/>
+    <workbookView xWindow="22760" yWindow="600" windowWidth="28440" windowHeight="26960" activeTab="3" xr2:uid="{BBF77493-EF1A-3942-9440-E7AC2E03DB26}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="2" r:id="rId1"/>

--- a/MIGC_Season_Dashboard.xlsx
+++ b/MIGC_Season_Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevinvargas/Desktop/migc-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72413F23-772B-6840-84AE-891B0645E7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6ACB93-07C7-5D4D-B2A0-652B10F9BF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22760" yWindow="600" windowWidth="28440" windowHeight="26960" activeTab="3" xr2:uid="{BBF77493-EF1A-3942-9440-E7AC2E03DB26}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="19160" xr2:uid="{BBF77493-EF1A-3942-9440-E7AC2E03DB26}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="2" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="126">
   <si>
     <t>Tournament ID</t>
   </si>
@@ -346,9 +346,6 @@
   </si>
   <si>
     <t>Flight B - Skins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Player, Flight, Handicap, Gross Score, Net Score, Front 9 Grose Score, Back 9 Gross Score and total putts. </t>
   </si>
   <si>
     <t>Devin Lerner</t>
@@ -1766,7 +1763,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>80</v>
@@ -1780,7 +1777,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>80</v>
@@ -1799,6 +1796,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -1827,7 +1825,7 @@
         <v>65</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -1844,7 +1842,7 @@
         <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -1861,7 +1859,7 @@
         <v>70</v>
       </c>
       <c r="E3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -1878,7 +1876,7 @@
         <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -1895,7 +1893,7 @@
         <v>75</v>
       </c>
       <c r="E5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -1912,126 +1910,126 @@
         <v>76</v>
       </c>
       <c r="E6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" t="s">
         <v>103</v>
-      </c>
-      <c r="B7" t="s">
-        <v>104</v>
       </c>
       <c r="C7" s="32">
         <v>46201</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" t="s">
         <v>106</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="C8" s="32" t="s">
-        <v>108</v>
-      </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s">
         <v>67</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
         <v>67</v>
       </c>
       <c r="E9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="C10" s="32" t="s">
-        <v>117</v>
-      </c>
       <c r="D10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C12" s="32">
         <v>46320</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C13" s="32">
         <v>46341</v>
       </c>
       <c r="D13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2041,15 +2039,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3B800D8-26AB-5145-974D-2E86BCED24A0}">
-  <dimension ref="A1:N152"/>
+  <dimension ref="A1:M152"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
     <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="10.83203125" style="1"/>
+    <col min="4" max="4" width="10.83203125" style="1"/>
+    <col min="5" max="6" width="10.83203125" style="1" customWidth="1"/>
+    <col min="7" max="10" width="10.83203125" style="1"/>
     <col min="12" max="12" width="15.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2081,13 +2082,13 @@
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -2117,13 +2118,13 @@
         <v>43</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>66</v>
       </c>
@@ -2153,13 +2154,13 @@
         <v>43</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>66</v>
       </c>
@@ -2189,16 +2190,13 @@
         <v>46</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K4" t="s">
-        <v>125</v>
-      </c>
-      <c r="N4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>66</v>
       </c>
@@ -2228,13 +2226,13 @@
         <v>47</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>66</v>
       </c>
@@ -2264,13 +2262,13 @@
         <v>49</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>66</v>
       </c>
@@ -2300,13 +2298,13 @@
         <v>45</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K7" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -2336,13 +2334,13 @@
         <v>49</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K8" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>66</v>
       </c>
@@ -2372,13 +2370,13 @@
         <v>52</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K9" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>66</v>
       </c>
@@ -2408,13 +2406,13 @@
         <v>51</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K10" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>66</v>
       </c>
@@ -2444,13 +2442,13 @@
         <v>48</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K11" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -2480,13 +2478,13 @@
         <v>52</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K12" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -2516,13 +2514,13 @@
         <v>48</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K13" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>66</v>
       </c>
@@ -2552,13 +2550,13 @@
         <v>50</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K14" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -2567,7 +2565,7 @@
         <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>12</v>
@@ -2588,13 +2586,13 @@
         <v>51</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K15" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>66</v>
       </c>
@@ -2624,10 +2622,10 @@
         <v>44</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
@@ -2660,10 +2658,10 @@
         <v>56</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
@@ -2696,10 +2694,10 @@
         <v>56</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
@@ -2732,10 +2730,10 @@
         <v>47</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
@@ -2768,10 +2766,10 @@
         <v>44</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
@@ -2804,10 +2802,10 @@
         <v>49</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
@@ -2840,10 +2838,10 @@
         <v>55</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K22" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
@@ -2876,10 +2874,10 @@
         <v>53</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
@@ -2912,10 +2910,10 @@
         <v>51</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
@@ -2948,10 +2946,10 @@
         <v>55</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
@@ -2984,10 +2982,10 @@
         <v>58</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
@@ -3020,10 +3018,10 @@
         <v>58</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
@@ -3056,10 +3054,10 @@
         <v>56</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
@@ -3092,10 +3090,10 @@
         <v>59</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
@@ -3128,10 +3126,10 @@
         <v>55</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
@@ -3143,7 +3141,7 @@
         <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>27</v>
@@ -3164,10 +3162,10 @@
         <v>56</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
@@ -3200,10 +3198,10 @@
         <v>58</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
@@ -3236,10 +3234,10 @@
         <v>54</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
@@ -3272,10 +3270,10 @@
         <v>55</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K34" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
@@ -3308,10 +3306,10 @@
         <v>55</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K35" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
@@ -3344,10 +3342,10 @@
         <v>76</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
@@ -3380,10 +3378,10 @@
         <v>59</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
@@ -3416,10 +3414,10 @@
         <v>44</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K38" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L38" s="1">
         <v>12</v>
@@ -3455,10 +3453,10 @@
         <v>51</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K39" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L39" s="1"/>
     </row>
@@ -3492,10 +3490,10 @@
         <v>46</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K40" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L40" s="1"/>
     </row>
@@ -3529,10 +3527,10 @@
         <v>50</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K41" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L41" s="1"/>
     </row>
@@ -3566,10 +3564,10 @@
         <v>44</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L42" s="1">
         <v>7.5</v>
@@ -3605,10 +3603,10 @@
         <v>48</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K43" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L43" s="1"/>
     </row>
@@ -3642,10 +3640,10 @@
         <v>52</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K44" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L44" s="1"/>
     </row>
@@ -3679,10 +3677,10 @@
         <v>47</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K45" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L45" s="1"/>
     </row>
@@ -3716,10 +3714,10 @@
         <v>45</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K46" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L46" s="1">
         <v>4</v>
@@ -3755,10 +3753,10 @@
         <v>55</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K47" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L47" s="1"/>
     </row>
@@ -3792,12 +3790,14 @@
         <v>57</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K48" t="s">
-        <v>122</v>
-      </c>
-      <c r="L48" s="1"/>
+        <v>121</v>
+      </c>
+      <c r="L48" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
@@ -3829,10 +3829,10 @@
         <v>56</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K49" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L49" s="1"/>
     </row>
@@ -3866,10 +3866,10 @@
         <v>56</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K50" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L50" s="1"/>
     </row>
@@ -3903,14 +3903,12 @@
         <v>44</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K51" t="s">
-        <v>123</v>
-      </c>
-      <c r="L51" s="1">
-        <v>11</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="L51" s="1"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
@@ -3942,10 +3940,10 @@
         <v>48</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K52" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L52" s="1">
         <v>10</v>
@@ -3981,10 +3979,10 @@
         <v>56</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K53" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L53" s="1"/>
     </row>
@@ -4018,10 +4016,10 @@
         <v>48</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K54" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L54" s="1">
         <v>7.5</v>
@@ -4057,10 +4055,10 @@
         <v>50</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K55" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L55" s="1"/>
     </row>
@@ -4094,10 +4092,10 @@
         <v>48</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K56" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L56" s="1">
         <v>5.5</v>
@@ -4133,10 +4131,10 @@
         <v>52</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K57" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L57" s="1"/>
     </row>
@@ -4170,10 +4168,10 @@
         <v>58</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K58" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L58" s="1"/>
     </row>
@@ -4207,10 +4205,10 @@
         <v>58</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K59" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L59" s="1"/>
     </row>
@@ -4244,10 +4242,10 @@
         <v>60</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K60" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L60" s="1">
         <v>2</v>
@@ -4283,10 +4281,10 @@
         <v>75</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K61" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L61" s="1"/>
     </row>
@@ -4320,7 +4318,7 @@
         <v>46</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L62" s="1"/>
       <c r="M62" s="1"/>
@@ -4355,10 +4353,10 @@
         <v>47</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K63" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L63" s="1">
         <v>13.5</v>
@@ -4395,7 +4393,7 @@
         <v>47</v>
       </c>
       <c r="J64" s="25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L64" s="25"/>
       <c r="M64" s="1"/>
@@ -4430,10 +4428,10 @@
         <v>46</v>
       </c>
       <c r="J65" s="25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K65" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L65" s="25">
         <v>11</v>
@@ -4470,10 +4468,10 @@
         <v>47</v>
       </c>
       <c r="J66" s="24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K66" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L66" s="24">
         <v>8.5</v>
@@ -4510,7 +4508,7 @@
         <v>44</v>
       </c>
       <c r="J67" s="22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L67" s="24"/>
       <c r="M67" s="1"/>
@@ -4545,7 +4543,7 @@
         <v>50</v>
       </c>
       <c r="J68" s="24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L68" s="24"/>
       <c r="M68" s="1"/>
@@ -4580,7 +4578,7 @@
         <v>47</v>
       </c>
       <c r="J69" s="22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L69" s="24"/>
       <c r="M69" s="1"/>
@@ -4615,7 +4613,7 @@
         <v>49</v>
       </c>
       <c r="J70" s="24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L70" s="24"/>
       <c r="M70" s="1"/>
@@ -4650,7 +4648,7 @@
         <v>45</v>
       </c>
       <c r="J71" s="22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L71" s="24"/>
       <c r="M71" s="1"/>
@@ -4685,7 +4683,7 @@
         <v>45</v>
       </c>
       <c r="J72" s="24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L72" s="24"/>
       <c r="M72" s="1"/>
@@ -4720,10 +4718,10 @@
         <v>47</v>
       </c>
       <c r="J73" s="22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K73" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L73" s="24">
         <v>3</v>
@@ -4760,10 +4758,10 @@
         <v>54</v>
       </c>
       <c r="J74" s="24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K74" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L74" s="24">
         <v>2</v>
@@ -4800,7 +4798,7 @@
         <v>60</v>
       </c>
       <c r="J75" s="22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L75" s="24"/>
     </row>
@@ -4834,7 +4832,7 @@
         <v>42</v>
       </c>
       <c r="J76" s="25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L76" s="24"/>
     </row>
@@ -4868,7 +4866,7 @@
         <v>46</v>
       </c>
       <c r="J77" s="22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L77" s="24"/>
     </row>
@@ -4902,10 +4900,10 @@
         <v>47</v>
       </c>
       <c r="J78" s="24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K78" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L78" s="24">
         <v>11.5</v>
@@ -4941,7 +4939,7 @@
         <v>50</v>
       </c>
       <c r="J79" s="22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L79" s="24"/>
     </row>
@@ -4975,10 +4973,10 @@
         <v>47</v>
       </c>
       <c r="J80" s="24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K80" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L80" s="24">
         <v>10</v>
@@ -5014,7 +5012,7 @@
         <v>48</v>
       </c>
       <c r="J81" s="22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L81" s="24"/>
     </row>
@@ -5048,7 +5046,7 @@
         <v>50</v>
       </c>
       <c r="J82" s="24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L82" s="24"/>
     </row>
@@ -5082,7 +5080,7 @@
         <v>53</v>
       </c>
       <c r="J83" s="22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L83" s="24"/>
     </row>
@@ -5116,10 +5114,10 @@
         <v>53</v>
       </c>
       <c r="J84" s="24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K84" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L84" s="24">
         <v>5</v>
@@ -5155,7 +5153,7 @@
         <v>55</v>
       </c>
       <c r="J85" s="22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L85" s="24"/>
     </row>
@@ -5189,7 +5187,7 @@
         <v>48</v>
       </c>
       <c r="J86" s="24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
@@ -5222,7 +5220,7 @@
         <v>59</v>
       </c>
       <c r="J87" s="22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
@@ -5255,7 +5253,7 @@
         <v>57</v>
       </c>
       <c r="J88" s="24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
@@ -5288,7 +5286,7 @@
         <v>61</v>
       </c>
       <c r="J89" s="22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
@@ -5324,7 +5322,7 @@
         <v>32</v>
       </c>
       <c r="K90" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L90" s="1">
         <v>18</v>
@@ -5431,7 +5429,7 @@
         <v>35</v>
       </c>
       <c r="K93" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L93" s="1">
         <v>15</v>
@@ -5572,7 +5570,7 @@
         <v>32</v>
       </c>
       <c r="K97" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L97" s="1">
         <v>11</v>
@@ -5645,7 +5643,7 @@
         <v>35</v>
       </c>
       <c r="K99" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L99" s="1">
         <v>9</v>
@@ -5684,7 +5682,7 @@
         <v>33</v>
       </c>
       <c r="K100" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L100" s="1">
         <v>7.5</v>
@@ -5995,7 +5993,7 @@
         <v>37</v>
       </c>
       <c r="K109" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L109" s="1">
         <v>16.5</v>
@@ -6271,7 +6269,12 @@
       <c r="J117" s="1">
         <v>38</v>
       </c>
-      <c r="L117" s="1"/>
+      <c r="K117" t="s">
+        <v>122</v>
+      </c>
+      <c r="L117" s="1">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
@@ -6305,12 +6308,6 @@
       <c r="J118" s="1">
         <v>37</v>
       </c>
-      <c r="K118" t="s">
-        <v>123</v>
-      </c>
-      <c r="L118" s="1">
-        <v>7.5</v>
-      </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
@@ -6481,7 +6478,7 @@
         <v>39</v>
       </c>
       <c r="K123" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L123" s="1">
         <v>2</v>
@@ -6758,7 +6755,7 @@
         <v>32</v>
       </c>
       <c r="K131" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L131" s="1">
         <v>8</v>
@@ -6797,7 +6794,7 @@
         <v>30</v>
       </c>
       <c r="K132" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L132" s="1">
         <v>6.5</v>
@@ -6870,7 +6867,7 @@
         <v>34</v>
       </c>
       <c r="K134" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L134" s="1">
         <v>5</v>
@@ -7011,7 +7008,7 @@
         <v>35</v>
       </c>
       <c r="K138" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L138" s="1">
         <v>1</v>
@@ -7152,7 +7149,7 @@
         <v>31</v>
       </c>
       <c r="K142" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L142" s="1">
         <v>8</v>
@@ -7225,7 +7222,7 @@
         <v>35</v>
       </c>
       <c r="K144" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L144" s="1">
         <v>8</v>
@@ -7264,7 +7261,7 @@
         <v>36</v>
       </c>
       <c r="K145" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L145" s="1">
         <v>6</v>
@@ -7337,7 +7334,7 @@
         <v>39</v>
       </c>
       <c r="K147" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L147" s="1">
         <v>4</v>
@@ -7452,9 +7449,16 @@
       <c r="L152" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L150" xr:uid="{F3B800D8-26AB-5145-974D-2E86BCED24A0}"/>
+  <autoFilter ref="A1:L150" xr:uid="{F3B800D8-26AB-5145-974D-2E86BCED24A0}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L150">
+      <sortCondition ref="A2:A150"/>
+      <sortCondition ref="D2:D150"/>
+      <sortCondition ref="G2:G150"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>

--- a/MIGC_Season_Dashboard.xlsx
+++ b/MIGC_Season_Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevinvargas/Desktop/migc-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6ACB93-07C7-5D4D-B2A0-652B10F9BF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE0CB3B-CD72-CA4C-9777-559922AB7168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="19160" xr2:uid="{BBF77493-EF1A-3942-9440-E7AC2E03DB26}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="19160" activeTab="2" xr2:uid="{BBF77493-EF1A-3942-9440-E7AC2E03DB26}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="2" r:id="rId1"/>

--- a/MIGC_Season_Dashboard.xlsx
+++ b/MIGC_Season_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevinvargas/Desktop/migc-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE0CB3B-CD72-CA4C-9777-559922AB7168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E29866A0-6BFB-A44E-BCD3-0A007ABD2592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="19160" activeTab="2" xr2:uid="{BBF77493-EF1A-3942-9440-E7AC2E03DB26}"/>
   </bookViews>
@@ -18,6 +18,7 @@
     <sheet name="Tournament_Results" sheetId="1" r:id="rId3"/>
     <sheet name="Tournament_Acheivements" sheetId="4" r:id="rId4"/>
     <sheet name="Tournament_Skins" sheetId="5" r:id="rId5"/>
+    <sheet name="Summary" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Players!$A$1:$D$45</definedName>
@@ -26,6 +27,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Tournament_Skins!$A$1:$F$57</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="5" r:id="rId7"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -46,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="129">
   <si>
     <t>Tournament ID</t>
   </si>
@@ -425,6 +429,15 @@
   <si>
     <t>TGL Points</t>
   </si>
+  <si>
+    <t>Sum of TGL Points</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
 </sst>
 </file>
 
@@ -589,7 +602,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -673,6 +686,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -800,6 +815,2320 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Kevin Vargas" refreshedDate="46183.90054328704" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="149" xr:uid="{F7B487D3-5268-2549-8478-0CB769A45238}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:L150" sheet="Tournament_Results"/>
+  </cacheSource>
+  <cacheFields count="12">
+    <cacheField name="Tournament ID" numFmtId="0">
+      <sharedItems count="5">
+        <s v="2026_01"/>
+        <s v="2026_02"/>
+        <s v="2026_03"/>
+        <s v="2026_04"/>
+        <s v="2026_05"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Player ID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="46"/>
+    </cacheField>
+    <cacheField name="Player" numFmtId="0">
+      <sharedItems count="46">
+        <s v="Taylor Yates"/>
+        <s v="Tai Ho"/>
+        <s v="Darrick Sogabe"/>
+        <s v="Tam Tran"/>
+        <s v="Colin Chang"/>
+        <s v="Tom Shea"/>
+        <s v="Jorge Rayo"/>
+        <s v="JP Hill"/>
+        <s v="Carlos Bouloy"/>
+        <s v="John Nothdurft"/>
+        <s v="Nick Harris"/>
+        <s v="Kevin Vargas"/>
+        <s v="Chris Chang"/>
+        <s v="Devin Lerner"/>
+        <s v="Andy Pendleton"/>
+        <s v="Spencer Higgins"/>
+        <s v="Paul Toledo"/>
+        <s v="Max O'Brien"/>
+        <s v="Mikel Hodges"/>
+        <s v="Danny Lopez"/>
+        <s v="Paul Hsieh"/>
+        <s v="Colin Harrison"/>
+        <s v="Art Hernandez"/>
+        <s v="Kevin Taylor"/>
+        <s v="Adrianna Moore"/>
+        <s v="Ken Sogabe"/>
+        <s v="Steve Chiang"/>
+        <s v="Mike Paguyo"/>
+        <s v="David Wu"/>
+        <s v="Tyler Nichols"/>
+        <s v="Charles Tran"/>
+        <s v="Danny Marin"/>
+        <s v="Will Vuong"/>
+        <s v="Marcel Mendoza"/>
+        <s v="Devan French"/>
+        <s v="Mark Horgan"/>
+        <s v="Brock Hansen"/>
+        <s v="Bryan Cappelli"/>
+        <s v="Juan Ramirez"/>
+        <s v="Mike Pena"/>
+        <s v="Lucas Bouloy"/>
+        <s v="Mat Vigil"/>
+        <s v="Sarith Kim"/>
+        <s v="Jeff Carey"/>
+        <s v="Med Baheta"/>
+        <s v="Jason Payton"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Flight" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Handicap" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="5" maxValue="36"/>
+    </cacheField>
+    <cacheField name="Gross" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="76" maxValue="140"/>
+    </cacheField>
+    <cacheField name="Net" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="66" maxValue="105"/>
+    </cacheField>
+    <cacheField name="Front 9" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="36" maxValue="73"/>
+    </cacheField>
+    <cacheField name="Back 9" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="38" maxValue="76"/>
+    </cacheField>
+    <cacheField name="Putts" numFmtId="0">
+      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="26" maxValue="42"/>
+    </cacheField>
+    <cacheField name="TGL Player" numFmtId="0">
+      <sharedItems containsBlank="1" count="4">
+        <s v="N/A"/>
+        <s v="Yes"/>
+        <s v="No"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="TGL Points" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="1" maxValue="18"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="149">
+  <r>
+    <x v="0"/>
+    <n v="36"/>
+    <x v="0"/>
+    <s v="A"/>
+    <n v="9"/>
+    <n v="79"/>
+    <n v="70"/>
+    <n v="36"/>
+    <n v="43"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="34"/>
+    <x v="1"/>
+    <s v="A"/>
+    <n v="15"/>
+    <n v="85"/>
+    <n v="70"/>
+    <n v="42"/>
+    <n v="43"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="12"/>
+    <x v="2"/>
+    <s v="A"/>
+    <n v="19"/>
+    <n v="92"/>
+    <n v="73"/>
+    <n v="46"/>
+    <n v="46"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="35"/>
+    <x v="3"/>
+    <s v="A"/>
+    <n v="20"/>
+    <n v="93"/>
+    <n v="73"/>
+    <n v="46"/>
+    <n v="47"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="8"/>
+    <x v="4"/>
+    <s v="A"/>
+    <n v="18"/>
+    <n v="94"/>
+    <n v="76"/>
+    <n v="45"/>
+    <n v="49"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="37"/>
+    <x v="5"/>
+    <s v="A"/>
+    <n v="5"/>
+    <n v="84"/>
+    <n v="79"/>
+    <n v="39"/>
+    <n v="45"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="16"/>
+    <x v="6"/>
+    <s v="A"/>
+    <n v="16"/>
+    <n v="97"/>
+    <n v="81"/>
+    <n v="48"/>
+    <n v="49"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="17"/>
+    <x v="7"/>
+    <s v="A"/>
+    <n v="13"/>
+    <n v="96"/>
+    <n v="83"/>
+    <n v="44"/>
+    <n v="52"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="6"/>
+    <x v="8"/>
+    <s v="A"/>
+    <n v="19"/>
+    <n v="102"/>
+    <n v="83"/>
+    <n v="51"/>
+    <n v="51"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="9"/>
+    <s v="A"/>
+    <n v="10"/>
+    <n v="95"/>
+    <n v="85"/>
+    <n v="47"/>
+    <n v="48"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="27"/>
+    <x v="10"/>
+    <s v="A"/>
+    <n v="17"/>
+    <n v="103"/>
+    <n v="86"/>
+    <n v="51"/>
+    <n v="52"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="20"/>
+    <x v="11"/>
+    <s v="A"/>
+    <n v="8"/>
+    <n v="95"/>
+    <n v="87"/>
+    <n v="47"/>
+    <n v="48"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="7"/>
+    <x v="12"/>
+    <s v="A"/>
+    <n v="13"/>
+    <n v="100"/>
+    <n v="87"/>
+    <n v="50"/>
+    <n v="50"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="45"/>
+    <x v="13"/>
+    <s v="A"/>
+    <n v="17"/>
+    <n v="104"/>
+    <n v="87"/>
+    <n v="53"/>
+    <n v="51"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="3"/>
+    <x v="14"/>
+    <s v="A"/>
+    <n v="7"/>
+    <n v="95"/>
+    <n v="88"/>
+    <n v="51"/>
+    <n v="44"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="32"/>
+    <x v="15"/>
+    <s v="A"/>
+    <n v="10"/>
+    <n v="103"/>
+    <n v="93"/>
+    <n v="47"/>
+    <n v="56"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="29"/>
+    <x v="16"/>
+    <s v="A"/>
+    <n v="11"/>
+    <n v="105"/>
+    <n v="94"/>
+    <n v="49"/>
+    <n v="56"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="23"/>
+    <x v="17"/>
+    <s v="B"/>
+    <n v="25"/>
+    <n v="97"/>
+    <n v="72"/>
+    <n v="50"/>
+    <n v="47"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="26"/>
+    <x v="18"/>
+    <s v="B"/>
+    <n v="21"/>
+    <n v="95"/>
+    <n v="74"/>
+    <n v="51"/>
+    <n v="44"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="19"/>
+    <s v="B"/>
+    <n v="21"/>
+    <n v="96"/>
+    <n v="75"/>
+    <n v="47"/>
+    <n v="49"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="28"/>
+    <x v="20"/>
+    <s v="B"/>
+    <n v="34"/>
+    <n v="109"/>
+    <n v="75"/>
+    <n v="54"/>
+    <n v="55"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="9"/>
+    <x v="21"/>
+    <s v="B"/>
+    <n v="20"/>
+    <n v="96"/>
+    <n v="76"/>
+    <n v="43"/>
+    <n v="53"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="22"/>
+    <s v="B"/>
+    <n v="21"/>
+    <n v="98"/>
+    <n v="77"/>
+    <n v="47"/>
+    <n v="51"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="19"/>
+    <x v="23"/>
+    <s v="B"/>
+    <n v="24"/>
+    <n v="102"/>
+    <n v="78"/>
+    <n v="47"/>
+    <n v="55"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="2"/>
+    <x v="24"/>
+    <s v="B"/>
+    <n v="36"/>
+    <n v="116"/>
+    <n v="80"/>
+    <n v="58"/>
+    <n v="58"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="30"/>
+    <x v="25"/>
+    <s v="B"/>
+    <n v="36"/>
+    <n v="117"/>
+    <n v="81"/>
+    <n v="59"/>
+    <n v="58"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="33"/>
+    <x v="26"/>
+    <s v="B"/>
+    <n v="22"/>
+    <n v="104"/>
+    <n v="82"/>
+    <n v="48"/>
+    <n v="56"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="24"/>
+    <x v="27"/>
+    <s v="B"/>
+    <n v="25"/>
+    <n v="108"/>
+    <n v="83"/>
+    <n v="49"/>
+    <n v="59"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="13"/>
+    <x v="28"/>
+    <s v="B"/>
+    <n v="21"/>
+    <n v="106"/>
+    <n v="85"/>
+    <n v="51"/>
+    <n v="55"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="46"/>
+    <x v="29"/>
+    <s v="B"/>
+    <n v="21"/>
+    <n v="108"/>
+    <n v="87"/>
+    <n v="52"/>
+    <n v="56"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="39"/>
+    <x v="30"/>
+    <s v="B"/>
+    <n v="30"/>
+    <n v="117"/>
+    <n v="87"/>
+    <n v="59"/>
+    <n v="58"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="11"/>
+    <x v="31"/>
+    <s v="B"/>
+    <n v="31"/>
+    <n v="118"/>
+    <n v="87"/>
+    <n v="64"/>
+    <n v="54"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="38"/>
+    <x v="32"/>
+    <s v="B"/>
+    <n v="20"/>
+    <n v="108"/>
+    <n v="88"/>
+    <n v="53"/>
+    <n v="55"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="21"/>
+    <x v="33"/>
+    <s v="B"/>
+    <n v="20"/>
+    <n v="113"/>
+    <n v="93"/>
+    <n v="58"/>
+    <n v="55"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="14"/>
+    <x v="34"/>
+    <s v="B"/>
+    <n v="36"/>
+    <n v="129"/>
+    <n v="93"/>
+    <n v="53"/>
+    <n v="76"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="22"/>
+    <x v="35"/>
+    <s v="B"/>
+    <n v="24"/>
+    <n v="118"/>
+    <n v="94"/>
+    <n v="59"/>
+    <n v="59"/>
+    <s v="TBD"/>
+    <x v="0"/>
+    <m/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="20"/>
+    <x v="11"/>
+    <s v="A"/>
+    <n v="9"/>
+    <n v="83"/>
+    <n v="74"/>
+    <n v="39"/>
+    <n v="44"/>
+    <s v="TBD"/>
+    <x v="1"/>
+    <n v="12"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="4"/>
+    <x v="36"/>
+    <s v="A"/>
+    <n v="20"/>
+    <n v="98"/>
+    <n v="78"/>
+    <n v="47"/>
+    <n v="51"/>
+    <s v="TBD"/>
+    <x v="2"/>
+    <m/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="3"/>
+    <x v="14"/>
+    <s v="A"/>
+    <n v="8"/>
+    <n v="89"/>
+    <n v="81"/>
+    <n v="43"/>
+    <n v="46"/>
+    <s v="TBD"/>
+    <x v="2"/>
+    <m/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="6"/>
+    <x v="8"/>
+    <s v="A"/>
+    <n v="21"/>
+    <n v="102"/>
+    <n v="81"/>
+    <n v="52"/>
+    <n v="50"/>
+    <s v="TBD"/>
+    <x v="2"/>
+    <m/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="36"/>
+    <x v="0"/>
+    <s v="A"/>
+    <n v="9"/>
+    <n v="92"/>
+    <n v="83"/>
+    <n v="48"/>
+    <n v="44"/>
+    <s v="TBD"/>
+    <x v="1"/>
+    <n v="7.5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="29"/>
+    <x v="16"/>
+    <s v="A"/>
+    <n v="13"/>
+    <n v="96"/>
+    <n v="83"/>
+    <n v="48"/>
+    <n v="48"/>
+    <s v="TBD"/>
+    <x v="2"/>
+    <m/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="35"/>
+    <x v="3"/>
+    <s v="A"/>
+    <n v="21"/>
+    <n v="105"/>
+    <n v="84"/>
+    <n v="53"/>
+    <n v="52"/>
+    <s v="TBD"/>
+    <x v="2"/>
+    <m/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="32"/>
+    <x v="15"/>
+    <s v="A"/>
+    <n v="11"/>
+    <n v="100"/>
+    <n v="89"/>
+    <n v="53"/>
+    <n v="47"/>
+    <s v="TBD"/>
+    <x v="2"/>
+    <m/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="34"/>
+    <x v="1"/>
+    <s v="A"/>
+    <n v="14"/>
+    <n v="104"/>
+    <n v="90"/>
+    <n v="59"/>
+    <n v="45"/>
+    <s v="TBD"/>
+    <x v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="12"/>
+    <x v="2"/>
+    <s v="A"/>
+    <n v="20"/>
+    <n v="111"/>
+    <n v="91"/>
+    <n v="56"/>
+    <n v="55"/>
+    <s v="TBD"/>
+    <x v="2"/>
+    <m/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="9"/>
+    <s v="A"/>
+    <n v="12"/>
+    <n v="107"/>
+    <n v="95"/>
+    <n v="50"/>
+    <n v="57"/>
+    <s v="TBD"/>
+    <x v="2"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="37"/>
+    <s v="A"/>
+    <n v="13"/>
+    <n v="117"/>
+    <n v="104"/>
+    <n v="61"/>
+    <n v="56"/>
+    <s v="TBD"/>
+    <x v="2"/>
+    <m/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="28"/>
+    <x v="20"/>
+    <s v="B"/>
+    <n v="34"/>
+    <n v="106"/>
+    <n v="72"/>
+    <n v="50"/>
+    <n v="56"/>
+    <s v="TBD"/>
+    <x v="2"/>
+    <m/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="26"/>
+    <x v="18"/>
+    <s v="B"/>
+    <n v="20"/>
+    <n v="93"/>
+    <n v="73"/>
+    <n v="49"/>
+    <n v="44"/>
+    <s v="TBD"/>
+    <x v="1"/>
+    <m/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="9"/>
+    <x v="21"/>
+    <s v="B"/>
+    <n v="19"/>
+    <n v="93"/>
+    <n v="74"/>
+    <n v="45"/>
+    <n v="48"/>
+    <s v="TBD"/>
+    <x v="1"/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="18"/>
+    <x v="38"/>
+    <s v="B"/>
+    <n v="36"/>
+    <n v="113"/>
+    <n v="77"/>
+    <n v="57"/>
+    <n v="56"/>
+    <s v="TBD"/>
+    <x v="2"/>
+    <m/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="19"/>
+    <x v="23"/>
+    <s v="B"/>
+    <n v="24"/>
+    <n v="102"/>
+    <n v="78"/>
+    <n v="54"/>
+    <n v="48"/>
+    <s v="TBD"/>
+    <x v="1"/>
+    <n v="7.5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="19"/>
+    <s v="B"/>
+    <n v="20"/>
+    <n v="98"/>
+    <n v="78"/>
+    <n v="48"/>
+    <n v="50"/>
+    <s v="TBD"/>
+    <x v="2"/>
+    <m/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1"/>
+    <x v="22"/>
+    <s v="B"/>
+    <n v="20"/>
+    <n v="103"/>
+    <n v="83"/>
+    <n v="55"/>
+    <n v="48"/>
+    <s v="TBD"/>
+    <x v="1"/>
+    <n v="5.5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="24"/>
+    <x v="27"/>
+    <s v="B"/>
+    <n v="24"/>
+    <n v="107"/>
+    <n v="83"/>
+    <n v="55"/>
+    <n v="52"/>
+    <s v="TBD"/>
+    <x v="2"/>
+    <m/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="30"/>
+    <x v="25"/>
+    <s v="B"/>
+    <n v="33"/>
+    <n v="121"/>
+    <n v="88"/>
+    <n v="63"/>
+    <n v="58"/>
+    <s v="TBD"/>
+    <x v="2"/>
+    <m/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="22"/>
+    <x v="35"/>
+    <s v="B"/>
+    <n v="22"/>
+    <n v="115"/>
+    <n v="93"/>
+    <n v="57"/>
+    <n v="58"/>
+    <s v="TBD"/>
+    <x v="2"/>
+    <m/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="23"/>
+    <x v="17"/>
+    <s v="B"/>
+    <n v="22"/>
+    <n v="121"/>
+    <n v="99"/>
+    <n v="61"/>
+    <n v="60"/>
+    <s v="TBD"/>
+    <x v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="25"/>
+    <x v="39"/>
+    <s v="B"/>
+    <n v="36"/>
+    <n v="140"/>
+    <n v="104"/>
+    <n v="65"/>
+    <n v="75"/>
+    <s v="TBD"/>
+    <x v="2"/>
+    <m/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="8"/>
+    <x v="4"/>
+    <s v="A"/>
+    <n v="20"/>
+    <n v="92"/>
+    <n v="72"/>
+    <n v="46"/>
+    <n v="46"/>
+    <s v="TBD"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="6"/>
+    <x v="8"/>
+    <s v="A"/>
+    <n v="21"/>
+    <n v="93"/>
+    <n v="72"/>
+    <n v="46"/>
+    <n v="47"/>
+    <s v="TBD"/>
+    <x v="1"/>
+    <n v="13.5"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="29"/>
+    <x v="16"/>
+    <s v="A"/>
+    <n v="20"/>
+    <n v="94"/>
+    <n v="74"/>
+    <n v="47"/>
+    <n v="47"/>
+    <s v="TBD"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="7"/>
+    <x v="12"/>
+    <s v="A"/>
+    <n v="17"/>
+    <n v="92"/>
+    <n v="75"/>
+    <n v="46"/>
+    <n v="46"/>
+    <s v="TBD"/>
+    <x v="1"/>
+    <n v="11"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="32"/>
+    <x v="15"/>
+    <s v="A"/>
+    <n v="10"/>
+    <n v="90"/>
+    <n v="80"/>
+    <n v="43"/>
+    <n v="47"/>
+    <s v="TBD"/>
+    <x v="1"/>
+    <n v="8.5"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="20"/>
+    <x v="11"/>
+    <s v="A"/>
+    <n v="7"/>
+    <n v="87"/>
+    <n v="80"/>
+    <n v="43"/>
+    <n v="44"/>
+    <s v="TBD"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="12"/>
+    <x v="2"/>
+    <s v="A"/>
+    <n v="20"/>
+    <n v="100"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="50"/>
+    <s v="TBD"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="27"/>
+    <x v="10"/>
+    <s v="A"/>
+    <n v="20"/>
+    <n v="100"/>
+    <n v="80"/>
+    <n v="53"/>
+    <n v="47"/>
+    <s v="TBD"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="15"/>
+    <x v="9"/>
+    <s v="A"/>
+    <n v="15"/>
+    <n v="98"/>
+    <n v="83"/>
+    <n v="49"/>
+    <n v="49"/>
+    <s v="TBD"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="34"/>
+    <x v="1"/>
+    <s v="A"/>
+    <n v="12"/>
+    <n v="95"/>
+    <n v="83"/>
+    <n v="50"/>
+    <n v="45"/>
+    <s v="TBD"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="17"/>
+    <x v="7"/>
+    <s v="A"/>
+    <n v="13"/>
+    <n v="96"/>
+    <n v="83"/>
+    <n v="51"/>
+    <n v="45"/>
+    <s v="TBD"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="3"/>
+    <x v="14"/>
+    <s v="A"/>
+    <n v="8"/>
+    <n v="97"/>
+    <n v="89"/>
+    <n v="50"/>
+    <n v="47"/>
+    <s v="TBD"/>
+    <x v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="13"/>
+    <x v="28"/>
+    <s v="A"/>
+    <n v="21"/>
+    <n v="118"/>
+    <n v="97"/>
+    <n v="64"/>
+    <n v="54"/>
+    <s v="TBD"/>
+    <x v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="5"/>
+    <x v="37"/>
+    <s v="A"/>
+    <n v="14"/>
+    <n v="119"/>
+    <n v="105"/>
+    <n v="59"/>
+    <n v="60"/>
+    <s v="TBD"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="24"/>
+    <x v="27"/>
+    <s v="B"/>
+    <n v="26"/>
+    <n v="92"/>
+    <n v="66"/>
+    <n v="50"/>
+    <n v="42"/>
+    <s v="TBD"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="22"/>
+    <s v="B"/>
+    <n v="22"/>
+    <n v="90"/>
+    <n v="68"/>
+    <n v="44"/>
+    <n v="46"/>
+    <s v="TBD"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="26"/>
+    <x v="18"/>
+    <s v="B"/>
+    <n v="20"/>
+    <n v="92"/>
+    <n v="72"/>
+    <n v="45"/>
+    <n v="47"/>
+    <s v="TBD"/>
+    <x v="1"/>
+    <n v="11.5"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="28"/>
+    <x v="20"/>
+    <s v="B"/>
+    <n v="31"/>
+    <n v="103"/>
+    <n v="72"/>
+    <n v="53"/>
+    <n v="50"/>
+    <s v="TBD"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="35"/>
+    <x v="3"/>
+    <s v="B"/>
+    <n v="19"/>
+    <n v="96"/>
+    <n v="77"/>
+    <n v="49"/>
+    <n v="47"/>
+    <s v="TBD"/>
+    <x v="1"/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="33"/>
+    <x v="26"/>
+    <s v="B"/>
+    <n v="21"/>
+    <n v="99"/>
+    <n v="78"/>
+    <n v="51"/>
+    <n v="48"/>
+    <s v="TBD"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="19"/>
+    <x v="23"/>
+    <s v="B"/>
+    <n v="24"/>
+    <n v="102"/>
+    <n v="78"/>
+    <n v="52"/>
+    <n v="50"/>
+    <s v="TBD"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="39"/>
+    <x v="30"/>
+    <s v="B"/>
+    <n v="29"/>
+    <n v="107"/>
+    <n v="78"/>
+    <n v="54"/>
+    <n v="53"/>
+    <s v="TBD"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="10"/>
+    <x v="19"/>
+    <s v="B"/>
+    <n v="20"/>
+    <n v="101"/>
+    <n v="81"/>
+    <n v="48"/>
+    <n v="53"/>
+    <s v="TBD"/>
+    <x v="1"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="30"/>
+    <x v="25"/>
+    <s v="B"/>
+    <n v="32"/>
+    <n v="113"/>
+    <n v="81"/>
+    <n v="58"/>
+    <n v="55"/>
+    <s v="TBD"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="9"/>
+    <x v="21"/>
+    <s v="B"/>
+    <n v="19"/>
+    <n v="100"/>
+    <n v="81"/>
+    <n v="52"/>
+    <n v="48"/>
+    <s v="TBD"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="2"/>
+    <x v="24"/>
+    <s v="B"/>
+    <n v="36"/>
+    <n v="122"/>
+    <n v="86"/>
+    <n v="63"/>
+    <n v="59"/>
+    <s v="TBD"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="22"/>
+    <x v="35"/>
+    <s v="B"/>
+    <n v="29"/>
+    <n v="115"/>
+    <n v="86"/>
+    <n v="58"/>
+    <n v="57"/>
+    <s v="TBD"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="25"/>
+    <x v="39"/>
+    <s v="B"/>
+    <n v="36"/>
+    <n v="130"/>
+    <n v="94"/>
+    <n v="69"/>
+    <n v="61"/>
+    <s v="TBD"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="29"/>
+    <x v="16"/>
+    <s v="A"/>
+    <n v="17"/>
+    <n v="84"/>
+    <n v="67"/>
+    <n v="41"/>
+    <n v="43"/>
+    <n v="32"/>
+    <x v="1"/>
+    <n v="18"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="40"/>
+    <x v="40"/>
+    <s v="A"/>
+    <n v="8"/>
+    <n v="76"/>
+    <n v="68"/>
+    <n v="37"/>
+    <n v="39"/>
+    <n v="35"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="7"/>
+    <x v="12"/>
+    <s v="A"/>
+    <n v="15"/>
+    <n v="86"/>
+    <n v="71"/>
+    <n v="45"/>
+    <n v="41"/>
+    <n v="40"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="15"/>
+    <x v="9"/>
+    <s v="A"/>
+    <n v="16"/>
+    <n v="87"/>
+    <n v="71"/>
+    <n v="45"/>
+    <n v="42"/>
+    <n v="35"/>
+    <x v="1"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="20"/>
+    <x v="11"/>
+    <s v="A"/>
+    <n v="8"/>
+    <n v="79"/>
+    <n v="71"/>
+    <n v="38"/>
+    <n v="41"/>
+    <n v="31"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="26"/>
+    <x v="18"/>
+    <s v="A"/>
+    <n v="21"/>
+    <n v="93"/>
+    <n v="72"/>
+    <n v="47"/>
+    <n v="46"/>
+    <n v="38"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="34"/>
+    <x v="1"/>
+    <s v="A"/>
+    <n v="13"/>
+    <n v="86"/>
+    <n v="73"/>
+    <n v="48"/>
+    <n v="38"/>
+    <n v="33"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="37"/>
+    <x v="5"/>
+    <s v="A"/>
+    <n v="8"/>
+    <n v="83"/>
+    <n v="75"/>
+    <n v="40"/>
+    <n v="43"/>
+    <n v="32"/>
+    <x v="1"/>
+    <n v="11"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="36"/>
+    <x v="0"/>
+    <s v="A"/>
+    <n v="9"/>
+    <n v="85"/>
+    <n v="76"/>
+    <n v="42"/>
+    <n v="43"/>
+    <n v="34"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="17"/>
+    <x v="7"/>
+    <s v="A"/>
+    <n v="15"/>
+    <n v="93"/>
+    <n v="78"/>
+    <n v="42"/>
+    <n v="51"/>
+    <n v="35"/>
+    <x v="1"/>
+    <n v="9"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="8"/>
+    <x v="4"/>
+    <s v="A"/>
+    <n v="17"/>
+    <n v="96"/>
+    <n v="79"/>
+    <n v="50"/>
+    <n v="46"/>
+    <n v="33"/>
+    <x v="1"/>
+    <n v="7.5"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="41"/>
+    <x v="41"/>
+    <s v="A"/>
+    <n v="15"/>
+    <n v="94"/>
+    <n v="79"/>
+    <n v="46"/>
+    <n v="48"/>
+    <n v="35"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="3"/>
+    <x v="14"/>
+    <s v="A"/>
+    <n v="9"/>
+    <n v="89"/>
+    <n v="80"/>
+    <n v="46"/>
+    <n v="43"/>
+    <n v="29"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="16"/>
+    <x v="6"/>
+    <s v="A"/>
+    <n v="18"/>
+    <n v="98"/>
+    <n v="80"/>
+    <n v="49"/>
+    <n v="49"/>
+    <n v="39"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="12"/>
+    <x v="2"/>
+    <s v="A"/>
+    <n v="20"/>
+    <n v="101"/>
+    <n v="81"/>
+    <n v="53"/>
+    <n v="48"/>
+    <n v="35"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="35"/>
+    <x v="3"/>
+    <s v="A"/>
+    <n v="21"/>
+    <n v="103"/>
+    <n v="82"/>
+    <n v="52"/>
+    <n v="51"/>
+    <n v="34"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="31"/>
+    <x v="42"/>
+    <s v="A"/>
+    <n v="17"/>
+    <n v="104"/>
+    <n v="87"/>
+    <n v="50"/>
+    <n v="54"/>
+    <n v="38"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="42"/>
+    <x v="43"/>
+    <s v="A"/>
+    <n v="11"/>
+    <n v="100"/>
+    <n v="89"/>
+    <n v="43"/>
+    <n v="57"/>
+    <n v="34"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="10"/>
+    <x v="19"/>
+    <s v="B"/>
+    <n v="20"/>
+    <n v="88"/>
+    <n v="68"/>
+    <n v="47"/>
+    <n v="41"/>
+    <n v="32"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="19"/>
+    <x v="23"/>
+    <s v="B"/>
+    <n v="24"/>
+    <n v="92"/>
+    <n v="68"/>
+    <n v="44"/>
+    <n v="48"/>
+    <n v="37"/>
+    <x v="1"/>
+    <n v="16.5"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="18"/>
+    <x v="38"/>
+    <s v="B"/>
+    <n v="36"/>
+    <n v="106"/>
+    <n v="70"/>
+    <n v="55"/>
+    <n v="51"/>
+    <n v="39"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="30"/>
+    <x v="25"/>
+    <s v="B"/>
+    <n v="30"/>
+    <n v="101"/>
+    <n v="71"/>
+    <n v="53"/>
+    <n v="48"/>
+    <n v="34"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="1"/>
+    <x v="22"/>
+    <s v="B"/>
+    <n v="22"/>
+    <n v="94"/>
+    <n v="72"/>
+    <n v="44"/>
+    <n v="50"/>
+    <n v="35"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="2"/>
+    <x v="24"/>
+    <s v="B"/>
+    <n v="36"/>
+    <n v="109"/>
+    <n v="73"/>
+    <n v="52"/>
+    <n v="57"/>
+    <n v="31"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="27"/>
+    <x v="10"/>
+    <s v="B"/>
+    <n v="19"/>
+    <n v="92"/>
+    <n v="73"/>
+    <n v="45"/>
+    <n v="47"/>
+    <n v="33"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="6"/>
+    <x v="8"/>
+    <s v="B"/>
+    <n v="16"/>
+    <n v="91"/>
+    <n v="75"/>
+    <n v="44"/>
+    <n v="47"/>
+    <n v="31"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="33"/>
+    <x v="26"/>
+    <s v="B"/>
+    <n v="22"/>
+    <n v="98"/>
+    <n v="76"/>
+    <n v="49"/>
+    <n v="49"/>
+    <n v="33"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="24"/>
+    <x v="27"/>
+    <s v="B"/>
+    <n v="22"/>
+    <n v="100"/>
+    <n v="78"/>
+    <n v="49"/>
+    <n v="51"/>
+    <n v="38"/>
+    <x v="1"/>
+    <n v="7.5"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="25"/>
+    <x v="39"/>
+    <s v="B"/>
+    <n v="36"/>
+    <n v="114"/>
+    <n v="78"/>
+    <n v="58"/>
+    <n v="56"/>
+    <n v="37"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="28"/>
+    <x v="20"/>
+    <s v="B"/>
+    <n v="30"/>
+    <n v="109"/>
+    <n v="79"/>
+    <n v="60"/>
+    <n v="49"/>
+    <n v="42"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="38"/>
+    <x v="32"/>
+    <s v="B"/>
+    <n v="20"/>
+    <n v="100"/>
+    <n v="80"/>
+    <n v="51"/>
+    <n v="49"/>
+    <n v="38"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="22"/>
+    <x v="35"/>
+    <s v="B"/>
+    <n v="24"/>
+    <n v="105"/>
+    <n v="81"/>
+    <n v="53"/>
+    <n v="52"/>
+    <n v="38"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="9"/>
+    <x v="21"/>
+    <s v="B"/>
+    <n v="19"/>
+    <n v="105"/>
+    <n v="86"/>
+    <n v="54"/>
+    <n v="51"/>
+    <n v="37"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="11"/>
+    <x v="31"/>
+    <s v="B"/>
+    <n v="30"/>
+    <n v="120"/>
+    <n v="90"/>
+    <n v="55"/>
+    <n v="65"/>
+    <n v="39"/>
+    <x v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="14"/>
+    <x v="34"/>
+    <s v="B"/>
+    <n v="36"/>
+    <n v="132"/>
+    <n v="96"/>
+    <n v="73"/>
+    <n v="59"/>
+    <n v="39"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="41"/>
+    <x v="41"/>
+    <s v="A"/>
+    <n v="13"/>
+    <n v="85"/>
+    <n v="72"/>
+    <n v="40"/>
+    <n v="45"/>
+    <n v="34"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="13"/>
+    <x v="28"/>
+    <s v="A"/>
+    <n v="21"/>
+    <n v="94"/>
+    <n v="73"/>
+    <n v="44"/>
+    <n v="50"/>
+    <n v="36"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="35"/>
+    <x v="3"/>
+    <s v="A"/>
+    <n v="20"/>
+    <n v="93"/>
+    <n v="73"/>
+    <n v="47"/>
+    <n v="46"/>
+    <n v="30"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="7"/>
+    <x v="12"/>
+    <s v="A"/>
+    <n v="12"/>
+    <n v="86"/>
+    <n v="74"/>
+    <n v="43"/>
+    <n v="43"/>
+    <n v="35"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="15"/>
+    <x v="9"/>
+    <s v="A"/>
+    <n v="14"/>
+    <n v="88"/>
+    <n v="74"/>
+    <n v="47"/>
+    <n v="41"/>
+    <n v="26"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="17"/>
+    <x v="7"/>
+    <s v="A"/>
+    <n v="15"/>
+    <n v="89"/>
+    <n v="74"/>
+    <n v="48"/>
+    <n v="41"/>
+    <n v="32"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="20"/>
+    <x v="11"/>
+    <s v="A"/>
+    <n v="8"/>
+    <n v="84"/>
+    <n v="76"/>
+    <n v="45"/>
+    <n v="39"/>
+    <n v="32"/>
+    <x v="1"/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="26"/>
+    <x v="18"/>
+    <s v="A"/>
+    <n v="19"/>
+    <n v="96"/>
+    <n v="77"/>
+    <n v="47"/>
+    <n v="49"/>
+    <n v="30"/>
+    <x v="1"/>
+    <n v="6.5"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="29"/>
+    <x v="16"/>
+    <s v="A"/>
+    <n v="14"/>
+    <n v="91"/>
+    <n v="77"/>
+    <n v="48"/>
+    <n v="43"/>
+    <n v="35"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="36"/>
+    <x v="0"/>
+    <s v="A"/>
+    <n v="9"/>
+    <n v="88"/>
+    <n v="79"/>
+    <n v="47"/>
+    <n v="41"/>
+    <n v="34"/>
+    <x v="1"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="6"/>
+    <x v="8"/>
+    <s v="A"/>
+    <n v="17"/>
+    <n v="97"/>
+    <n v="80"/>
+    <n v="45"/>
+    <n v="52"/>
+    <n v="33"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="44"/>
+    <x v="44"/>
+    <s v="A"/>
+    <n v="19"/>
+    <n v="100"/>
+    <n v="81"/>
+    <n v="53"/>
+    <n v="47"/>
+    <n v="36"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="4"/>
+    <x v="36"/>
+    <s v="A"/>
+    <n v="20"/>
+    <n v="106"/>
+    <n v="86"/>
+    <n v="48"/>
+    <n v="58"/>
+    <n v="32"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="34"/>
+    <x v="1"/>
+    <s v="A"/>
+    <n v="12"/>
+    <n v="100"/>
+    <n v="88"/>
+    <n v="48"/>
+    <n v="52"/>
+    <n v="35"/>
+    <x v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="14"/>
+    <x v="34"/>
+    <s v="B"/>
+    <n v="36"/>
+    <n v="104"/>
+    <n v="68"/>
+    <n v="52"/>
+    <n v="52"/>
+    <n v="37"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="10"/>
+    <x v="19"/>
+    <s v="B"/>
+    <n v="19"/>
+    <n v="92"/>
+    <n v="73"/>
+    <n v="47"/>
+    <n v="45"/>
+    <n v="28"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="43"/>
+    <x v="45"/>
+    <s v="B"/>
+    <n v="30"/>
+    <n v="104"/>
+    <n v="74"/>
+    <n v="51"/>
+    <n v="53"/>
+    <n v="38"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="1"/>
+    <x v="22"/>
+    <s v="B"/>
+    <n v="21"/>
+    <n v="96"/>
+    <n v="75"/>
+    <n v="51"/>
+    <n v="45"/>
+    <n v="31"/>
+    <x v="1"/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="24"/>
+    <x v="27"/>
+    <s v="B"/>
+    <n v="23"/>
+    <n v="98"/>
+    <n v="75"/>
+    <n v="47"/>
+    <n v="51"/>
+    <n v="36"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="38"/>
+    <x v="32"/>
+    <s v="B"/>
+    <n v="20"/>
+    <n v="95"/>
+    <n v="75"/>
+    <n v="47"/>
+    <n v="48"/>
+    <n v="35"/>
+    <x v="1"/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="18"/>
+    <x v="38"/>
+    <s v="B"/>
+    <n v="36"/>
+    <n v="112"/>
+    <n v="76"/>
+    <n v="58"/>
+    <n v="54"/>
+    <n v="36"/>
+    <x v="1"/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="19"/>
+    <x v="23"/>
+    <s v="B"/>
+    <n v="22"/>
+    <n v="99"/>
+    <n v="77"/>
+    <n v="51"/>
+    <n v="48"/>
+    <n v="34"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="28"/>
+    <x v="20"/>
+    <s v="B"/>
+    <n v="31"/>
+    <n v="110"/>
+    <n v="79"/>
+    <n v="52"/>
+    <n v="58"/>
+    <n v="39"/>
+    <x v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="30"/>
+    <x v="25"/>
+    <s v="B"/>
+    <n v="35"/>
+    <n v="116"/>
+    <n v="81"/>
+    <n v="58"/>
+    <n v="58"/>
+    <n v="36"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="9"/>
+    <x v="21"/>
+    <s v="B"/>
+    <n v="20"/>
+    <n v="105"/>
+    <n v="85"/>
+    <n v="45"/>
+    <n v="60"/>
+    <n v="33"/>
+    <x v="3"/>
+    <m/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="25"/>
+    <x v="39"/>
+    <s v="B"/>
+    <n v="36"/>
+    <n v="127"/>
+    <n v="91"/>
+    <n v="67"/>
+    <n v="60"/>
+    <n v="39"/>
+    <x v="3"/>
+    <m/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6B84E77E-8640-4E4C-884A-D557847C822A}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="12">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="47">
+        <item h="1" x="24"/>
+        <item h="1" x="14"/>
+        <item h="1" x="22"/>
+        <item h="1" x="36"/>
+        <item h="1" x="37"/>
+        <item h="1" x="8"/>
+        <item h="1" x="30"/>
+        <item h="1" x="12"/>
+        <item h="1" x="4"/>
+        <item h="1" x="21"/>
+        <item h="1" x="19"/>
+        <item h="1" x="31"/>
+        <item h="1" x="2"/>
+        <item h="1" x="28"/>
+        <item h="1" x="34"/>
+        <item h="1" x="13"/>
+        <item h="1" x="45"/>
+        <item h="1" x="43"/>
+        <item h="1" x="9"/>
+        <item h="1" x="6"/>
+        <item h="1" x="7"/>
+        <item h="1" x="38"/>
+        <item h="1" x="25"/>
+        <item h="1" x="23"/>
+        <item h="1" x="11"/>
+        <item h="1" x="40"/>
+        <item h="1" x="33"/>
+        <item h="1" x="35"/>
+        <item h="1" x="41"/>
+        <item h="1" x="17"/>
+        <item h="1" x="44"/>
+        <item h="1" x="27"/>
+        <item h="1" x="39"/>
+        <item h="1" x="18"/>
+        <item h="1" x="10"/>
+        <item h="1" x="20"/>
+        <item h="1" x="16"/>
+        <item h="1" x="42"/>
+        <item h="1" x="15"/>
+        <item h="1" x="26"/>
+        <item h="1" x="1"/>
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
+        <item h="1" x="5"/>
+        <item h="1" x="29"/>
+        <item h="1" x="32"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="5">
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item x="1"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="0"/>
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="1">
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="10" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of TGL Points" fld="11" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11257,4 +13586,40 @@
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F879FA0E-F1DC-144C-8C37-AC2E1B6DC0E5}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" s="33"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/MIGC_Season_Dashboard.xlsx
+++ b/MIGC_Season_Dashboard.xlsx
@@ -8,27 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevinvargas/Desktop/migc-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A89A63A-7800-044B-981D-D3814C90B386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC647395-F83B-6D48-B07F-2F1B5641F25C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="19160" activeTab="1" xr2:uid="{BBF77493-EF1A-3942-9440-E7AC2E03DB26}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="19160" activeTab="3" xr2:uid="{BBF77493-EF1A-3942-9440-E7AC2E03DB26}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="2" r:id="rId1"/>
     <sheet name="Tournament_Info" sheetId="3" r:id="rId2"/>
     <sheet name="Tournament_Results" sheetId="1" r:id="rId3"/>
-    <sheet name="Tournament_Acheivements" sheetId="4" r:id="rId4"/>
-    <sheet name="Tournament_Skins" sheetId="5" r:id="rId5"/>
-    <sheet name="Summary" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet2" sheetId="8" r:id="rId4"/>
+    <sheet name="Tournament_Acheivements" sheetId="4" r:id="rId5"/>
+    <sheet name="Tournament_Skins" sheetId="5" r:id="rId6"/>
+    <sheet name="Summary" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Players!$A$1:$D$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Tournament_Acheivements!$A$1:$F$122</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Tournament_Results!$A$1:$L$150</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Tournament_Skins!$A$1:$F$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Tournament_Acheivements!$A$1:$F$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Tournament_Results!$A$1:$M$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Tournament_Skins!$A$1:$F$57</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId7"/>
+    <pivotCache cacheId="10" r:id="rId8"/>
+    <pivotCache cacheId="42" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -50,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1565" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="132">
   <si>
     <t>Tournament ID</t>
   </si>
@@ -444,6 +446,9 @@
   <si>
     <t>(All)</t>
   </si>
+  <si>
+    <t>Sum of Amount</t>
+  </si>
 </sst>
 </file>
 
@@ -623,7 +628,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -633,6 +637,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -871,6 +876,77 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Kevin Vargas" refreshedDate="46205.655988078703" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="146" xr:uid="{A6D1F967-7EF8-7A46-B934-679A2410D049}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:F147" sheet="Tournament_Acheivements"/>
+  </cacheSource>
+  <cacheFields count="6">
+    <cacheField name="Tournament ID" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Player ID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="47"/>
+    </cacheField>
+    <cacheField name="Player" numFmtId="0">
+      <sharedItems count="37">
+        <s v="Tai Ho"/>
+        <s v="Spencer Higgins"/>
+        <s v="Max O'Brien"/>
+        <s v="Darrick Sogabe"/>
+        <s v="Tam Tran"/>
+        <s v="Taylor Yates"/>
+        <s v="Mikel Hodges"/>
+        <s v="Colin Harrison"/>
+        <s v="Devan French"/>
+        <s v="Kevin Taylor"/>
+        <s v="Danny Lopez"/>
+        <s v="Paul Hsieh"/>
+        <s v="Tom Shea"/>
+        <s v="Mike Pena"/>
+        <s v="Mike Paguyo"/>
+        <s v="Kevin Vargas"/>
+        <s v="Carlos Bouloy"/>
+        <s v="Brock Hansen"/>
+        <s v="Colin Chang"/>
+        <s v="Adrianna Moore"/>
+        <s v="Nick Harris"/>
+        <s v="Paul Toledo"/>
+        <s v="Art Hernandez"/>
+        <s v="Chris Chang"/>
+        <s v="Lucas Bouloy"/>
+        <s v="Jorge Rayo"/>
+        <s v="John Nothdurft"/>
+        <s v="Juan Ramirez"/>
+        <s v="Ken Sogabe"/>
+        <s v="Andy Pendleton"/>
+        <s v="Med Baheta"/>
+        <s v="JP Hill"/>
+        <s v="Mat Vigil"/>
+        <s v="David Wu"/>
+        <s v="Jason Payton"/>
+        <s v="Marcel Mendoza"/>
+        <s v="William Colbert"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Category" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Placement" numFmtId="0">
+      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="3"/>
+    </cacheField>
+    <cacheField name="Amount" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="4" maxValue="95"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="149">
   <r>
@@ -2962,8 +3038,1379 @@
 </pivotCacheRecords>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="146">
+  <r>
+    <s v="2026_01"/>
+    <n v="34"/>
+    <x v="0"/>
+    <s v="Closest to the Pin"/>
+    <s v="Winner"/>
+    <n v="47.5"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="32"/>
+    <x v="1"/>
+    <s v="Closest to the Pin"/>
+    <s v="Winner"/>
+    <n v="47.5"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="34"/>
+    <x v="0"/>
+    <s v="Closest to the Pin"/>
+    <s v="Winner"/>
+    <n v="47.5"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="23"/>
+    <x v="2"/>
+    <s v="Closest to the Pin"/>
+    <s v="Winner"/>
+    <n v="47.5"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="34"/>
+    <x v="0"/>
+    <s v="Flight A - Back 9"/>
+    <n v="1"/>
+    <n v="38"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="12"/>
+    <x v="3"/>
+    <s v="Flight A - Back 9"/>
+    <n v="2"/>
+    <n v="9.5"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="35"/>
+    <x v="4"/>
+    <s v="Flight A - Back 9"/>
+    <n v="2"/>
+    <n v="9.5"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="36"/>
+    <x v="5"/>
+    <s v="Flight A - Front 9"/>
+    <n v="1"/>
+    <n v="38"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="34"/>
+    <x v="0"/>
+    <s v="Flight A - Front 9"/>
+    <n v="2"/>
+    <n v="19"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="36"/>
+    <x v="5"/>
+    <s v="Flight A - Long Drive"/>
+    <s v="Winner"/>
+    <n v="38"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="36"/>
+    <x v="5"/>
+    <s v="Flight A - Overall"/>
+    <n v="1"/>
+    <n v="76"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="34"/>
+    <x v="0"/>
+    <s v="Flight A - Overall"/>
+    <n v="1"/>
+    <n v="76"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="12"/>
+    <x v="3"/>
+    <s v="Flight A - Overall"/>
+    <n v="3"/>
+    <n v="19"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="35"/>
+    <x v="4"/>
+    <s v="Flight A - Overall"/>
+    <n v="3"/>
+    <n v="19"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="26"/>
+    <x v="6"/>
+    <s v="Flight B - Back 9"/>
+    <n v="1"/>
+    <n v="38"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="23"/>
+    <x v="2"/>
+    <s v="Flight B - Back 9"/>
+    <n v="2"/>
+    <n v="19"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="9"/>
+    <x v="7"/>
+    <s v="Flight B - Front 9"/>
+    <n v="1"/>
+    <n v="38"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="14"/>
+    <x v="8"/>
+    <s v="Flight B - Front 9"/>
+    <n v="2"/>
+    <n v="9.5"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="19"/>
+    <x v="9"/>
+    <s v="Flight B - Front 9"/>
+    <n v="2"/>
+    <n v="9.5"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="23"/>
+    <x v="2"/>
+    <s v="Flight B - Long Drive"/>
+    <s v="Winner"/>
+    <n v="38"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="23"/>
+    <x v="2"/>
+    <s v="Flight B - Overall"/>
+    <n v="1"/>
+    <n v="95"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="26"/>
+    <x v="6"/>
+    <s v="Flight B - Overall"/>
+    <n v="2"/>
+    <n v="57"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="10"/>
+    <x v="10"/>
+    <s v="Flight B - Overall"/>
+    <n v="3"/>
+    <n v="19"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="28"/>
+    <x v="11"/>
+    <s v="Flight B - Overall"/>
+    <n v="3"/>
+    <n v="19"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="12"/>
+    <x v="3"/>
+    <s v="Low Putts"/>
+    <n v="1"/>
+    <n v="12.66"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="37"/>
+    <x v="12"/>
+    <s v="Low Putts"/>
+    <n v="1"/>
+    <n v="12.66"/>
+  </r>
+  <r>
+    <s v="2026_01"/>
+    <n v="35"/>
+    <x v="4"/>
+    <s v="Low Putts"/>
+    <n v="1"/>
+    <n v="12.66"/>
+  </r>
+  <r>
+    <s v="2026_02"/>
+    <n v="25"/>
+    <x v="13"/>
+    <s v="Closest to the Pin"/>
+    <s v="Winner"/>
+    <n v="30"/>
+  </r>
+  <r>
+    <s v="2026_02"/>
+    <n v="10"/>
+    <x v="10"/>
+    <s v="Closest to the Pin"/>
+    <s v="Winner"/>
+    <n v="30"/>
+  </r>
+  <r>
+    <s v="2026_02"/>
+    <n v="10"/>
+    <x v="10"/>
+    <s v="Closest to the Pin"/>
+    <s v="Winner"/>
+    <n v="30"/>
+  </r>
+  <r>
+    <s v="2026_02"/>
+    <n v="24"/>
+    <x v="14"/>
+    <s v="Closest to the Pin"/>
+    <s v="Winner"/>
+    <n v="30"/>
+  </r>
+  <r>
+    <s v="2026_02"/>
+    <n v="20"/>
+    <x v="15"/>
+    <s v="Flight A - Back 9"/>
+    <n v="2"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <s v="2026_02"/>
+    <n v="6"/>
+    <x v="16"/>
+    <s v="Flight A - Back 9"/>
+    <n v="2"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <s v="2026_02"/>
+    <n v="36"/>
+    <x v="5"/>
+    <s v="Flight A - Back 9"/>
+    <n v="2"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <s v="2026_02"/>
+    <n v="34"/>
+    <x v="0"/>
+    <s v="Flight A - Back 9"/>
+    <n v="1"/>
+    <n v="24"/>
+  </r>
+  <r>
+    <s v="2026_02"/>
+    <n v="20"/>
+    <x v="15"/>
+    <s v="Flight A - Front 9"/>
+    <n v="1"/>
+    <n v="24"/>
+  </r>
+  <r>
+    <s v="2026_02"/>
+    <n v="4"/>
+    <x v="17"/>
+    <s v="Flight A - Front 9"/>
+    <n v="2"/>
+    <n v="12"/>
+  </r>
+  <r>
+    <s v="2026_02"/>
+    <n v="20"/>
+    <x v="15"/>
+    <s v="Flight A - Long Drive"/>
+    <s v="Winner"/>
+    <n v="24"/>
+  </r>
+  <r>
+    <s v="2026_02"/>
+    <n v="20"/>
+    <x v="15"/>
+    <s v="Flight A - Overall"/>
+    <n v="1"/>
+    <n v="60"/>
+  </r>
+  <r>
+    <s v="2026_02"/>
+    <n v="4"/>
+    <x v="17"/>
+    <s v="Flight A - Overall"/>
+    <n v="2"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <s v="2026_02"/>
+    <n v="6"/>
+    <x v="16"/>
+    <s v="Flight A - Overall"/>
+    <n v="3"/>
+    <n v="24"/>
+  </r>
+  <r>
+    <s v="2026_02"/>
+    <n v="26"/>
+    <x v="6"/>
+    <s v="Flight B - Back 9"/>
+    <n v="1"/>
+    <n v="24"/>
+  </r>
+  <r>
+    <s v="2026_02"/>
+    <n v="19"/>
+    <x v="9"/>
+    <s v="Flight B - Back 9"/>
+    <n v="2"/>
+    <n v="12"/>
+  </r>
+  <r>
+    <s v="2026_02"/>
+    <n v="28"/>
+    <x v="11"/>
+    <s v="Flight B - Front 9"/>
+    <n v="1"/>
+    <n v="24"/>
+  </r>
+  <r>
+    <s v="2026_02"/>
+    <n v="9"/>
+    <x v="7"/>
+    <s v="Flight B - Front 9"/>
+    <n v="2"/>
+    <n v="12"/>
+  </r>
+  <r>
+    <s v="2026_02"/>
+    <n v="26"/>
+    <x v="6"/>
+    <s v="Flight B - Long Drive"/>
+    <s v="Winner"/>
+    <n v="24"/>
+  </r>
+  <r>
+    <s v="2026_02"/>
+    <n v="28"/>
+    <x v="11"/>
+    <s v="Flight B - Overall"/>
+    <n v="1"/>
+    <n v="60"/>
+  </r>
+  <r>
+    <s v="2026_02"/>
+    <n v="26"/>
+    <x v="6"/>
+    <s v="Flight B - Overall"/>
+    <n v="2"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <s v="2026_02"/>
+    <n v="9"/>
+    <x v="7"/>
+    <s v="Flight B - Overall"/>
+    <n v="3"/>
+    <n v="24"/>
+  </r>
+  <r>
+    <s v="2026_02"/>
+    <n v="20"/>
+    <x v="15"/>
+    <s v="Low Putts"/>
+    <s v="Winner"/>
+    <n v="24"/>
+  </r>
+  <r>
+    <s v="2026_03"/>
+    <n v="20"/>
+    <x v="15"/>
+    <s v="Closest to the Pin"/>
+    <s v="Winner"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <s v="2026_03"/>
+    <n v="26"/>
+    <x v="6"/>
+    <s v="Closest to the Pin"/>
+    <s v="Winner"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <s v="2026_03"/>
+    <n v="8"/>
+    <x v="18"/>
+    <s v="Closest to the Pin"/>
+    <s v="Winner"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <s v="2026_03"/>
+    <n v="2"/>
+    <x v="19"/>
+    <s v="Closest to the Pin"/>
+    <s v="Winner"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <s v="2026_03"/>
+    <n v="8"/>
+    <x v="18"/>
+    <s v="Flight A - Back 9"/>
+    <n v="1"/>
+    <n v="28"/>
+  </r>
+  <r>
+    <s v="2026_03"/>
+    <n v="6"/>
+    <x v="16"/>
+    <s v="Flight A - Back 9"/>
+    <n v="2"/>
+    <n v="7"/>
+  </r>
+  <r>
+    <s v="2026_03"/>
+    <n v="27"/>
+    <x v="20"/>
+    <s v="Flight A - Back 9"/>
+    <n v="2"/>
+    <n v="7"/>
+  </r>
+  <r>
+    <s v="2026_03"/>
+    <n v="29"/>
+    <x v="21"/>
+    <s v="Flight A - Front 9"/>
+    <n v="1"/>
+    <n v="28"/>
+  </r>
+  <r>
+    <s v="2026_03"/>
+    <n v="6"/>
+    <x v="16"/>
+    <s v="Flight A - Front 9"/>
+    <n v="2"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <s v="2026_03"/>
+    <n v="32"/>
+    <x v="1"/>
+    <s v="Flight A - Long Drive"/>
+    <s v="Winner"/>
+    <n v="28"/>
+  </r>
+  <r>
+    <s v="2026_03"/>
+    <n v="6"/>
+    <x v="16"/>
+    <s v="Flight A - Overall"/>
+    <n v="1"/>
+    <n v="56"/>
+  </r>
+  <r>
+    <s v="2026_03"/>
+    <n v="8"/>
+    <x v="18"/>
+    <s v="Flight A - Overall"/>
+    <n v="1"/>
+    <n v="56"/>
+  </r>
+  <r>
+    <s v="2026_03"/>
+    <n v="29"/>
+    <x v="21"/>
+    <s v="Flight A - Overall"/>
+    <n v="3"/>
+    <n v="28"/>
+  </r>
+  <r>
+    <s v="2026_03"/>
+    <n v="24"/>
+    <x v="14"/>
+    <s v="Flight B - Back 9"/>
+    <n v="1"/>
+    <n v="28"/>
+  </r>
+  <r>
+    <s v="2026_03"/>
+    <n v="1"/>
+    <x v="22"/>
+    <s v="Flight B - Back 9"/>
+    <n v="2"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <s v="2026_03"/>
+    <n v="26"/>
+    <x v="6"/>
+    <s v="Flight B - Front 9"/>
+    <n v="1"/>
+    <n v="28"/>
+  </r>
+  <r>
+    <s v="2026_03"/>
+    <n v="24"/>
+    <x v="14"/>
+    <s v="Flight B - Front 9"/>
+    <n v="2"/>
+    <n v="4.66"/>
+  </r>
+  <r>
+    <s v="2026_03"/>
+    <n v="1"/>
+    <x v="22"/>
+    <s v="Flight B - Front 9"/>
+    <n v="2"/>
+    <n v="4.66"/>
+  </r>
+  <r>
+    <s v="2026_03"/>
+    <n v="28"/>
+    <x v="11"/>
+    <s v="Flight B - Front 9"/>
+    <n v="2"/>
+    <n v="4.66"/>
+  </r>
+  <r>
+    <s v="2026_03"/>
+    <n v="24"/>
+    <x v="14"/>
+    <s v="Flight B - Long Drive"/>
+    <s v="Winner"/>
+    <n v="28"/>
+  </r>
+  <r>
+    <s v="2026_03"/>
+    <n v="24"/>
+    <x v="14"/>
+    <s v="Flight B - Overall"/>
+    <n v="1"/>
+    <n v="70"/>
+  </r>
+  <r>
+    <s v="2026_03"/>
+    <n v="1"/>
+    <x v="22"/>
+    <s v="Flight B - Overall"/>
+    <n v="2"/>
+    <n v="42"/>
+  </r>
+  <r>
+    <s v="2026_03"/>
+    <n v="26"/>
+    <x v="6"/>
+    <s v="Flight B - Overall"/>
+    <n v="3"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <s v="2026_03"/>
+    <n v="28"/>
+    <x v="11"/>
+    <s v="Flight B - Overall"/>
+    <n v="3"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <s v="2026_03"/>
+    <n v="1"/>
+    <x v="22"/>
+    <s v="Low Putts"/>
+    <s v="Winner"/>
+    <n v="28"/>
+  </r>
+  <r>
+    <s v="2026_04"/>
+    <n v="37"/>
+    <x v="12"/>
+    <s v="Closest to the Pin"/>
+    <s v="Winner"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <s v="2026_04"/>
+    <n v="20"/>
+    <x v="15"/>
+    <s v="Closest to the Pin"/>
+    <s v="Winner"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <s v="2026_04"/>
+    <n v="7"/>
+    <x v="23"/>
+    <s v="Closest to the Pin"/>
+    <s v="Winner"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <s v="2026_04"/>
+    <n v="37"/>
+    <x v="12"/>
+    <s v="Closest to the Pin"/>
+    <s v="Winner"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <s v="2026_04"/>
+    <n v="34"/>
+    <x v="0"/>
+    <s v="Flight A - Back 9"/>
+    <n v="1"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <s v="2026_04"/>
+    <n v="7"/>
+    <x v="23"/>
+    <s v="Flight A - Back 9"/>
+    <n v="2"/>
+    <n v="18"/>
+  </r>
+  <r>
+    <s v="2026_04"/>
+    <n v="29"/>
+    <x v="21"/>
+    <s v="Flight A - Front 9"/>
+    <n v="1"/>
+    <n v="27"/>
+  </r>
+  <r>
+    <s v="2026_04"/>
+    <n v="40"/>
+    <x v="24"/>
+    <s v="Flight A - Front 9"/>
+    <n v="1"/>
+    <n v="27"/>
+  </r>
+  <r>
+    <s v="2026_04"/>
+    <n v="16"/>
+    <x v="25"/>
+    <s v="Flight A - Long Drive"/>
+    <s v="Winner"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <s v="2026_04"/>
+    <n v="29"/>
+    <x v="21"/>
+    <s v="Flight A - Overall"/>
+    <n v="1"/>
+    <n v="90"/>
+  </r>
+  <r>
+    <s v="2026_04"/>
+    <n v="40"/>
+    <x v="24"/>
+    <s v="Flight A - Overall"/>
+    <n v="2"/>
+    <n v="54"/>
+  </r>
+  <r>
+    <s v="2026_04"/>
+    <n v="20"/>
+    <x v="15"/>
+    <s v="Flight A - Overall"/>
+    <n v="3"/>
+    <n v="12"/>
+  </r>
+  <r>
+    <s v="2026_04"/>
+    <n v="7"/>
+    <x v="23"/>
+    <s v="Flight A - Overall"/>
+    <n v="3"/>
+    <n v="12"/>
+  </r>
+  <r>
+    <s v="2026_04"/>
+    <n v="15"/>
+    <x v="26"/>
+    <s v="Flight A - Overall"/>
+    <n v="3"/>
+    <n v="12"/>
+  </r>
+  <r>
+    <s v="2026_04"/>
+    <n v="10"/>
+    <x v="10"/>
+    <s v="Flight B - Back 9"/>
+    <n v="1"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <s v="2026_04"/>
+    <n v="18"/>
+    <x v="27"/>
+    <s v="Flight B - Back 9"/>
+    <n v="2"/>
+    <n v="9"/>
+  </r>
+  <r>
+    <s v="2026_04"/>
+    <n v="30"/>
+    <x v="28"/>
+    <s v="Flight B - Back 9"/>
+    <n v="2"/>
+    <n v="9"/>
+  </r>
+  <r>
+    <s v="2026_04"/>
+    <n v="19"/>
+    <x v="9"/>
+    <s v="Flight B - Front 9"/>
+    <n v="1"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <s v="2026_04"/>
+    <n v="1"/>
+    <x v="22"/>
+    <s v="Flight B - Front 9"/>
+    <n v="2"/>
+    <n v="18"/>
+  </r>
+  <r>
+    <s v="2026_04"/>
+    <n v="28"/>
+    <x v="11"/>
+    <s v="Flight B - Long Drive"/>
+    <s v="Winner"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <s v="2026_04"/>
+    <n v="10"/>
+    <x v="10"/>
+    <s v="Flight B - Overall"/>
+    <n v="1"/>
+    <n v="72"/>
+  </r>
+  <r>
+    <s v="2026_04"/>
+    <n v="19"/>
+    <x v="9"/>
+    <s v="Flight B - Overall"/>
+    <n v="1"/>
+    <n v="72"/>
+  </r>
+  <r>
+    <s v="2026_04"/>
+    <n v="18"/>
+    <x v="27"/>
+    <s v="Flight B - Overall"/>
+    <n v="3"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <s v="2026_04"/>
+    <n v="3"/>
+    <x v="29"/>
+    <s v="Low Putts"/>
+    <s v="Winner"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <s v="2026_05"/>
+    <n v="20"/>
+    <x v="15"/>
+    <s v="Closest to the Pin"/>
+    <s v="Winner"/>
+    <n v="27"/>
+  </r>
+  <r>
+    <s v="2026_05"/>
+    <n v="44"/>
+    <x v="30"/>
+    <s v="Closest to the Pin"/>
+    <s v="Winner"/>
+    <n v="27"/>
+  </r>
+  <r>
+    <s v="2026_05"/>
+    <n v="29"/>
+    <x v="21"/>
+    <s v="Closest to the Pin"/>
+    <s v="Winner"/>
+    <n v="27"/>
+  </r>
+  <r>
+    <s v="2026_05"/>
+    <n v="25"/>
+    <x v="13"/>
+    <s v="Closest to the Pin"/>
+    <s v="Winner"/>
+    <n v="27"/>
+  </r>
+  <r>
+    <s v="2026_05"/>
+    <n v="1"/>
+    <x v="22"/>
+    <s v="Closest to the Pin"/>
+    <s v="Winner"/>
+    <n v="27"/>
+  </r>
+  <r>
+    <s v="2026_05"/>
+    <n v="17"/>
+    <x v="31"/>
+    <s v="Flight A - Back 9"/>
+    <n v="1"/>
+    <n v="28"/>
+  </r>
+  <r>
+    <s v="2026_05"/>
+    <n v="15"/>
+    <x v="26"/>
+    <s v="Flight A - Back 9"/>
+    <n v="2"/>
+    <n v="14"/>
+  </r>
+  <r>
+    <s v="2026_05"/>
+    <n v="41"/>
+    <x v="32"/>
+    <s v="Flight A - Front 9"/>
+    <n v="1"/>
+    <n v="21"/>
+  </r>
+  <r>
+    <s v="2026_05"/>
+    <n v="13"/>
+    <x v="33"/>
+    <s v="Flight A - Front 9"/>
+    <n v="1"/>
+    <n v="21"/>
+  </r>
+  <r>
+    <s v="2026_05"/>
+    <n v="20"/>
+    <x v="15"/>
+    <s v="Flight A - Long Drive"/>
+    <s v="Winner"/>
+    <n v="28"/>
+  </r>
+  <r>
+    <s v="2026_05"/>
+    <n v="41"/>
+    <x v="32"/>
+    <s v="Flight A - Overall"/>
+    <n v="1"/>
+    <n v="70"/>
+  </r>
+  <r>
+    <s v="2026_05"/>
+    <n v="13"/>
+    <x v="33"/>
+    <s v="Flight A - Overall"/>
+    <n v="2"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <s v="2026_05"/>
+    <n v="35"/>
+    <x v="4"/>
+    <s v="Flight A - Overall"/>
+    <n v="2"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <s v="2026_05"/>
+    <n v="14"/>
+    <x v="8"/>
+    <s v="Flight B - Back 9"/>
+    <n v="1"/>
+    <n v="19.5"/>
+  </r>
+  <r>
+    <s v="2026_05"/>
+    <n v="1"/>
+    <x v="22"/>
+    <s v="Flight B - Back 9"/>
+    <n v="1"/>
+    <n v="19.5"/>
+  </r>
+  <r>
+    <s v="2026_05"/>
+    <n v="14"/>
+    <x v="8"/>
+    <s v="Flight B - Front 9"/>
+    <n v="1"/>
+    <n v="26"/>
+  </r>
+  <r>
+    <s v="2026_05"/>
+    <n v="9"/>
+    <x v="7"/>
+    <s v="Flight B - Front 9"/>
+    <n v="2"/>
+    <n v="13"/>
+  </r>
+  <r>
+    <s v="2026_05"/>
+    <n v="19"/>
+    <x v="9"/>
+    <s v="Flight B - Long Drive"/>
+    <s v="Winner"/>
+    <n v="26"/>
+  </r>
+  <r>
+    <s v="2026_05"/>
+    <n v="14"/>
+    <x v="8"/>
+    <s v="Flight B - Overall"/>
+    <n v="1"/>
+    <n v="65"/>
+  </r>
+  <r>
+    <s v="2026_05"/>
+    <n v="10"/>
+    <x v="10"/>
+    <s v="Flight B - Overall"/>
+    <n v="2"/>
+    <n v="39"/>
+  </r>
+  <r>
+    <s v="2026_05"/>
+    <n v="43"/>
+    <x v="34"/>
+    <s v="Flight B - Overall"/>
+    <n v="3"/>
+    <n v="26"/>
+  </r>
+  <r>
+    <s v="2026_05"/>
+    <n v="15"/>
+    <x v="26"/>
+    <s v="Low Putts"/>
+    <s v="Winner"/>
+    <n v="27"/>
+  </r>
+  <r>
+    <s v="2026_06"/>
+    <n v="15"/>
+    <x v="26"/>
+    <s v="Flight A - Overall"/>
+    <n v="1"/>
+    <n v="50"/>
+  </r>
+  <r>
+    <s v="2026_06"/>
+    <n v="34"/>
+    <x v="0"/>
+    <s v="Flight A - Overall"/>
+    <n v="2"/>
+    <n v="25"/>
+  </r>
+  <r>
+    <s v="2026_06"/>
+    <n v="16"/>
+    <x v="25"/>
+    <s v="Flight A - Overall"/>
+    <n v="2"/>
+    <n v="25"/>
+  </r>
+  <r>
+    <s v="2026_06"/>
+    <n v="18"/>
+    <x v="27"/>
+    <s v="Flight B - Overall"/>
+    <n v="1"/>
+    <n v="50"/>
+  </r>
+  <r>
+    <s v="2026_06"/>
+    <n v="10"/>
+    <x v="10"/>
+    <s v="Flight B - Overall"/>
+    <n v="2"/>
+    <n v="30"/>
+  </r>
+  <r>
+    <s v="2026_06"/>
+    <n v="27"/>
+    <x v="20"/>
+    <s v="Flight B - Overall"/>
+    <n v="3"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <s v="2026_06"/>
+    <n v="20"/>
+    <x v="15"/>
+    <s v="Flight A - Front 9"/>
+    <n v="1"/>
+    <n v="10"/>
+  </r>
+  <r>
+    <s v="2026_06"/>
+    <n v="15"/>
+    <x v="26"/>
+    <s v="Flight A - Front 9"/>
+    <n v="1"/>
+    <n v="10"/>
+  </r>
+  <r>
+    <s v="2026_06"/>
+    <n v="34"/>
+    <x v="0"/>
+    <s v="Flight A - Front 9"/>
+    <n v="1"/>
+    <n v="10"/>
+  </r>
+  <r>
+    <s v="2026_06"/>
+    <n v="18"/>
+    <x v="27"/>
+    <s v="Flight B - Front 9"/>
+    <n v="1"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <s v="2026_06"/>
+    <n v="10"/>
+    <x v="10"/>
+    <s v="Flight B - Front 9"/>
+    <n v="2"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <s v="2026_06"/>
+    <n v="2"/>
+    <x v="19"/>
+    <s v="Flight B - Front 9"/>
+    <n v="2"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <s v="2026_06"/>
+    <n v="15"/>
+    <x v="26"/>
+    <s v="Flight A - Back 9"/>
+    <n v="1"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <s v="2026_06"/>
+    <n v="41"/>
+    <x v="32"/>
+    <s v="Flight A - Back 9"/>
+    <n v="1"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <s v="2026_06"/>
+    <n v="18"/>
+    <x v="27"/>
+    <s v="Flight B - Back 9"/>
+    <n v="1"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <s v="2026_06"/>
+    <n v="27"/>
+    <x v="20"/>
+    <s v="Flight B - Back 9"/>
+    <n v="2"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <s v="2026_06"/>
+    <n v="10"/>
+    <x v="10"/>
+    <s v="Flight B - Back 9"/>
+    <n v="2"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <s v="2026_06"/>
+    <n v="41"/>
+    <x v="32"/>
+    <s v="Low Putts"/>
+    <s v="Winner"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <s v="2026_06"/>
+    <n v="21"/>
+    <x v="35"/>
+    <s v="Low Putts"/>
+    <s v="Winner"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <s v="2026_06"/>
+    <n v="47"/>
+    <x v="36"/>
+    <s v="Flight A - Long Drive"/>
+    <s v="Winner"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <s v="2026_06"/>
+    <n v="35"/>
+    <x v="4"/>
+    <s v="Flight B - Long Drive"/>
+    <s v="Winner"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <s v="2026_06"/>
+    <n v="44"/>
+    <x v="30"/>
+    <s v="Closest to the Pin"/>
+    <s v="Winner"/>
+    <n v="25"/>
+  </r>
+  <r>
+    <s v="2026_06"/>
+    <n v="44"/>
+    <x v="30"/>
+    <s v="Closest to the Pin"/>
+    <s v="Winner"/>
+    <n v="25"/>
+  </r>
+  <r>
+    <s v="2026_06"/>
+    <n v="41"/>
+    <x v="32"/>
+    <s v="Closest to the Pin"/>
+    <s v="Winner"/>
+    <n v="25"/>
+  </r>
+  <r>
+    <s v="2026_06"/>
+    <n v="20"/>
+    <x v="15"/>
+    <s v="Closest to the Pin"/>
+    <s v="Winner"/>
+    <n v="25"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6B84E77E-8640-4E4C-884A-D557847C822A}" name="PivotTable1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{16E07778-B581-1B4F-B1D0-2729780D865C}" name="PivotTable2" cacheId="42" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B41" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="6">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="38">
+        <item x="19"/>
+        <item x="29"/>
+        <item x="22"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="23"/>
+        <item x="18"/>
+        <item x="7"/>
+        <item x="10"/>
+        <item x="3"/>
+        <item x="33"/>
+        <item x="8"/>
+        <item x="34"/>
+        <item x="26"/>
+        <item x="25"/>
+        <item x="31"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="9"/>
+        <item x="15"/>
+        <item x="24"/>
+        <item x="35"/>
+        <item x="32"/>
+        <item x="2"/>
+        <item x="30"/>
+        <item x="14"/>
+        <item x="13"/>
+        <item x="6"/>
+        <item x="20"/>
+        <item x="11"/>
+        <item x="21"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="36"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="38">
+    <i>
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="34"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="36"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6B84E77E-8640-4E4C-884A-D557847C822A}" name="PivotTable1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="12">
     <pivotField axis="axisRow" showAll="0">
@@ -4082,7 +5529,7 @@
       <c r="A48" s="5">
         <v>47</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B48" s="24" t="s">
         <v>128</v>
       </c>
       <c r="C48" s="5" t="s">
@@ -4354,9 +5801,10 @@
     <col min="5" max="6" width="10.83203125" style="1" customWidth="1"/>
     <col min="7" max="10" width="10.83203125" style="1"/>
     <col min="12" max="12" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4393,8 +5841,11 @@
       <c r="L1" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M1" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="20" t="s">
         <v>66</v>
       </c>
@@ -4427,8 +5878,12 @@
       </c>
       <c r="K2" s="7"/>
       <c r="L2" s="7"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M2" t="str">
+        <f>_xlfn.XLOOKUP(C2,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="20" t="s">
         <v>66</v>
       </c>
@@ -4461,8 +5916,12 @@
       </c>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M3" t="str">
+        <f>_xlfn.XLOOKUP(C3,Players!B:B,Players!D:D)</f>
+        <v>White Rice</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>66</v>
       </c>
@@ -4495,8 +5954,12 @@
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M4" t="str">
+        <f>_xlfn.XLOOKUP(C4,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="20" t="s">
         <v>66</v>
       </c>
@@ -4529,8 +5992,12 @@
       </c>
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M5" t="str">
+        <f>_xlfn.XLOOKUP(C5,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="20" t="s">
         <v>66</v>
       </c>
@@ -4563,8 +6030,12 @@
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M6" t="str">
+        <f>_xlfn.XLOOKUP(C6,Players!B:B,Players!D:D)</f>
+        <v>White Rice</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="20" t="s">
         <v>66</v>
       </c>
@@ -4597,8 +6068,12 @@
       </c>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" t="str">
+        <f>_xlfn.XLOOKUP(C7,Players!B:B,Players!D:D)</f>
+        <v>White Rice</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="20" t="s">
         <v>66</v>
       </c>
@@ -4631,8 +6106,12 @@
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" t="str">
+        <f>_xlfn.XLOOKUP(C8,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="20" t="s">
         <v>66</v>
       </c>
@@ -4665,8 +6144,12 @@
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" t="str">
+        <f>_xlfn.XLOOKUP(C9,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="20" t="s">
         <v>66</v>
       </c>
@@ -4699,8 +6182,12 @@
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" t="str">
+        <f>_xlfn.XLOOKUP(C10,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="20" t="s">
         <v>66</v>
       </c>
@@ -4733,8 +6220,12 @@
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" t="str">
+        <f>_xlfn.XLOOKUP(C11,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="20" t="s">
         <v>66</v>
       </c>
@@ -4767,8 +6258,12 @@
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" t="str">
+        <f>_xlfn.XLOOKUP(C12,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="20" t="s">
         <v>66</v>
       </c>
@@ -4801,8 +6296,12 @@
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" t="str">
+        <f>_xlfn.XLOOKUP(C13,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="20" t="s">
         <v>66</v>
       </c>
@@ -4835,8 +6334,12 @@
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" t="str">
+        <f>_xlfn.XLOOKUP(C14,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="20" t="s">
         <v>66</v>
       </c>
@@ -4869,8 +6372,12 @@
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" t="str">
+        <f>_xlfn.XLOOKUP(C15,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="20" t="s">
         <v>66</v>
       </c>
@@ -4903,8 +6410,12 @@
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M16" t="str">
+        <f>_xlfn.XLOOKUP(C16,Players!B:B,Players!D:D)</f>
+        <v>White Rice</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="20" t="s">
         <v>66</v>
       </c>
@@ -4937,8 +6448,12 @@
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M17" t="str">
+        <f>_xlfn.XLOOKUP(C17,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="20" t="s">
         <v>66</v>
       </c>
@@ -4971,8 +6486,12 @@
       </c>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M18" t="str">
+        <f>_xlfn.XLOOKUP(C18,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="20" t="s">
         <v>66</v>
       </c>
@@ -5005,8 +6524,12 @@
       </c>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M19" t="str">
+        <f>_xlfn.XLOOKUP(C19,Players!B:B,Players!D:D)</f>
+        <v>White Rice</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="20" t="s">
         <v>66</v>
       </c>
@@ -5039,8 +6562,12 @@
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M20" t="str">
+        <f>_xlfn.XLOOKUP(C20,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="20" t="s">
         <v>66</v>
       </c>
@@ -5073,8 +6600,12 @@
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M21" t="str">
+        <f>_xlfn.XLOOKUP(C21,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="20" t="s">
         <v>66</v>
       </c>
@@ -5107,8 +6638,12 @@
       </c>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M22" t="str">
+        <f>_xlfn.XLOOKUP(C22,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="20" t="s">
         <v>66</v>
       </c>
@@ -5141,8 +6676,12 @@
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M23" t="str">
+        <f>_xlfn.XLOOKUP(C23,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="20" t="s">
         <v>66</v>
       </c>
@@ -5175,8 +6714,12 @@
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M24" t="str">
+        <f>_xlfn.XLOOKUP(C24,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="20" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +6752,12 @@
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M25" t="str">
+        <f>_xlfn.XLOOKUP(C25,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="20" t="s">
         <v>66</v>
       </c>
@@ -5243,8 +6790,12 @@
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M26" t="str">
+        <f>_xlfn.XLOOKUP(C26,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="20" t="s">
         <v>66</v>
       </c>
@@ -5277,8 +6828,12 @@
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M27" t="str">
+        <f>_xlfn.XLOOKUP(C27,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="20" t="s">
         <v>66</v>
       </c>
@@ -5311,8 +6866,12 @@
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M28" t="str">
+        <f>_xlfn.XLOOKUP(C28,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="20" t="s">
         <v>66</v>
       </c>
@@ -5345,8 +6904,12 @@
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M29" t="str">
+        <f>_xlfn.XLOOKUP(C29,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="20" t="s">
         <v>66</v>
       </c>
@@ -5379,8 +6942,12 @@
       </c>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M30" t="str">
+        <f>_xlfn.XLOOKUP(C30,Players!B:B,Players!D:D)</f>
+        <v>White Rice</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="20" t="s">
         <v>66</v>
       </c>
@@ -5413,8 +6980,12 @@
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M31" t="str">
+        <f>_xlfn.XLOOKUP(C31,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" s="20" t="s">
         <v>66</v>
       </c>
@@ -5447,8 +7018,12 @@
       </c>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M32" t="str">
+        <f>_xlfn.XLOOKUP(C32,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="20" t="s">
         <v>66</v>
       </c>
@@ -5481,8 +7056,12 @@
       </c>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M33" t="str">
+        <f>_xlfn.XLOOKUP(C33,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="20" t="s">
         <v>66</v>
       </c>
@@ -5515,8 +7094,12 @@
       </c>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M34" t="str">
+        <f>_xlfn.XLOOKUP(C34,Players!B:B,Players!D:D)</f>
+        <v>White Rice</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" s="20" t="s">
         <v>66</v>
       </c>
@@ -5549,8 +7132,12 @@
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M35" t="str">
+        <f>_xlfn.XLOOKUP(C35,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="20" t="s">
         <v>66</v>
       </c>
@@ -5583,8 +7170,12 @@
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M36" t="str">
+        <f>_xlfn.XLOOKUP(C36,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="20" t="s">
         <v>66</v>
       </c>
@@ -5617,8 +7208,12 @@
       </c>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M37" t="str">
+        <f>_xlfn.XLOOKUP(C37,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" s="20" t="s">
         <v>68</v>
       </c>
@@ -5655,8 +7250,12 @@
       <c r="L38" s="20">
         <v>12</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M38" t="str">
+        <f>_xlfn.XLOOKUP(C38,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" s="20" t="s">
         <v>68</v>
       </c>
@@ -5689,8 +7288,12 @@
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M39" t="str">
+        <f>_xlfn.XLOOKUP(C39,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" s="20" t="s">
         <v>68</v>
       </c>
@@ -5723,8 +7326,12 @@
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M40" t="str">
+        <f>_xlfn.XLOOKUP(C40,Players!B:B,Players!D:D)</f>
+        <v>White Rice</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" s="20" t="s">
         <v>68</v>
       </c>
@@ -5757,8 +7364,12 @@
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M41" t="str">
+        <f>_xlfn.XLOOKUP(C41,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" s="20" t="s">
         <v>68</v>
       </c>
@@ -5795,8 +7406,12 @@
       <c r="L42" s="20">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M42" t="str">
+        <f>_xlfn.XLOOKUP(C42,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" s="20" t="s">
         <v>68</v>
       </c>
@@ -5829,8 +7444,12 @@
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M43" t="str">
+        <f>_xlfn.XLOOKUP(C43,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" s="20" t="s">
         <v>68</v>
       </c>
@@ -5863,8 +7482,12 @@
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M44" t="str">
+        <f>_xlfn.XLOOKUP(C44,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" s="20" t="s">
         <v>68</v>
       </c>
@@ -5897,8 +7520,12 @@
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M45" t="str">
+        <f>_xlfn.XLOOKUP(C45,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" s="20" t="s">
         <v>68</v>
       </c>
@@ -5935,8 +7562,12 @@
       <c r="L46" s="20">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M46" t="str">
+        <f>_xlfn.XLOOKUP(C46,Players!B:B,Players!D:D)</f>
+        <v>White Rice</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" s="20" t="s">
         <v>68</v>
       </c>
@@ -5969,8 +7600,12 @@
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M47" t="str">
+        <f>_xlfn.XLOOKUP(C47,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" s="20" t="s">
         <v>68</v>
       </c>
@@ -6006,6 +7641,10 @@
       </c>
       <c r="L48" s="20">
         <v>2</v>
+      </c>
+      <c r="M48" t="str">
+        <f>_xlfn.XLOOKUP(C48,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
@@ -6041,6 +7680,10 @@
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
+      <c r="M49" t="str">
+        <f>_xlfn.XLOOKUP(C49,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50" s="20" t="s">
@@ -6075,6 +7718,10 @@
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
+      <c r="M50" t="str">
+        <f>_xlfn.XLOOKUP(C50,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51" s="20" t="s">
@@ -6109,6 +7756,10 @@
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
+      <c r="M51" t="str">
+        <f>_xlfn.XLOOKUP(C51,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52" s="20" t="s">
@@ -6147,6 +7798,10 @@
       <c r="L52" s="20">
         <v>10</v>
       </c>
+      <c r="M52" t="str">
+        <f>_xlfn.XLOOKUP(C52,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53" s="20" t="s">
@@ -6181,6 +7836,10 @@
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
+      <c r="M53" t="str">
+        <f>_xlfn.XLOOKUP(C53,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54" s="20" t="s">
@@ -6219,6 +7878,10 @@
       <c r="L54" s="20">
         <v>7.5</v>
       </c>
+      <c r="M54" t="str">
+        <f>_xlfn.XLOOKUP(C54,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55" s="20" t="s">
@@ -6253,6 +7916,10 @@
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
+      <c r="M55" t="str">
+        <f>_xlfn.XLOOKUP(C55,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" s="20" t="s">
@@ -6291,6 +7958,10 @@
       <c r="L56" s="20">
         <v>5.5</v>
       </c>
+      <c r="M56" t="str">
+        <f>_xlfn.XLOOKUP(C56,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57" s="20" t="s">
@@ -6325,6 +7996,10 @@
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
+      <c r="M57" t="str">
+        <f>_xlfn.XLOOKUP(C57,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58" s="20" t="s">
@@ -6359,6 +8034,10 @@
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
+      <c r="M58" t="str">
+        <f>_xlfn.XLOOKUP(C58,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59" s="20" t="s">
@@ -6393,6 +8072,10 @@
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
+      <c r="M59" t="str">
+        <f>_xlfn.XLOOKUP(C59,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60" s="20" t="s">
@@ -6431,6 +8114,10 @@
       <c r="L60" s="20">
         <v>2</v>
       </c>
+      <c r="M60" t="str">
+        <f>_xlfn.XLOOKUP(C60,Players!B:B,Players!D:D)</f>
+        <v>White Rice</v>
+      </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61" s="20" t="s">
@@ -6465,6 +8152,10 @@
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
+      <c r="M61" t="str">
+        <f>_xlfn.XLOOKUP(C61,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62" s="20" t="s">
@@ -6499,7 +8190,10 @@
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
-      <c r="M62" s="1"/>
+      <c r="M62" t="str">
+        <f>_xlfn.XLOOKUP(C62,Players!B:B,Players!D:D)</f>
+        <v>White Rice</v>
+      </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63" s="20" t="s">
@@ -6538,7 +8232,10 @@
       <c r="L63" s="20">
         <v>13.5</v>
       </c>
-      <c r="M63" s="1"/>
+      <c r="M63" t="str">
+        <f>_xlfn.XLOOKUP(C63,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64" s="20" t="s">
@@ -6573,7 +8270,10 @@
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
-      <c r="M64" s="1"/>
+      <c r="M64" t="str">
+        <f>_xlfn.XLOOKUP(C64,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65" s="20" t="s">
@@ -6612,7 +8312,10 @@
       <c r="L65" s="21">
         <v>11</v>
       </c>
-      <c r="M65" s="1"/>
+      <c r="M65" t="str">
+        <f>_xlfn.XLOOKUP(C65,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66" s="20" t="s">
@@ -6651,7 +8354,10 @@
       <c r="L66" s="21">
         <v>10</v>
       </c>
-      <c r="M66" s="1"/>
+      <c r="M66" t="str">
+        <f>_xlfn.XLOOKUP(C66,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67" s="20" t="s">
@@ -6686,7 +8392,10 @@
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
-      <c r="M67" s="1"/>
+      <c r="M67" t="str">
+        <f>_xlfn.XLOOKUP(C67,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68" s="20" t="s">
@@ -6721,7 +8430,10 @@
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
-      <c r="M68" s="1"/>
+      <c r="M68" t="str">
+        <f>_xlfn.XLOOKUP(C68,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A69" s="20" t="s">
@@ -6756,7 +8468,10 @@
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
-      <c r="M69" s="1"/>
+      <c r="M69" t="str">
+        <f>_xlfn.XLOOKUP(C69,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A70" s="20" t="s">
@@ -6791,7 +8506,10 @@
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
-      <c r="M70" s="1"/>
+      <c r="M70" t="str">
+        <f>_xlfn.XLOOKUP(C70,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A71" s="20" t="s">
@@ -6826,7 +8544,10 @@
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
-      <c r="M71" s="1"/>
+      <c r="M71" t="str">
+        <f>_xlfn.XLOOKUP(C71,Players!B:B,Players!D:D)</f>
+        <v>White Rice</v>
+      </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72" s="20" t="s">
@@ -6861,7 +8582,10 @@
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
-      <c r="M72" s="1"/>
+      <c r="M72" t="str">
+        <f>_xlfn.XLOOKUP(C72,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73" s="20" t="s">
@@ -6900,7 +8624,10 @@
       <c r="L73" s="21">
         <v>3</v>
       </c>
-      <c r="M73" s="1"/>
+      <c r="M73" t="str">
+        <f>_xlfn.XLOOKUP(C73,Players!B:B,Players!D:D)</f>
+        <v>White Rice</v>
+      </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A74" s="20" t="s">
@@ -6939,7 +8666,10 @@
       <c r="L74" s="21">
         <v>2</v>
       </c>
-      <c r="M74" s="1"/>
+      <c r="M74" t="str">
+        <f>_xlfn.XLOOKUP(C74,Players!B:B,Players!D:D)</f>
+        <v>White Rice</v>
+      </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A75" s="20" t="s">
@@ -6974,6 +8704,10 @@
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
+      <c r="M75" t="str">
+        <f>_xlfn.XLOOKUP(C75,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A76" s="20" t="s">
@@ -7008,6 +8742,10 @@
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
+      <c r="M76" t="str">
+        <f>_xlfn.XLOOKUP(C76,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A77" s="20" t="s">
@@ -7042,6 +8780,10 @@
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
+      <c r="M77" t="str">
+        <f>_xlfn.XLOOKUP(C77,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A78" s="20" t="s">
@@ -7080,6 +8822,10 @@
       <c r="L78" s="21">
         <v>11.5</v>
       </c>
+      <c r="M78" t="str">
+        <f>_xlfn.XLOOKUP(C78,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79" s="20" t="s">
@@ -7114,6 +8860,10 @@
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
+      <c r="M79" t="str">
+        <f>_xlfn.XLOOKUP(C79,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80" s="20" t="s">
@@ -7152,8 +8902,12 @@
       <c r="L80" s="21">
         <v>10</v>
       </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M80" t="str">
+        <f>_xlfn.XLOOKUP(C80,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81" s="20" t="s">
         <v>71</v>
       </c>
@@ -7186,8 +8940,12 @@
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M81" t="str">
+        <f>_xlfn.XLOOKUP(C81,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A82" s="20" t="s">
         <v>71</v>
       </c>
@@ -7220,8 +8978,12 @@
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M82" t="str">
+        <f>_xlfn.XLOOKUP(C82,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83" s="20" t="s">
         <v>71</v>
       </c>
@@ -7254,8 +9016,12 @@
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M83" t="str">
+        <f>_xlfn.XLOOKUP(C83,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84" s="20" t="s">
         <v>71</v>
       </c>
@@ -7292,8 +9058,12 @@
       <c r="L84" s="21">
         <v>5.5</v>
       </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M84" t="str">
+        <f>_xlfn.XLOOKUP(C84,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85" s="20" t="s">
         <v>71</v>
       </c>
@@ -7326,8 +9096,12 @@
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M85" t="str">
+        <f>_xlfn.XLOOKUP(C85,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86" s="20" t="s">
         <v>71</v>
       </c>
@@ -7360,8 +9134,12 @@
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M86" t="str">
+        <f>_xlfn.XLOOKUP(C86,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87" s="20" t="s">
         <v>71</v>
       </c>
@@ -7394,8 +9172,12 @@
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M87" t="str">
+        <f>_xlfn.XLOOKUP(C87,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88" s="20" t="s">
         <v>71</v>
       </c>
@@ -7428,8 +9210,12 @@
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M88" t="str">
+        <f>_xlfn.XLOOKUP(C88,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89" s="20" t="s">
         <v>71</v>
       </c>
@@ -7462,8 +9248,12 @@
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M89" t="str">
+        <f>_xlfn.XLOOKUP(C89,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90" s="20" t="s">
         <v>74</v>
       </c>
@@ -7500,8 +9290,12 @@
       <c r="L90" s="20">
         <v>18</v>
       </c>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M90" t="str">
+        <f>_xlfn.XLOOKUP(C90,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91" s="20" t="s">
         <v>74</v>
       </c>
@@ -7534,8 +9328,12 @@
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M91" t="str">
+        <f>_xlfn.XLOOKUP(C91,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A92" s="20" t="s">
         <v>74</v>
       </c>
@@ -7568,8 +9366,12 @@
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M92" t="str">
+        <f>_xlfn.XLOOKUP(C92,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93" s="20" t="s">
         <v>74</v>
       </c>
@@ -7606,8 +9408,12 @@
       <c r="L93" s="20">
         <v>15</v>
       </c>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M93" t="str">
+        <f>_xlfn.XLOOKUP(C93,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94" s="20" t="s">
         <v>74</v>
       </c>
@@ -7640,8 +9446,12 @@
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M94" t="str">
+        <f>_xlfn.XLOOKUP(C94,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95" s="20" t="s">
         <v>74</v>
       </c>
@@ -7674,8 +9484,12 @@
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M95" t="str">
+        <f>_xlfn.XLOOKUP(C95,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A96" s="20" t="s">
         <v>74</v>
       </c>
@@ -7708,8 +9522,12 @@
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M96" t="str">
+        <f>_xlfn.XLOOKUP(C96,Players!B:B,Players!D:D)</f>
+        <v>White Rice</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97" s="20" t="s">
         <v>74</v>
       </c>
@@ -7746,8 +9564,12 @@
       <c r="L97" s="20">
         <v>11</v>
       </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M97" t="str">
+        <f>_xlfn.XLOOKUP(C97,Players!B:B,Players!D:D)</f>
+        <v>White Rice</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A98" s="20" t="s">
         <v>74</v>
       </c>
@@ -7780,8 +9602,12 @@
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M98" t="str">
+        <f>_xlfn.XLOOKUP(C98,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A99" s="20" t="s">
         <v>74</v>
       </c>
@@ -7818,8 +9644,12 @@
       <c r="L99" s="20">
         <v>9</v>
       </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M99" t="str">
+        <f>_xlfn.XLOOKUP(C99,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A100" s="20" t="s">
         <v>74</v>
       </c>
@@ -7856,8 +9686,12 @@
       <c r="L100" s="20">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M100" t="str">
+        <f>_xlfn.XLOOKUP(C100,Players!B:B,Players!D:D)</f>
+        <v>White Rice</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" s="20" t="s">
         <v>74</v>
       </c>
@@ -7890,8 +9724,12 @@
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M101" t="str">
+        <f>_xlfn.XLOOKUP(C101,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102" s="20" t="s">
         <v>74</v>
       </c>
@@ -7924,8 +9762,12 @@
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M102" t="str">
+        <f>_xlfn.XLOOKUP(C102,Players!B:B,Players!D:D)</f>
+        <v>White Rice</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103" s="20" t="s">
         <v>74</v>
       </c>
@@ -7958,8 +9800,12 @@
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M103" t="str">
+        <f>_xlfn.XLOOKUP(C103,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A104" s="20" t="s">
         <v>74</v>
       </c>
@@ -7992,8 +9838,12 @@
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M104" t="str">
+        <f>_xlfn.XLOOKUP(C104,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A105" s="20" t="s">
         <v>74</v>
       </c>
@@ -8026,8 +9876,12 @@
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M105" t="str">
+        <f>_xlfn.XLOOKUP(C105,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A106" s="20" t="s">
         <v>74</v>
       </c>
@@ -8060,8 +9914,12 @@
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M106" t="str">
+        <f>_xlfn.XLOOKUP(C106,Players!B:B,Players!D:D)</f>
+        <v>White Rice</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107" s="20" t="s">
         <v>74</v>
       </c>
@@ -8094,8 +9952,12 @@
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M107" t="str">
+        <f>_xlfn.XLOOKUP(C107,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108" s="20" t="s">
         <v>74</v>
       </c>
@@ -8128,8 +9990,12 @@
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M108" t="str">
+        <f>_xlfn.XLOOKUP(C108,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A109" s="20" t="s">
         <v>74</v>
       </c>
@@ -8166,8 +10032,12 @@
       <c r="L109" s="20">
         <v>17.5</v>
       </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M109" t="str">
+        <f>_xlfn.XLOOKUP(C109,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A110" s="20" t="s">
         <v>74</v>
       </c>
@@ -8200,8 +10070,12 @@
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M110" t="str">
+        <f>_xlfn.XLOOKUP(C110,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A111" s="20" t="s">
         <v>74</v>
       </c>
@@ -8234,8 +10108,12 @@
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M111" t="str">
+        <f>_xlfn.XLOOKUP(C111,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A112" s="20" t="s">
         <v>74</v>
       </c>
@@ -8268,8 +10146,12 @@
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M112" t="str">
+        <f>_xlfn.XLOOKUP(C112,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A113" s="20" t="s">
         <v>74</v>
       </c>
@@ -8302,8 +10184,12 @@
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
-    </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M113" t="str">
+        <f>_xlfn.XLOOKUP(C113,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A114" s="20" t="s">
         <v>74</v>
       </c>
@@ -8336,8 +10222,12 @@
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M114" t="str">
+        <f>_xlfn.XLOOKUP(C114,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A115" s="20" t="s">
         <v>74</v>
       </c>
@@ -8370,8 +10260,12 @@
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M115" t="str">
+        <f>_xlfn.XLOOKUP(C115,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A116" s="20" t="s">
         <v>74</v>
       </c>
@@ -8404,8 +10298,12 @@
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M116" t="str">
+        <f>_xlfn.XLOOKUP(C116,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A117" s="20" t="s">
         <v>74</v>
       </c>
@@ -8442,8 +10340,12 @@
       <c r="L117" s="20">
         <v>8.5</v>
       </c>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M117" t="str">
+        <f>_xlfn.XLOOKUP(C117,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118" s="20" t="s">
         <v>74</v>
       </c>
@@ -8476,8 +10378,12 @@
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M118" t="str">
+        <f>_xlfn.XLOOKUP(C118,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A119" s="20" t="s">
         <v>74</v>
       </c>
@@ -8510,8 +10416,12 @@
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M119" t="str">
+        <f>_xlfn.XLOOKUP(C119,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A120" s="20" t="s">
         <v>74</v>
       </c>
@@ -8544,8 +10454,12 @@
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M120" t="str">
+        <f>_xlfn.XLOOKUP(C120,Players!B:B,Players!D:D)</f>
+        <v>White Rice</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A121" s="20" t="s">
         <v>74</v>
       </c>
@@ -8578,8 +10492,12 @@
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M121" t="str">
+        <f>_xlfn.XLOOKUP(C121,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A122" s="20" t="s">
         <v>74</v>
       </c>
@@ -8612,8 +10530,12 @@
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M122" t="str">
+        <f>_xlfn.XLOOKUP(C122,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A123" s="20" t="s">
         <v>74</v>
       </c>
@@ -8650,8 +10572,12 @@
       <c r="L123" s="20">
         <v>3</v>
       </c>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M123" t="str">
+        <f>_xlfn.XLOOKUP(C123,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A124" s="20" t="s">
         <v>74</v>
       </c>
@@ -8684,8 +10610,12 @@
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M124" t="str">
+        <f>_xlfn.XLOOKUP(C124,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A125" s="20" t="s">
         <v>74</v>
       </c>
@@ -8718,8 +10648,12 @@
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M125" t="str">
+        <f>_xlfn.XLOOKUP(C125,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A126" s="20" t="s">
         <v>10</v>
       </c>
@@ -8752,8 +10686,12 @@
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M126" t="str">
+        <f>_xlfn.XLOOKUP(C126,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A127" s="20" t="s">
         <v>10</v>
       </c>
@@ -8786,8 +10724,12 @@
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M127" t="str">
+        <f>_xlfn.XLOOKUP(C127,Players!B:B,Players!D:D)</f>
+        <v>White Rice</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A128" s="20" t="s">
         <v>10</v>
       </c>
@@ -8820,8 +10762,12 @@
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
-    </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M128" t="str">
+        <f>_xlfn.XLOOKUP(C128,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A129" s="20" t="s">
         <v>10</v>
       </c>
@@ -8854,8 +10800,12 @@
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
-    </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M129" t="str">
+        <f>_xlfn.XLOOKUP(C129,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A130" s="20" t="s">
         <v>10</v>
       </c>
@@ -8888,8 +10838,12 @@
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M130" t="str">
+        <f>_xlfn.XLOOKUP(C130,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A131" s="20" t="s">
         <v>10</v>
       </c>
@@ -8922,8 +10876,12 @@
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M131" t="str">
+        <f>_xlfn.XLOOKUP(C131,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A132" s="20" t="s">
         <v>10</v>
       </c>
@@ -8960,8 +10918,12 @@
       <c r="L132" s="20">
         <v>8</v>
       </c>
-    </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M132" t="str">
+        <f>_xlfn.XLOOKUP(C132,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A133" s="20" t="s">
         <v>10</v>
       </c>
@@ -8998,8 +10960,12 @@
       <c r="L133" s="20">
         <v>6.5</v>
       </c>
-    </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M133" t="str">
+        <f>_xlfn.XLOOKUP(C133,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A134" s="20" t="s">
         <v>10</v>
       </c>
@@ -9032,8 +10998,12 @@
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M134" t="str">
+        <f>_xlfn.XLOOKUP(C134,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A135" s="20" t="s">
         <v>10</v>
       </c>
@@ -9070,8 +11040,12 @@
       <c r="L135" s="20">
         <v>5</v>
       </c>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M135" t="str">
+        <f>_xlfn.XLOOKUP(C135,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A136" s="20" t="s">
         <v>10</v>
       </c>
@@ -9104,8 +11078,12 @@
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M136" t="str">
+        <f>_xlfn.XLOOKUP(C136,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A137" s="20" t="s">
         <v>10</v>
       </c>
@@ -9138,8 +11116,12 @@
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M137" t="str">
+        <f>_xlfn.XLOOKUP(C137,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A138" s="20" t="s">
         <v>10</v>
       </c>
@@ -9172,8 +11154,12 @@
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
-    </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M138" t="str">
+        <f>_xlfn.XLOOKUP(C138,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A139" s="20" t="s">
         <v>10</v>
       </c>
@@ -9210,8 +11196,12 @@
       <c r="L139" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M139" t="str">
+        <f>_xlfn.XLOOKUP(C139,Players!B:B,Players!D:D)</f>
+        <v>White Rice</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A140" s="20" t="s">
         <v>10</v>
       </c>
@@ -9244,8 +11234,12 @@
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M140" t="str">
+        <f>_xlfn.XLOOKUP(C140,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A141" s="20" t="s">
         <v>10</v>
       </c>
@@ -9278,8 +11272,12 @@
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
-    </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M141" t="str">
+        <f>_xlfn.XLOOKUP(C141,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A142" s="20" t="s">
         <v>10</v>
       </c>
@@ -9312,8 +11310,12 @@
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
-    </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M142" t="str">
+        <f>_xlfn.XLOOKUP(C142,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A143" s="20" t="s">
         <v>10</v>
       </c>
@@ -9350,8 +11352,12 @@
       <c r="L143" s="20">
         <v>9</v>
       </c>
-    </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M143" t="str">
+        <f>_xlfn.XLOOKUP(C143,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A144" s="20" t="s">
         <v>10</v>
       </c>
@@ -9384,8 +11390,12 @@
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
-    </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M144" t="str">
+        <f>_xlfn.XLOOKUP(C144,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A145" s="20" t="s">
         <v>10</v>
       </c>
@@ -9422,8 +11432,12 @@
       <c r="L145" s="20">
         <v>9</v>
       </c>
-    </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M145" t="str">
+        <f>_xlfn.XLOOKUP(C145,Players!B:B,Players!D:D)</f>
+        <v>White Rice</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A146" s="20" t="s">
         <v>10</v>
       </c>
@@ -9460,8 +11474,12 @@
       <c r="L146" s="20">
         <v>7</v>
       </c>
-    </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M146" t="str">
+        <f>_xlfn.XLOOKUP(C146,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A147" s="20" t="s">
         <v>10</v>
       </c>
@@ -9494,8 +11512,12 @@
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M147" t="str">
+        <f>_xlfn.XLOOKUP(C147,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A148" s="20" t="s">
         <v>10</v>
       </c>
@@ -9532,8 +11554,12 @@
       <c r="L148" s="20">
         <v>5</v>
       </c>
-    </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M148" t="str">
+        <f>_xlfn.XLOOKUP(C148,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A149" s="20" t="s">
         <v>10</v>
       </c>
@@ -9566,8 +11592,12 @@
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M149" t="str">
+        <f>_xlfn.XLOOKUP(C149,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A150" s="20" t="s">
         <v>10</v>
       </c>
@@ -9600,8 +11630,12 @@
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
-    </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M150" t="str">
+        <f>_xlfn.XLOOKUP(C150,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A151" s="20" t="s">
         <v>10</v>
       </c>
@@ -9634,8 +11668,12 @@
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M151" t="str">
+        <f>_xlfn.XLOOKUP(C151,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A152" s="20" t="s">
         <v>10</v>
       </c>
@@ -9668,8 +11706,12 @@
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
-    </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M152" t="str">
+        <f>_xlfn.XLOOKUP(C152,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A153" s="20" t="s">
         <v>102</v>
       </c>
@@ -9706,8 +11748,12 @@
       <c r="L153" s="20">
         <v>10</v>
       </c>
-    </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M153" t="str">
+        <f>_xlfn.XLOOKUP(C153,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A154" s="20" t="s">
         <v>102</v>
       </c>
@@ -9744,8 +11790,12 @@
       <c r="L154" s="20">
         <v>8.5</v>
       </c>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M154" t="str">
+        <f>_xlfn.XLOOKUP(C154,Players!B:B,Players!D:D)</f>
+        <v>White Rice</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A155" s="20" t="s">
         <v>102</v>
       </c>
@@ -9782,8 +11832,12 @@
       <c r="L155" s="20">
         <v>8.5</v>
       </c>
-    </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M155" t="str">
+        <f>_xlfn.XLOOKUP(C155,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A156" s="20" t="s">
         <v>102</v>
       </c>
@@ -9820,8 +11874,12 @@
       <c r="L156" s="20">
         <v>6.5</v>
       </c>
-    </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M156" t="str">
+        <f>_xlfn.XLOOKUP(C156,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A157" s="20" t="s">
         <v>102</v>
       </c>
@@ -9854,8 +11912,12 @@
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
-    </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M157" t="str">
+        <f>_xlfn.XLOOKUP(C157,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A158" s="20" t="s">
         <v>102</v>
       </c>
@@ -9888,8 +11950,12 @@
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
-    </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M158" t="str">
+        <f>_xlfn.XLOOKUP(C158,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A159" s="20" t="s">
         <v>102</v>
       </c>
@@ -9926,8 +11992,12 @@
       <c r="L159" s="20">
         <v>4</v>
       </c>
-    </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M159" t="str">
+        <f>_xlfn.XLOOKUP(C159,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A160" s="20" t="s">
         <v>102</v>
       </c>
@@ -9964,8 +12034,12 @@
       <c r="L160" s="20">
         <v>3</v>
       </c>
-    </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M160" t="str">
+        <f>_xlfn.XLOOKUP(C160,Players!B:B,Players!D:D)</f>
+        <v>The Money Team</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A161" s="20" t="s">
         <v>102</v>
       </c>
@@ -9998,8 +12072,12 @@
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
-    </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M161" t="str">
+        <f>_xlfn.XLOOKUP(C161,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A162" s="20" t="s">
         <v>102</v>
       </c>
@@ -10032,8 +12110,12 @@
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
-    </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M162" t="str">
+        <f>_xlfn.XLOOKUP(C162,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A163" s="20" t="s">
         <v>102</v>
       </c>
@@ -10066,8 +12148,12 @@
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
-    </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M163" t="str">
+        <f>_xlfn.XLOOKUP(C163,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A164" s="20" t="s">
         <v>102</v>
       </c>
@@ -10100,8 +12186,12 @@
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M164" t="str">
+        <f>_xlfn.XLOOKUP(C164,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A165" s="20" t="s">
         <v>102</v>
       </c>
@@ -10138,8 +12228,12 @@
       <c r="L165" s="20">
         <v>8</v>
       </c>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M165" t="str">
+        <f>_xlfn.XLOOKUP(C165,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A166" s="20" t="s">
         <v>102</v>
       </c>
@@ -10172,8 +12266,12 @@
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
-    </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M166" t="str">
+        <f>_xlfn.XLOOKUP(C166,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A167" s="20" t="s">
         <v>102</v>
       </c>
@@ -10206,8 +12304,12 @@
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
-    </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M167" t="str">
+        <f>_xlfn.XLOOKUP(C167,Players!B:B,Players!D:D)</f>
+        <v>19th Hole Cartel</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A168" s="20" t="s">
         <v>102</v>
       </c>
@@ -10240,8 +12342,12 @@
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M168" t="str">
+        <f>_xlfn.XLOOKUP(C168,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A169" s="20" t="s">
         <v>102</v>
       </c>
@@ -10274,8 +12380,12 @@
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M169" t="str">
+        <f>_xlfn.XLOOKUP(C169,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A170" s="20" t="s">
         <v>102</v>
       </c>
@@ -10308,8 +12418,12 @@
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
-    </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M170" t="str">
+        <f>_xlfn.XLOOKUP(C170,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A171" s="20" t="s">
         <v>102</v>
       </c>
@@ -10342,8 +12456,12 @@
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
-    </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M171" t="str">
+        <f>_xlfn.XLOOKUP(C171,Players!B:B,Players!D:D)</f>
+        <v>Just the Tips</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A172" s="20" t="s">
         <v>102</v>
       </c>
@@ -10376,15 +12494,13 @@
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
+      <c r="M172" t="str">
+        <f>_xlfn.XLOOKUP(C172,Players!B:B,Players!D:D)</f>
+        <v>None</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L150" xr:uid="{F3B800D8-26AB-5145-974D-2E86BCED24A0}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L150">
-      <sortCondition ref="A2:A150"/>
-      <sortCondition ref="D2:D150"/>
-      <sortCondition ref="G2:G150"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:M172" xr:uid="{F3B800D8-26AB-5145-974D-2E86BCED24A0}"/>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -10393,6 +12509,332 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA816D42-B639-E949-87B3-41E4444B756C}">
+  <dimension ref="A3:B41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="26">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="26">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="26">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="26">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="26">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="26">
+        <v>199.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="26">
+        <v>160.66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="26">
+        <v>157.66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="26">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="26">
+        <v>155.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="26">
+        <v>153.16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="26">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="26">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="26">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="26">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="26">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="26">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="26">
+        <v>102.66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="26">
+        <v>96.16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="26">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="26">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="26">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="26">
+        <v>75.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="26">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="26">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="26">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="26">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="26">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="26">
+        <v>41.16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="26">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="26">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" s="26">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="26">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B37" s="26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B38" s="26">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="26">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40" s="26">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B41" s="26">
+        <v>4171.9599999999991</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45C531C9-F436-4F48-BF76-4EB6DECD4D79}">
   <dimension ref="A1:F147"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -11092,7 +13534,7 @@
         <v>90</v>
       </c>
       <c r="E33" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="10">
         <v>4</v>
@@ -11113,7 +13555,7 @@
         <v>90</v>
       </c>
       <c r="E34" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="10">
         <v>4</v>
@@ -11134,7 +13576,7 @@
         <v>90</v>
       </c>
       <c r="E35" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" s="10">
         <v>4</v>
@@ -12968,532 +15410,532 @@
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A123" s="25" t="s">
+      <c r="A123" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B123" s="10">
         <f>_xlfn.XLOOKUP(C123,Players!B:B,Players!A:A)</f>
         <v>15</v>
       </c>
-      <c r="C123" s="25" t="s">
+      <c r="C123" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D123" s="25" t="s">
+      <c r="D123" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="E123" s="25">
+      <c r="E123" s="24">
         <v>1</v>
       </c>
-      <c r="F123" s="25">
+      <c r="F123" s="24">
         <v>50</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A124" s="25" t="s">
+      <c r="A124" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B124" s="10">
         <f>_xlfn.XLOOKUP(C124,Players!B:B,Players!A:A)</f>
         <v>34</v>
       </c>
-      <c r="C124" s="25" t="s">
+      <c r="C124" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D124" s="25" t="s">
+      <c r="D124" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="E124" s="25">
+      <c r="E124" s="24">
         <v>2</v>
       </c>
-      <c r="F124" s="25">
+      <c r="F124" s="24">
         <v>25</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A125" s="25" t="s">
+      <c r="A125" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B125" s="10">
         <f>_xlfn.XLOOKUP(C125,Players!B:B,Players!A:A)</f>
         <v>16</v>
       </c>
-      <c r="C125" s="25" t="s">
+      <c r="C125" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="D125" s="25" t="s">
+      <c r="D125" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="E125" s="25">
+      <c r="E125" s="24">
         <v>2</v>
       </c>
-      <c r="F125" s="25">
+      <c r="F125" s="24">
         <v>25</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A126" s="25" t="s">
+      <c r="A126" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B126" s="10">
         <f>_xlfn.XLOOKUP(C126,Players!B:B,Players!A:A)</f>
         <v>18</v>
       </c>
-      <c r="C126" s="25" t="s">
+      <c r="C126" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="D126" s="25" t="s">
+      <c r="D126" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="E126" s="25">
+      <c r="E126" s="24">
         <v>1</v>
       </c>
-      <c r="F126" s="25">
+      <c r="F126" s="24">
         <v>50</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A127" s="25" t="s">
+      <c r="A127" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B127" s="10">
         <f>_xlfn.XLOOKUP(C127,Players!B:B,Players!A:A)</f>
         <v>10</v>
       </c>
-      <c r="C127" s="25" t="s">
+      <c r="C127" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D127" s="25" t="s">
+      <c r="D127" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="E127" s="25">
+      <c r="E127" s="24">
         <v>2</v>
       </c>
-      <c r="F127" s="25">
-        <v>25</v>
+      <c r="F127" s="24">
+        <v>30</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A128" s="25" t="s">
+      <c r="A128" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B128" s="10">
         <f>_xlfn.XLOOKUP(C128,Players!B:B,Players!A:A)</f>
         <v>27</v>
       </c>
-      <c r="C128" s="25" t="s">
+      <c r="C128" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="D128" s="25" t="s">
+      <c r="D128" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="E128" s="25">
+      <c r="E128" s="24">
         <v>3</v>
       </c>
-      <c r="F128" s="25">
-        <v>25</v>
+      <c r="F128" s="24">
+        <v>20</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A129" s="25" t="s">
+      <c r="A129" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B129" s="10">
         <f>_xlfn.XLOOKUP(C129,Players!B:B,Players!A:A)</f>
         <v>20</v>
       </c>
-      <c r="C129" s="25" t="s">
+      <c r="C129" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D129" s="26" t="s">
+      <c r="D129" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="E129" s="25">
+      <c r="E129" s="24">
         <v>1</v>
       </c>
-      <c r="F129" s="25">
+      <c r="F129" s="24">
         <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A130" s="25" t="s">
+      <c r="A130" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B130" s="10">
         <f>_xlfn.XLOOKUP(C130,Players!B:B,Players!A:A)</f>
         <v>15</v>
       </c>
-      <c r="C130" s="25" t="s">
+      <c r="C130" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D130" s="26" t="s">
+      <c r="D130" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="E130" s="25">
+      <c r="E130" s="24">
         <v>1</v>
       </c>
-      <c r="F130" s="25">
+      <c r="F130" s="24">
         <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A131" s="25" t="s">
+      <c r="A131" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B131" s="10">
         <f>_xlfn.XLOOKUP(C131,Players!B:B,Players!A:A)</f>
         <v>34</v>
       </c>
-      <c r="C131" s="25" t="s">
+      <c r="C131" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D131" s="26" t="s">
+      <c r="D131" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="E131" s="25">
+      <c r="E131" s="24">
         <v>1</v>
       </c>
-      <c r="F131" s="25">
+      <c r="F131" s="24">
         <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A132" s="25" t="s">
+      <c r="A132" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B132" s="10">
         <f>_xlfn.XLOOKUP(C132,Players!B:B,Players!A:A)</f>
         <v>18</v>
       </c>
-      <c r="C132" s="25" t="s">
+      <c r="C132" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="D132" s="26" t="s">
+      <c r="D132" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="E132" s="25">
+      <c r="E132" s="24">
         <v>1</v>
       </c>
-      <c r="F132" s="25">
+      <c r="F132" s="24">
         <v>20</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A133" s="25" t="s">
+      <c r="A133" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B133" s="10">
         <f>_xlfn.XLOOKUP(C133,Players!B:B,Players!A:A)</f>
         <v>10</v>
       </c>
-      <c r="C133" s="25" t="s">
+      <c r="C133" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D133" s="26" t="s">
+      <c r="D133" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="E133" s="25">
+      <c r="E133" s="24">
         <v>2</v>
       </c>
-      <c r="F133" s="25">
+      <c r="F133" s="24">
         <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A134" s="25" t="s">
+      <c r="A134" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B134" s="10">
         <f>_xlfn.XLOOKUP(C134,Players!B:B,Players!A:A)</f>
         <v>2</v>
       </c>
-      <c r="C134" s="25" t="s">
+      <c r="C134" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="D134" s="26" t="s">
+      <c r="D134" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="E134" s="25">
+      <c r="E134" s="24">
         <v>2</v>
       </c>
-      <c r="F134" s="25">
+      <c r="F134" s="24">
         <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A135" s="25" t="s">
+      <c r="A135" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B135" s="10">
         <f>_xlfn.XLOOKUP(C135,Players!B:B,Players!A:A)</f>
         <v>15</v>
       </c>
-      <c r="C135" s="25" t="s">
+      <c r="C135" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D135" s="26" t="s">
+      <c r="D135" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="E135" s="25">
+      <c r="E135" s="24">
         <v>1</v>
       </c>
-      <c r="F135" s="25">
+      <c r="F135" s="24">
         <v>15</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A136" s="25" t="s">
+      <c r="A136" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B136" s="10">
         <f>_xlfn.XLOOKUP(C136,Players!B:B,Players!A:A)</f>
         <v>41</v>
       </c>
-      <c r="C136" s="25" t="s">
+      <c r="C136" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D136" s="26" t="s">
+      <c r="D136" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="E136" s="25">
+      <c r="E136" s="24">
         <v>1</v>
       </c>
-      <c r="F136" s="25">
+      <c r="F136" s="24">
         <v>15</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A137" s="25" t="s">
+      <c r="A137" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B137" s="10">
         <f>_xlfn.XLOOKUP(C137,Players!B:B,Players!A:A)</f>
         <v>18</v>
       </c>
-      <c r="C137" s="25" t="s">
+      <c r="C137" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="D137" s="26" t="s">
+      <c r="D137" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="E137" s="25">
+      <c r="E137" s="24">
         <v>1</v>
       </c>
-      <c r="F137" s="25">
+      <c r="F137" s="24">
         <v>20</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A138" s="25" t="s">
+      <c r="A138" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B138" s="10">
         <f>_xlfn.XLOOKUP(C138,Players!B:B,Players!A:A)</f>
         <v>27</v>
       </c>
-      <c r="C138" s="25" t="s">
+      <c r="C138" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="D138" s="26" t="s">
+      <c r="D138" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="E138" s="25">
+      <c r="E138" s="24">
         <v>2</v>
       </c>
-      <c r="F138" s="25">
+      <c r="F138" s="24">
         <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A139" s="25" t="s">
+      <c r="A139" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B139" s="10">
         <f>_xlfn.XLOOKUP(C139,Players!B:B,Players!A:A)</f>
         <v>10</v>
       </c>
-      <c r="C139" s="25" t="s">
+      <c r="C139" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D139" s="26" t="s">
+      <c r="D139" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="E139" s="25">
+      <c r="E139" s="24">
         <v>2</v>
       </c>
-      <c r="F139" s="25">
+      <c r="F139" s="24">
         <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A140" s="25" t="s">
+      <c r="A140" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B140" s="10">
         <f>_xlfn.XLOOKUP(C140,Players!B:B,Players!A:A)</f>
         <v>41</v>
       </c>
-      <c r="C140" s="25" t="s">
+      <c r="C140" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D140" s="26" t="s">
+      <c r="D140" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="E140" s="25" t="s">
+      <c r="E140" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="F140" s="25">
+      <c r="F140" s="24">
         <v>20</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A141" s="25" t="s">
+      <c r="A141" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B141" s="10">
         <f>_xlfn.XLOOKUP(C141,Players!B:B,Players!A:A)</f>
         <v>21</v>
       </c>
-      <c r="C141" s="25" t="s">
+      <c r="C141" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="D141" s="26" t="s">
+      <c r="D141" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="E141" s="25" t="s">
+      <c r="E141" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="F141" s="25">
+      <c r="F141" s="24">
         <v>20</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A142" s="25" t="s">
+      <c r="A142" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B142" s="10">
         <f>_xlfn.XLOOKUP(C142,Players!B:B,Players!A:A)</f>
         <v>47</v>
       </c>
-      <c r="C142" s="25" t="s">
+      <c r="C142" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="D142" s="26" t="s">
+      <c r="D142" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="E142" s="25" t="s">
+      <c r="E142" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="F142" s="25">
-        <v>10</v>
+      <c r="F142" s="24">
+        <v>20</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A143" s="25" t="s">
+      <c r="A143" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B143" s="10">
         <f>_xlfn.XLOOKUP(C143,Players!B:B,Players!A:A)</f>
         <v>35</v>
       </c>
-      <c r="C143" s="25" t="s">
+      <c r="C143" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D143" s="25" t="s">
+      <c r="D143" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="E143" s="25" t="s">
+      <c r="E143" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="F143" s="25">
-        <v>10</v>
+      <c r="F143" s="24">
+        <v>20</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A144" s="25" t="s">
+      <c r="A144" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B144" s="10">
         <f>_xlfn.XLOOKUP(C144,Players!B:B,Players!A:A)</f>
         <v>44</v>
       </c>
-      <c r="C144" s="25" t="s">
+      <c r="C144" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="D144" s="26" t="s">
+      <c r="D144" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="E144" s="25" t="s">
+      <c r="E144" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="F144" s="25">
+      <c r="F144" s="24">
         <v>25</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A145" s="25" t="s">
+      <c r="A145" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B145" s="10">
         <f>_xlfn.XLOOKUP(C145,Players!B:B,Players!A:A)</f>
         <v>44</v>
       </c>
-      <c r="C145" s="25" t="s">
+      <c r="C145" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="D145" s="26" t="s">
+      <c r="D145" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="E145" s="25" t="s">
+      <c r="E145" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="F145" s="25">
+      <c r="F145" s="24">
         <v>25</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A146" s="25" t="s">
+      <c r="A146" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B146" s="10">
         <f>_xlfn.XLOOKUP(C146,Players!B:B,Players!A:A)</f>
         <v>41</v>
       </c>
-      <c r="C146" s="25" t="s">
+      <c r="C146" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D146" s="26" t="s">
+      <c r="D146" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="E146" s="25" t="s">
+      <c r="E146" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="F146" s="25">
+      <c r="F146" s="24">
         <v>25</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A147" s="25" t="s">
+      <c r="A147" s="24" t="s">
         <v>102</v>
       </c>
       <c r="B147" s="10">
         <f>_xlfn.XLOOKUP(C147,Players!B:B,Players!A:A)</f>
         <v>20</v>
       </c>
-      <c r="C147" s="25" t="s">
+      <c r="C147" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D147" s="26" t="s">
+      <c r="D147" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="E147" s="25" t="s">
+      <c r="E147" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="F147" s="25">
+      <c r="F147" s="24">
         <v>25</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F122" xr:uid="{45C531C9-F436-4F48-BF76-4EB6DECD4D79}"/>
+  <autoFilter ref="A1:F147" xr:uid="{45C531C9-F436-4F48-BF76-4EB6DECD4D79}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F122">
     <sortCondition ref="A2:A122"/>
     <sortCondition ref="D2:D122"/>
@@ -13503,7 +15945,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4723CA7E-3717-814A-BF66-62A12120D4EC}">
   <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -14903,7 +17345,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F879FA0E-F1DC-144C-8C37-AC2E1B6DC0E5}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -14932,43 +17374,36 @@
       <c r="A4" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B4" s="23"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="23"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B6" s="23"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="23"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="23"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="23"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="B10" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
